--- a/_semantics/plan-vilochnye-pogruzchiki.xlsx
+++ b/_semantics/plan-vilochnye-pogruzchiki.xlsx
@@ -581,14 +581,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I32"/>
+  <dimension ref="A1:I42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="46" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="48" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
@@ -598,14 +598,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Вилочные погрузчики — план статей</t>
+          <t>Вилочные погрузчики — план статей (v2, расширенный)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>26 статей, только вилочные погрузчики. Источник: 19 файлов Букварикса, точная частотность, регион «Весь мир» (не Россия — см. лист «Как читать»).</t>
+          <t>37 статей, только вилочные погрузчики. Источник: 19 файлов Букварикса, точная частотность, регион «Весь мир» (не Россия — см. лист «Как читать»).</t>
         </is>
       </c>
     </row>
@@ -683,10 +683,10 @@
         </is>
       </c>
       <c r="F5" s="4" t="n">
-        <v>11585</v>
+        <v>10531</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>6563</v>
+        <v>6055</v>
       </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
@@ -695,7 +695,7 @@
       </c>
       <c r="I5" s="6" t="inlineStr">
         <is>
-          <t>Головной запрос «вилочный погрузчик» и общие формы — не попавшее в специализированные статьи ниже.</t>
+          <t>Головной запрос «вилочный погрузчик» и все формы, не забранные специализированными статьями выше.</t>
         </is>
       </c>
     </row>
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="F6" s="7" t="n">
-        <v>250</v>
+        <v>197</v>
       </c>
       <c r="G6" s="7" t="n">
-        <v>51</v>
+        <v>30</v>
       </c>
       <c r="H6" s="8" t="inlineStr">
         <is>
@@ -761,10 +761,10 @@
         </is>
       </c>
       <c r="F7" s="7" t="n">
-        <v>2393</v>
+        <v>2007</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>1144</v>
+        <v>792</v>
       </c>
       <c r="H7" s="8" t="inlineStr">
         <is>
@@ -798,10 +798,10 @@
         </is>
       </c>
       <c r="F8" s="7" t="n">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="H8" s="8" t="inlineStr">
         <is>
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="F9" s="7" t="n">
-        <v>668</v>
+        <v>662</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
@@ -863,63 +863,63 @@
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
+          <t>Мачта, высота подъёма и габариты вилочного погрузчика</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="inlineStr">
+        <is>
+          <t>/articles/machta-vysota-podema-i-gabarity-vilochnogo-pogruzchika/</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="n">
+        <v>204</v>
+      </c>
+      <c r="G10" s="7" t="n">
+        <v>106</v>
+      </c>
+      <c r="H10" s="8" t="inlineStr">
+        <is>
+          <t>Не начато</t>
+        </is>
+      </c>
+      <c r="I10" s="9" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>Неделя 4</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>Выбор и виды</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
           <t>Вилочный погрузчик и автопогрузчик — в чём разница с рохлей и штабелёром</t>
         </is>
       </c>
-      <c r="E10" s="9" t="inlineStr">
+      <c r="E11" s="9" t="inlineStr">
         <is>
           <t>/articles/vilochnyy-pogruzchik-i-avtopogruzchik/</t>
         </is>
       </c>
-      <c r="F10" s="7" t="n">
-        <v>250</v>
-      </c>
-      <c r="G10" s="7" t="n">
-        <v>22</v>
-      </c>
-      <c r="H10" s="8" t="inlineStr">
+      <c r="F11" s="7" t="n">
+        <v>526</v>
+      </c>
+      <c r="G11" s="7" t="n">
+        <v>68</v>
+      </c>
+      <c r="H11" s="8" t="inlineStr">
         <is>
           <t>Не начато</t>
         </is>
       </c>
-      <c r="I10" s="9" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="B11" s="11" t="inlineStr">
-        <is>
-          <t>Неделя 4</t>
-        </is>
-      </c>
-      <c r="C11" s="11" t="inlineStr">
-        <is>
-          <t>Тоннаж</t>
-        </is>
-      </c>
-      <c r="D11" s="12" t="inlineStr">
-        <is>
-          <t>Вилочный погрузчик до 2 тонн: компактные модели для небольшого склада</t>
-        </is>
-      </c>
-      <c r="E11" s="12" t="inlineStr">
-        <is>
-          <t>/articles/vilochnyy-pogruzchik-do-2-tonn/</t>
-        </is>
-      </c>
-      <c r="F11" s="10" t="n">
-        <v>62</v>
-      </c>
-      <c r="G11" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="H11" s="11" t="inlineStr">
-        <is>
-          <t>Не начато</t>
-        </is>
-      </c>
-      <c r="I11" s="12" t="inlineStr"/>
+      <c r="I11" s="9" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="10" t="n">
@@ -937,19 +937,19 @@
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
-          <t>Вилочный погрузчик 3 тонны: какие задачи закрывает</t>
+          <t>Вилочный погрузчик до 2 тонн: компактные модели для небольшого склада</t>
         </is>
       </c>
       <c r="E12" s="12" t="inlineStr">
         <is>
-          <t>/articles/vilochnyy-pogruzchik-3-tonny/</t>
+          <t>/articles/vilochnyy-pogruzchik-do-2-tonn/</t>
         </is>
       </c>
       <c r="F12" s="10" t="n">
-        <v>352</v>
+        <v>110</v>
       </c>
       <c r="G12" s="10" t="n">
-        <v>86</v>
+        <v>51</v>
       </c>
       <c r="H12" s="11" t="inlineStr">
         <is>
@@ -974,19 +974,19 @@
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>Вилочный погрузчик 5 тонн: характеристики и подбор</t>
+          <t>Вилочный погрузчик 3 тонны: какие задачи закрывает</t>
         </is>
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>/articles/vilochnyy-pogruzchik-5-tonn/</t>
+          <t>/articles/vilochnyy-pogruzchik-3-tonny/</t>
         </is>
       </c>
       <c r="F13" s="10" t="n">
-        <v>446</v>
+        <v>317</v>
       </c>
       <c r="G13" s="10" t="n">
-        <v>194</v>
+        <v>76</v>
       </c>
       <c r="H13" s="11" t="inlineStr">
         <is>
@@ -1011,63 +1011,63 @@
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
+          <t>Вилочный погрузчик 5 тонн: характеристики и подбор</t>
+        </is>
+      </c>
+      <c r="E14" s="12" t="inlineStr">
+        <is>
+          <t>/articles/vilochnyy-pogruzchik-5-tonn/</t>
+        </is>
+      </c>
+      <c r="F14" s="10" t="n">
+        <v>402</v>
+      </c>
+      <c r="G14" s="10" t="n">
+        <v>169</v>
+      </c>
+      <c r="H14" s="11" t="inlineStr">
+        <is>
+          <t>Не начато</t>
+        </is>
+      </c>
+      <c r="I14" s="12" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="10" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="11" t="inlineStr">
+        <is>
+          <t>Неделя 6</t>
+        </is>
+      </c>
+      <c r="C15" s="11" t="inlineStr">
+        <is>
+          <t>Тоннаж</t>
+        </is>
+      </c>
+      <c r="D15" s="12" t="inlineStr">
+        <is>
           <t>Вилочный погрузчик от 7 тонн: тяжёлый класс для металла и контейнеров</t>
         </is>
       </c>
-      <c r="E14" s="12" t="inlineStr">
+      <c r="E15" s="12" t="inlineStr">
         <is>
           <t>/articles/vilochnyy-pogruzchik-ot-7-tonn/</t>
         </is>
       </c>
-      <c r="F14" s="10" t="n">
-        <v>389</v>
-      </c>
-      <c r="G14" s="10" t="n">
-        <v>67</v>
-      </c>
-      <c r="H14" s="11" t="inlineStr">
+      <c r="F15" s="10" t="n">
+        <v>369</v>
+      </c>
+      <c r="G15" s="10" t="n">
+        <v>64</v>
+      </c>
+      <c r="H15" s="11" t="inlineStr">
         <is>
           <t>Не начато</t>
         </is>
       </c>
-      <c r="I14" s="12" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="13" t="n">
-        <v>11</v>
-      </c>
-      <c r="B15" s="14" t="inlineStr">
-        <is>
-          <t>Неделя 6</t>
-        </is>
-      </c>
-      <c r="C15" s="14" t="inlineStr">
-        <is>
-          <t>Покупка</t>
-        </is>
-      </c>
-      <c r="D15" s="15" t="inlineStr">
-        <is>
-          <t>Купить вилочный погрузчик: как устроена сделка и на что уходит время</t>
-        </is>
-      </c>
-      <c r="E15" s="15" t="inlineStr">
-        <is>
-          <t>/articles/kupit-vilochnyy-pogruzchik/</t>
-        </is>
-      </c>
-      <c r="F15" s="13" t="n">
-        <v>3899</v>
-      </c>
-      <c r="G15" s="13" t="n">
-        <v>1146</v>
-      </c>
-      <c r="H15" s="14" t="inlineStr">
-        <is>
-          <t>Не начато</t>
-        </is>
-      </c>
-      <c r="I15" s="15" t="inlineStr"/>
+      <c r="I15" s="12" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="13" t="n">
@@ -1085,137 +1085,137 @@
       </c>
       <c r="D16" s="15" t="inlineStr">
         <is>
+          <t>Купить вилочный погрузчик: как устроена сделка и на что уходит время</t>
+        </is>
+      </c>
+      <c r="E16" s="15" t="inlineStr">
+        <is>
+          <t>/articles/kupit-vilochnyy-pogruzchik/</t>
+        </is>
+      </c>
+      <c r="F16" s="13" t="n">
+        <v>3560</v>
+      </c>
+      <c r="G16" s="13" t="n">
+        <v>804</v>
+      </c>
+      <c r="H16" s="14" t="inlineStr">
+        <is>
+          <t>Не начато</t>
+        </is>
+      </c>
+      <c r="I16" s="15" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="13" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" s="14" t="inlineStr">
+        <is>
+          <t>Неделя 7</t>
+        </is>
+      </c>
+      <c r="C17" s="14" t="inlineStr">
+        <is>
+          <t>Покупка</t>
+        </is>
+      </c>
+      <c r="D17" s="15" t="inlineStr">
+        <is>
           <t>Вилочный погрузчик б/у: на что смотреть при покупке и как проверить перед сделкой</t>
         </is>
       </c>
-      <c r="E16" s="15" t="inlineStr">
+      <c r="E17" s="15" t="inlineStr">
         <is>
           <t>/articles/vilochnyy-pogruzchik-bu/</t>
         </is>
       </c>
-      <c r="F16" s="13" t="n">
-        <v>2049</v>
-      </c>
-      <c r="G16" s="13" t="n">
-        <v>963</v>
-      </c>
-      <c r="H16" s="14" t="inlineStr">
+      <c r="F17" s="13" t="n">
+        <v>1650</v>
+      </c>
+      <c r="G17" s="13" t="n">
+        <v>840</v>
+      </c>
+      <c r="H17" s="14" t="inlineStr">
         <is>
           <t>Не начато</t>
         </is>
       </c>
-      <c r="I16" s="15" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="16" t="n">
-        <v>13</v>
-      </c>
-      <c r="B17" s="17" t="inlineStr">
-        <is>
-          <t>Неделя 7</t>
-        </is>
-      </c>
-      <c r="C17" s="17" t="inlineStr">
-        <is>
-          <t>Бренды</t>
-        </is>
-      </c>
-      <c r="D17" s="18" t="inlineStr">
-        <is>
-          <t>Heli: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
-        </is>
-      </c>
-      <c r="E17" s="18" t="inlineStr">
-        <is>
-          <t>/articles/heli/</t>
-        </is>
-      </c>
-      <c r="F17" s="16" t="n">
-        <v>2880</v>
-      </c>
-      <c r="G17" s="16" t="n">
-        <v>1390</v>
-      </c>
-      <c r="H17" s="17" t="inlineStr">
+      <c r="I17" s="15" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="13" t="n">
+        <v>14</v>
+      </c>
+      <c r="B18" s="14" t="inlineStr">
+        <is>
+          <t>Неделя 8</t>
+        </is>
+      </c>
+      <c r="C18" s="14" t="inlineStr">
+        <is>
+          <t>Покупка</t>
+        </is>
+      </c>
+      <c r="D18" s="15" t="inlineStr">
+        <is>
+          <t>Из чего складывается цена вилочного погрузчика</t>
+        </is>
+      </c>
+      <c r="E18" s="15" t="inlineStr">
+        <is>
+          <t>/articles/iz-chego-skladyvaetsya-cena-vilochnogo-pogruzchika/</t>
+        </is>
+      </c>
+      <c r="F18" s="13" t="n">
+        <v>379</v>
+      </c>
+      <c r="G18" s="13" t="n">
+        <v>353</v>
+      </c>
+      <c r="H18" s="14" t="inlineStr">
         <is>
           <t>Не начато</t>
         </is>
       </c>
-      <c r="I17" s="18" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="16" t="n">
-        <v>14</v>
-      </c>
-      <c r="B18" s="17" t="inlineStr">
+      <c r="I18" s="15" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="13" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" s="14" t="inlineStr">
         <is>
           <t>Неделя 8</t>
         </is>
       </c>
-      <c r="C18" s="17" t="inlineStr">
-        <is>
-          <t>Бренды</t>
-        </is>
-      </c>
-      <c r="D18" s="18" t="inlineStr">
-        <is>
-          <t>Toyota: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
-        </is>
-      </c>
-      <c r="E18" s="18" t="inlineStr">
-        <is>
-          <t>/articles/toyota/</t>
-        </is>
-      </c>
-      <c r="F18" s="16" t="n">
-        <v>567</v>
-      </c>
-      <c r="G18" s="16" t="n">
-        <v>600</v>
-      </c>
-      <c r="H18" s="17" t="inlineStr">
+      <c r="C19" s="14" t="inlineStr">
+        <is>
+          <t>Покупка</t>
+        </is>
+      </c>
+      <c r="D19" s="15" t="inlineStr">
+        <is>
+          <t>Вилочный погрузчик на Авито: как не купить проблемный</t>
+        </is>
+      </c>
+      <c r="E19" s="15" t="inlineStr">
+        <is>
+          <t>/articles/vilochnyy-pogruzchik-na-avito/</t>
+        </is>
+      </c>
+      <c r="F19" s="13" t="n">
+        <v>544</v>
+      </c>
+      <c r="G19" s="13" t="n">
+        <v>198</v>
+      </c>
+      <c r="H19" s="14" t="inlineStr">
         <is>
           <t>Не начато</t>
         </is>
       </c>
-      <c r="I18" s="18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="16" t="n">
-        <v>15</v>
-      </c>
-      <c r="B19" s="17" t="inlineStr">
-        <is>
-          <t>Неделя 8</t>
-        </is>
-      </c>
-      <c r="C19" s="17" t="inlineStr">
-        <is>
-          <t>Бренды</t>
-        </is>
-      </c>
-      <c r="D19" s="18" t="inlineStr">
-        <is>
-          <t>Komatsu: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
-        </is>
-      </c>
-      <c r="E19" s="18" t="inlineStr">
-        <is>
-          <t>/articles/komatsu/</t>
-        </is>
-      </c>
-      <c r="F19" s="16" t="n">
-        <v>498</v>
-      </c>
-      <c r="G19" s="16" t="n">
-        <v>392</v>
-      </c>
-      <c r="H19" s="17" t="inlineStr">
-        <is>
-          <t>Не начато</t>
-        </is>
-      </c>
-      <c r="I19" s="18" t="inlineStr"/>
+      <c r="I19" s="15" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="16" t="n">
@@ -1233,19 +1233,19 @@
       </c>
       <c r="D20" s="18" t="inlineStr">
         <is>
-          <t>Львовский, Балканкар, ТВЭКС, Амкодор — советские и постсоветские марки: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
+          <t>Heli: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
         </is>
       </c>
       <c r="E20" s="18" t="inlineStr">
         <is>
-          <t>/articles/lvovskiy-balkankar-tveks-amkodor/</t>
+          <t>/articles/heli/</t>
         </is>
       </c>
       <c r="F20" s="16" t="n">
-        <v>821</v>
+        <v>2965</v>
       </c>
       <c r="G20" s="16" t="n">
-        <v>396</v>
+        <v>1499</v>
       </c>
       <c r="H20" s="17" t="inlineStr">
         <is>
@@ -1270,19 +1270,19 @@
       </c>
       <c r="D21" s="18" t="inlineStr">
         <is>
-          <t>Still, Linde, Jungheinrich, Yale, Hyster, Doosan, Clark — европейские и корейские марки: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
+          <t>Toyota: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
         </is>
       </c>
       <c r="E21" s="18" t="inlineStr">
         <is>
-          <t>/articles/still-linde-jungheinrich-yale-hyster-doosan-clark/</t>
+          <t>/articles/toyota/</t>
         </is>
       </c>
       <c r="F21" s="16" t="n">
-        <v>393</v>
+        <v>649</v>
       </c>
       <c r="G21" s="16" t="n">
-        <v>280</v>
+        <v>650</v>
       </c>
       <c r="H21" s="17" t="inlineStr">
         <is>
@@ -1307,19 +1307,19 @@
       </c>
       <c r="D22" s="18" t="inlineStr">
         <is>
-          <t>LiuGong и Lonking: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
+          <t>Komatsu: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
         </is>
       </c>
       <c r="E22" s="18" t="inlineStr">
         <is>
-          <t>/articles/liugong-i-lonking/</t>
+          <t>/articles/komatsu/</t>
         </is>
       </c>
       <c r="F22" s="16" t="n">
-        <v>272</v>
+        <v>539</v>
       </c>
       <c r="G22" s="16" t="n">
-        <v>81</v>
+        <v>435</v>
       </c>
       <c r="H22" s="17" t="inlineStr">
         <is>
@@ -1344,19 +1344,19 @@
       </c>
       <c r="D23" s="18" t="inlineStr">
         <is>
-          <t>Nissan, Mitsubishi, TCM: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
+          <t>Львовский погрузчик: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
         </is>
       </c>
       <c r="E23" s="18" t="inlineStr">
         <is>
-          <t>/articles/nissan-mitsubishi-tcm/</t>
+          <t>/articles/lvovskiy-pogruzchik/</t>
         </is>
       </c>
       <c r="F23" s="16" t="n">
-        <v>251</v>
+        <v>449</v>
       </c>
       <c r="G23" s="16" t="n">
-        <v>263</v>
+        <v>223</v>
       </c>
       <c r="H23" s="17" t="inlineStr">
         <is>
@@ -1381,19 +1381,19 @@
       </c>
       <c r="D24" s="18" t="inlineStr">
         <is>
-          <t>Hangcha: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
+          <t>JAC: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
         </is>
       </c>
       <c r="E24" s="18" t="inlineStr">
         <is>
-          <t>/articles/hangcha/</t>
+          <t>/articles/jac/</t>
         </is>
       </c>
       <c r="F24" s="16" t="n">
-        <v>224</v>
+        <v>303</v>
       </c>
       <c r="G24" s="16" t="n">
-        <v>84</v>
+        <v>209</v>
       </c>
       <c r="H24" s="17" t="inlineStr">
         <is>
@@ -1418,19 +1418,19 @@
       </c>
       <c r="D25" s="18" t="inlineStr">
         <is>
-          <t>JAC: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
+          <t>Hangcha: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
         </is>
       </c>
       <c r="E25" s="18" t="inlineStr">
         <is>
-          <t>/articles/jac/</t>
+          <t>/articles/hangcha/</t>
         </is>
       </c>
       <c r="F25" s="16" t="n">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="G25" s="16" t="n">
-        <v>165</v>
+        <v>111</v>
       </c>
       <c r="H25" s="17" t="inlineStr">
         <is>
@@ -1455,19 +1455,19 @@
       </c>
       <c r="D26" s="18" t="inlineStr">
         <is>
-          <t>Manitou, Kalmar, Zoomlion, Shantui: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
+          <t>LiuGong: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
         </is>
       </c>
       <c r="E26" s="18" t="inlineStr">
         <is>
-          <t>/articles/manitou-kalmar-zoomlion-shantui/</t>
+          <t>/articles/liugong/</t>
         </is>
       </c>
       <c r="F26" s="16" t="n">
-        <v>382</v>
+        <v>81</v>
       </c>
       <c r="G26" s="16" t="n">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="H26" s="17" t="inlineStr">
         <is>
@@ -1492,191 +1492,561 @@
       </c>
       <c r="D27" s="18" t="inlineStr">
         <is>
-          <t>Погрузчик «кара»: что это за техника и чем она отличается от современных моделей</t>
+          <t>Lonking: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
         </is>
       </c>
       <c r="E27" s="18" t="inlineStr">
         <is>
-          <t>/articles/pogruzchik-kara/</t>
+          <t>/articles/lonking/</t>
         </is>
       </c>
       <c r="F27" s="16" t="n">
-        <v>138</v>
+        <v>206</v>
       </c>
       <c r="G27" s="16" t="n">
+        <v>53</v>
+      </c>
+      <c r="H27" s="17" t="inlineStr">
+        <is>
+          <t>Не начато</t>
+        </is>
+      </c>
+      <c r="I27" s="18" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="16" t="n">
         <v>24</v>
       </c>
-      <c r="H27" s="17" t="inlineStr">
+      <c r="B28" s="17" t="inlineStr">
+        <is>
+          <t>Неделя 13</t>
+        </is>
+      </c>
+      <c r="C28" s="17" t="inlineStr">
+        <is>
+          <t>Бренды</t>
+        </is>
+      </c>
+      <c r="D28" s="18" t="inlineStr">
+        <is>
+          <t>Zoomlion: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
+        </is>
+      </c>
+      <c r="E28" s="18" t="inlineStr">
+        <is>
+          <t>/articles/zoomlion/</t>
+        </is>
+      </c>
+      <c r="F28" s="16" t="n">
+        <v>194</v>
+      </c>
+      <c r="G28" s="16" t="n">
+        <v>30</v>
+      </c>
+      <c r="H28" s="17" t="inlineStr">
         <is>
           <t>Не начато</t>
         </is>
       </c>
-      <c r="I27" s="18" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="19" t="n">
-        <v>24</v>
-      </c>
-      <c r="B28" s="20" t="inlineStr">
+      <c r="I28" s="18" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="16" t="n">
+        <v>25</v>
+      </c>
+      <c r="B29" s="17" t="inlineStr">
         <is>
           <t>Неделя 13</t>
         </is>
       </c>
-      <c r="C28" s="20" t="inlineStr">
+      <c r="C29" s="17" t="inlineStr">
+        <is>
+          <t>Бренды</t>
+        </is>
+      </c>
+      <c r="D29" s="18" t="inlineStr">
+        <is>
+          <t>Doosan: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
+        </is>
+      </c>
+      <c r="E29" s="18" t="inlineStr">
+        <is>
+          <t>/articles/doosan/</t>
+        </is>
+      </c>
+      <c r="F29" s="16" t="n">
+        <v>159</v>
+      </c>
+      <c r="G29" s="16" t="n">
+        <v>111</v>
+      </c>
+      <c r="H29" s="17" t="inlineStr">
+        <is>
+          <t>Не начато</t>
+        </is>
+      </c>
+      <c r="I29" s="18" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="16" t="n">
+        <v>26</v>
+      </c>
+      <c r="B30" s="17" t="inlineStr">
+        <is>
+          <t>Неделя 14</t>
+        </is>
+      </c>
+      <c r="C30" s="17" t="inlineStr">
+        <is>
+          <t>Бренды</t>
+        </is>
+      </c>
+      <c r="D30" s="18" t="inlineStr">
+        <is>
+          <t>Балканкар и «Кара»: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
+        </is>
+      </c>
+      <c r="E30" s="18" t="inlineStr">
+        <is>
+          <t>/articles/balkankar-i-kara/</t>
+        </is>
+      </c>
+      <c r="F30" s="16" t="n">
+        <v>149</v>
+      </c>
+      <c r="G30" s="16" t="n">
+        <v>130</v>
+      </c>
+      <c r="H30" s="17" t="inlineStr">
+        <is>
+          <t>Не начато</t>
+        </is>
+      </c>
+      <c r="I30" s="18" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="16" t="n">
+        <v>27</v>
+      </c>
+      <c r="B31" s="17" t="inlineStr">
+        <is>
+          <t>Неделя 14</t>
+        </is>
+      </c>
+      <c r="C31" s="17" t="inlineStr">
+        <is>
+          <t>Бренды</t>
+        </is>
+      </c>
+      <c r="D31" s="18" t="inlineStr">
+        <is>
+          <t>Погрузчик «кара» без привязки к марке: что это за техника</t>
+        </is>
+      </c>
+      <c r="E31" s="18" t="inlineStr">
+        <is>
+          <t>/articles/pogruzchik-kara-bez-privyazki-k-marke/</t>
+        </is>
+      </c>
+      <c r="F31" s="16" t="n">
+        <v>141</v>
+      </c>
+      <c r="G31" s="16" t="n">
+        <v>29</v>
+      </c>
+      <c r="H31" s="17" t="inlineStr">
+        <is>
+          <t>Не начато</t>
+        </is>
+      </c>
+      <c r="I31" s="18" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="16" t="n">
+        <v>28</v>
+      </c>
+      <c r="B32" s="17" t="inlineStr">
+        <is>
+          <t>Неделя 15</t>
+        </is>
+      </c>
+      <c r="C32" s="17" t="inlineStr">
+        <is>
+          <t>Бренды</t>
+        </is>
+      </c>
+      <c r="D32" s="18" t="inlineStr">
+        <is>
+          <t>ТВЭКС и Амкодор: вилочные погрузчики российского и белорусского производства</t>
+        </is>
+      </c>
+      <c r="E32" s="18" t="inlineStr">
+        <is>
+          <t>/articles/tveks-i-amkodor/</t>
+        </is>
+      </c>
+      <c r="F32" s="16" t="n">
+        <v>188</v>
+      </c>
+      <c r="G32" s="16" t="n">
+        <v>58</v>
+      </c>
+      <c r="H32" s="17" t="inlineStr">
+        <is>
+          <t>Не начато</t>
+        </is>
+      </c>
+      <c r="I32" s="18" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="16" t="n">
+        <v>29</v>
+      </c>
+      <c r="B33" s="17" t="inlineStr">
+        <is>
+          <t>Неделя 15</t>
+        </is>
+      </c>
+      <c r="C33" s="17" t="inlineStr">
+        <is>
+          <t>Бренды</t>
+        </is>
+      </c>
+      <c r="D33" s="18" t="inlineStr">
+        <is>
+          <t>Советские и постсоветские вилочные погрузчики: обзор марок</t>
+        </is>
+      </c>
+      <c r="E33" s="18" t="inlineStr">
+        <is>
+          <t>/articles/sovetskie-i-postsovetskie-vilochnye-pogruzchiki/</t>
+        </is>
+      </c>
+      <c r="F33" s="16" t="n">
+        <v>159</v>
+      </c>
+      <c r="G33" s="16" t="n">
+        <v>28</v>
+      </c>
+      <c r="H33" s="17" t="inlineStr">
+        <is>
+          <t>Не начато</t>
+        </is>
+      </c>
+      <c r="I33" s="18" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="16" t="n">
+        <v>30</v>
+      </c>
+      <c r="B34" s="17" t="inlineStr">
+        <is>
+          <t>Неделя 16</t>
+        </is>
+      </c>
+      <c r="C34" s="17" t="inlineStr">
+        <is>
+          <t>Бренды</t>
+        </is>
+      </c>
+      <c r="D34" s="18" t="inlineStr">
+        <is>
+          <t>Nissan, Mitsubishi, TCM, Manitou, Kalmar, Shantui: редкие бренды на вторичном рынке</t>
+        </is>
+      </c>
+      <c r="E34" s="18" t="inlineStr">
+        <is>
+          <t>/articles/nissan-mitsubishi-tcm-manitou-kalmar-shantui/</t>
+        </is>
+      </c>
+      <c r="F34" s="16" t="n">
+        <v>469</v>
+      </c>
+      <c r="G34" s="16" t="n">
+        <v>325</v>
+      </c>
+      <c r="H34" s="17" t="inlineStr">
+        <is>
+          <t>Не начато</t>
+        </is>
+      </c>
+      <c r="I34" s="18" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="16" t="n">
+        <v>31</v>
+      </c>
+      <c r="B35" s="17" t="inlineStr">
+        <is>
+          <t>Неделя 16</t>
+        </is>
+      </c>
+      <c r="C35" s="17" t="inlineStr">
+        <is>
+          <t>Бренды</t>
+        </is>
+      </c>
+      <c r="D35" s="18" t="inlineStr">
+        <is>
+          <t>Still, Linde, Jungheinrich, Yale, Hyster, Clark: европейские бренды на вторичном рынке</t>
+        </is>
+      </c>
+      <c r="E35" s="18" t="inlineStr">
+        <is>
+          <t>/articles/still-linde-jungheinrich-yale-hyster-clark/</t>
+        </is>
+      </c>
+      <c r="F35" s="16" t="n">
+        <v>273</v>
+      </c>
+      <c r="G35" s="16" t="n">
+        <v>221</v>
+      </c>
+      <c r="H35" s="17" t="inlineStr">
+        <is>
+          <t>Не начато</t>
+        </is>
+      </c>
+      <c r="I35" s="18" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="19" t="n">
+        <v>32</v>
+      </c>
+      <c r="B36" s="20" t="inlineStr">
+        <is>
+          <t>Неделя 17</t>
+        </is>
+      </c>
+      <c r="C36" s="20" t="inlineStr">
         <is>
           <t>Эксплуатация</t>
         </is>
       </c>
-      <c r="D28" s="21" t="inlineStr">
+      <c r="D36" s="21" t="inlineStr">
         <is>
           <t>Навесное оборудование для вилочного погрузчика: какое бывает и зачем</t>
         </is>
       </c>
-      <c r="E28" s="21" t="inlineStr">
+      <c r="E36" s="21" t="inlineStr">
         <is>
           <t>/articles/navesnoe-oborudovanie-dlya-vilochnogo-pogruzchika/</t>
         </is>
       </c>
-      <c r="F28" s="19" t="n">
-        <v>593</v>
-      </c>
-      <c r="G28" s="19" t="n">
-        <v>108</v>
-      </c>
-      <c r="H28" s="20" t="inlineStr">
+      <c r="F36" s="19" t="n">
+        <v>987</v>
+      </c>
+      <c r="G36" s="19" t="n">
+        <v>165</v>
+      </c>
+      <c r="H36" s="20" t="inlineStr">
         <is>
           <t>Не начато</t>
         </is>
       </c>
-      <c r="I28" s="21" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="19" t="n">
-        <v>25</v>
-      </c>
-      <c r="B29" s="20" t="inlineStr">
-        <is>
-          <t>Неделя 13</t>
-        </is>
-      </c>
-      <c r="C29" s="20" t="inlineStr">
+      <c r="I36" s="21" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="19" t="n">
+        <v>33</v>
+      </c>
+      <c r="B37" s="20" t="inlineStr">
+        <is>
+          <t>Неделя 17</t>
+        </is>
+      </c>
+      <c r="C37" s="20" t="inlineStr">
         <is>
           <t>Эксплуатация</t>
         </is>
       </c>
-      <c r="D29" s="21" t="inlineStr">
+      <c r="D37" s="21" t="inlineStr">
+        <is>
+          <t>Шины для вилочного погрузчика: какие бывают и как выбрать</t>
+        </is>
+      </c>
+      <c r="E37" s="21" t="inlineStr">
+        <is>
+          <t>/articles/shiny-dlya-vilochnogo-pogruzchika/</t>
+        </is>
+      </c>
+      <c r="F37" s="19" t="n">
+        <v>156</v>
+      </c>
+      <c r="G37" s="19" t="n">
+        <v>109</v>
+      </c>
+      <c r="H37" s="20" t="inlineStr">
+        <is>
+          <t>Не начато</t>
+        </is>
+      </c>
+      <c r="I37" s="21" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="19" t="n">
+        <v>34</v>
+      </c>
+      <c r="B38" s="20" t="inlineStr">
+        <is>
+          <t>Неделя 18</t>
+        </is>
+      </c>
+      <c r="C38" s="20" t="inlineStr">
+        <is>
+          <t>Эксплуатация</t>
+        </is>
+      </c>
+      <c r="D38" s="21" t="inlineStr">
+        <is>
+          <t>Ремонт и диагностика неисправностей вилочного погрузчика</t>
+        </is>
+      </c>
+      <c r="E38" s="21" t="inlineStr">
+        <is>
+          <t>/articles/remont-i-diagnostika-neispravnostey-vilochnogo-pogruzchika/</t>
+        </is>
+      </c>
+      <c r="F38" s="19" t="n">
+        <v>435</v>
+      </c>
+      <c r="G38" s="19" t="n">
+        <v>329</v>
+      </c>
+      <c r="H38" s="20" t="inlineStr">
+        <is>
+          <t>Не начато</t>
+        </is>
+      </c>
+      <c r="I38" s="21" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="19" t="n">
+        <v>35</v>
+      </c>
+      <c r="B39" s="20" t="inlineStr">
+        <is>
+          <t>Неделя 18</t>
+        </is>
+      </c>
+      <c r="C39" s="20" t="inlineStr">
+        <is>
+          <t>Эксплуатация</t>
+        </is>
+      </c>
+      <c r="D39" s="21" t="inlineStr">
         <is>
           <t>Запчасти для вилочного погрузчика: что изнашивается быстрее всего</t>
         </is>
       </c>
-      <c r="E29" s="21" t="inlineStr">
+      <c r="E39" s="21" t="inlineStr">
         <is>
           <t>/articles/zapchasti-dlya-vilochnogo-pogruzchika/</t>
         </is>
       </c>
-      <c r="F29" s="19" t="n">
-        <v>1022</v>
-      </c>
-      <c r="G29" s="19" t="n">
-        <v>656</v>
-      </c>
-      <c r="H29" s="20" t="inlineStr">
+      <c r="F39" s="19" t="n">
+        <v>713</v>
+      </c>
+      <c r="G39" s="19" t="n">
+        <v>562</v>
+      </c>
+      <c r="H39" s="20" t="inlineStr">
         <is>
           <t>Не начато</t>
         </is>
       </c>
-      <c r="I29" s="21" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="19" t="n">
-        <v>26</v>
-      </c>
-      <c r="B30" s="20" t="inlineStr">
-        <is>
-          <t>Неделя 14</t>
-        </is>
-      </c>
-      <c r="C30" s="20" t="inlineStr">
+      <c r="I39" s="21" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="19" t="n">
+        <v>36</v>
+      </c>
+      <c r="B40" s="20" t="inlineStr">
+        <is>
+          <t>Неделя 19</t>
+        </is>
+      </c>
+      <c r="C40" s="20" t="inlineStr">
         <is>
           <t>Эксплуатация</t>
         </is>
       </c>
-      <c r="D30" s="21" t="inlineStr">
+      <c r="D40" s="21" t="inlineStr">
         <is>
           <t>Регистрация вилочного погрузчика в Гостехнадзоре: что нужно знать владельцу</t>
         </is>
       </c>
-      <c r="E30" s="21" t="inlineStr">
+      <c r="E40" s="21" t="inlineStr">
         <is>
           <t>/articles/registraciya-vilochnogo-pogruzchika-v-gostehnadzore/</t>
         </is>
       </c>
-      <c r="F30" s="19" t="n">
+      <c r="F40" s="19" t="n">
         <v>517</v>
       </c>
-      <c r="G30" s="19" t="n">
+      <c r="G40" s="19" t="n">
         <v>143</v>
       </c>
-      <c r="H30" s="20" t="inlineStr">
+      <c r="H40" s="20" t="inlineStr">
         <is>
           <t>Не начато</t>
         </is>
       </c>
-      <c r="I30" s="21" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="22" t="n">
-        <v>27</v>
-      </c>
-      <c r="B31" s="23" t="inlineStr">
-        <is>
-          <t>Неделя 14</t>
-        </is>
-      </c>
-      <c r="C31" s="23" t="inlineStr">
+      <c r="I40" s="21" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="22" t="n">
+        <v>37</v>
+      </c>
+      <c r="B41" s="23" t="inlineStr">
+        <is>
+          <t>Неделя 19</t>
+        </is>
+      </c>
+      <c r="C41" s="23" t="inlineStr">
         <is>
           <t>Аренда</t>
         </is>
       </c>
-      <c r="D31" s="24" t="inlineStr">
+      <c r="D41" s="24" t="inlineStr">
         <is>
           <t>Аренда вилочного погрузчика: когда выгоднее покупки</t>
         </is>
       </c>
-      <c r="E31" s="24" t="inlineStr">
+      <c r="E41" s="24" t="inlineStr">
         <is>
           <t>/articles/arenda-vilochnogo-pogruzchika/</t>
         </is>
       </c>
-      <c r="F31" s="22" t="n">
-        <v>1770</v>
-      </c>
-      <c r="G31" s="22" t="n">
-        <v>662</v>
-      </c>
-      <c r="H31" s="23" t="inlineStr">
+      <c r="F41" s="22" t="n">
+        <v>1777</v>
+      </c>
+      <c r="G41" s="22" t="n">
+        <v>672</v>
+      </c>
+      <c r="H41" s="23" t="inlineStr">
         <is>
           <t>Не начато</t>
         </is>
       </c>
-      <c r="I31" s="24" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="25" t="n"/>
-      <c r="B32" s="25" t="n"/>
-      <c r="C32" s="25" t="n"/>
-      <c r="D32" s="26" t="inlineStr">
+      <c r="I41" s="24" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="25" t="n"/>
+      <c r="B42" s="25" t="n"/>
+      <c r="C42" s="25" t="n"/>
+      <c r="D42" s="26" t="inlineStr">
         <is>
           <t>Итого по плану</t>
         </is>
       </c>
-      <c r="E32" s="25" t="n"/>
-      <c r="F32" s="27" t="n">
-        <v>33093</v>
-      </c>
-      <c r="G32" s="25" t="n"/>
-      <c r="H32" s="25" t="n"/>
-      <c r="I32" s="25" t="n"/>
+      <c r="E42" s="25" t="n"/>
+      <c r="F42" s="27" t="n">
+        <v>33392</v>
+      </c>
+      <c r="G42" s="25" t="n"/>
+      <c r="H42" s="25" t="n"/>
+      <c r="I42" s="25" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1684,7 +2054,7 @@
     <mergeCell ref="A2:I2"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="H5 H6 H7 H8 H9 H10 H11 H12 H13 H14 H15 H16 H17 H18 H19 H20 H21 H22 H23 H24 H25 H26 H27 H28 H29 H30 H31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H5 H6 H7 H8 H9 H10 H11 H12 H13 H14 H15 H16 H17 H18 H19 H20 H21 H22 H23 H24 H25 H26 H27 H28 H29 H30 H31 H32 H33 H34 H35 H36 H37 H38 H39 H40 H41" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Не начато,Пишется,Написано,Опубликовано"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1698,11 +2068,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E328"/>
+  <dimension ref="A1:E448"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="46" customWidth="1" min="2" max="2"/>
+    <col width="48" customWidth="1" min="2" max="2"/>
     <col width="46" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
@@ -1718,7 +2088,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Топ фраз для каждой статьи — используйте в тексте, заголовках и подзаголовках. Полный список длиннее (см. колонку «Фраз в группе» на первом листе).</t>
+          <t>Топ фраз для каждой статьи. Полный список длиннее (см. «Фраз в группе» на первом листе).</t>
         </is>
       </c>
     </row>
@@ -1846,11 +2216,11 @@
       </c>
       <c r="C9" s="29" t="inlineStr">
         <is>
-          <t>щетка на вилочный погрузчик</t>
+          <t>автопогрузчик фото</t>
         </is>
       </c>
       <c r="D9" s="28" t="n">
-        <v>131</v>
+        <v>56</v>
       </c>
       <c r="E9" s="28" t="n">
         <v>5</v>
@@ -1867,11 +2237,11 @@
       </c>
       <c r="C10" s="29" t="inlineStr">
         <is>
-          <t>автопогрузчик это</t>
+          <t>самодельный вилочный погрузчик</t>
         </is>
       </c>
       <c r="D10" s="28" t="n">
-        <v>129</v>
+        <v>53</v>
       </c>
       <c r="E10" s="28" t="n">
         <v>6</v>
@@ -1888,11 +2258,11 @@
       </c>
       <c r="C11" s="29" t="inlineStr">
         <is>
-          <t>ковш на вилочный погрузчик</t>
+          <t>вилочный погрузчик код тн вэд</t>
         </is>
       </c>
       <c r="D11" s="28" t="n">
-        <v>72</v>
+        <v>43</v>
       </c>
       <c r="E11" s="28" t="n">
         <v>7</v>
@@ -1909,11 +2279,11 @@
       </c>
       <c r="C12" s="29" t="inlineStr">
         <is>
-          <t>авито вилочный погрузчик</t>
+          <t>колеса на вилочный погрузчик</t>
         </is>
       </c>
       <c r="D12" s="28" t="n">
-        <v>71</v>
+        <v>39</v>
       </c>
       <c r="E12" s="28" t="n">
         <v>8</v>
@@ -1930,11 +2300,11 @@
       </c>
       <c r="C13" s="29" t="inlineStr">
         <is>
-          <t>отвал на вилочный погрузчик</t>
+          <t>вилочный погрузчик размеры</t>
         </is>
       </c>
       <c r="D13" s="28" t="n">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="E13" s="28" t="n">
         <v>9</v>
@@ -1951,11 +2321,11 @@
       </c>
       <c r="C14" s="29" t="inlineStr">
         <is>
-          <t>автопогрузчик фото</t>
+          <t>вилочный погрузчик хендай</t>
         </is>
       </c>
       <c r="D14" s="28" t="n">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="E14" s="28" t="n">
         <v>10</v>
@@ -1972,11 +2342,11 @@
       </c>
       <c r="C15" s="29" t="inlineStr">
         <is>
-          <t>автопогрузчик это транспортное средство или оборудование</t>
+          <t>вилочный погрузчик китайский</t>
         </is>
       </c>
       <c r="D15" s="28" t="n">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="E15" s="28" t="n">
         <v>11</v>
@@ -1993,11 +2363,11 @@
       </c>
       <c r="C16" s="29" t="inlineStr">
         <is>
-          <t>самодельный вилочный погрузчик</t>
+          <t>trf вилочный погрузчик</t>
         </is>
       </c>
       <c r="D16" s="28" t="n">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="E16" s="28" t="n">
         <v>12</v>
@@ -2077,11 +2447,11 @@
       </c>
       <c r="C20" s="29" t="inlineStr">
         <is>
-          <t>сколько весит погрузчик вилочный львовский</t>
+          <t>рейтинг вилочных погрузчиков по надежности и качеству</t>
         </is>
       </c>
       <c r="D20" s="28" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E20" s="28" t="n">
         <v>4</v>
@@ -2098,11 +2468,11 @@
       </c>
       <c r="C21" s="29" t="inlineStr">
         <is>
-          <t>сколько весит вилочный погрузчик грузоподъемностью 3 тонны</t>
+          <t>остаточная грузоподъемность вилочного погрузчика</t>
         </is>
       </c>
       <c r="D21" s="28" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E21" s="28" t="n">
         <v>5</v>
@@ -2119,11 +2489,11 @@
       </c>
       <c r="C22" s="29" t="inlineStr">
         <is>
-          <t>рейтинг вилочных погрузчиков по надежности и качеству</t>
+          <t>сколько весит погрузчик вилочный 3т</t>
         </is>
       </c>
       <c r="D22" s="28" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E22" s="28" t="n">
         <v>6</v>
@@ -2140,11 +2510,11 @@
       </c>
       <c r="C23" s="29" t="inlineStr">
         <is>
-          <t>остаточная грузоподъемность вилочного погрузчика</t>
+          <t>погрузчик вилочный как выбрать</t>
         </is>
       </c>
       <c r="D23" s="28" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E23" s="28" t="n">
         <v>7</v>
@@ -2161,11 +2531,11 @@
       </c>
       <c r="C24" s="29" t="inlineStr">
         <is>
-          <t>сколько весит погрузчик вилочный 3т</t>
+          <t>рейтинг вилочных погрузчиков</t>
         </is>
       </c>
       <c r="D24" s="28" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E24" s="28" t="n">
         <v>8</v>
@@ -2182,11 +2552,11 @@
       </c>
       <c r="C25" s="29" t="inlineStr">
         <is>
-          <t>сколько весит вилочный погрузчик тойота</t>
+          <t>сколько весит автопогрузчик</t>
         </is>
       </c>
       <c r="D25" s="28" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E25" s="28" t="n">
         <v>9</v>
@@ -2203,11 +2573,11 @@
       </c>
       <c r="C26" s="29" t="inlineStr">
         <is>
-          <t>сколько весит вилочный погрузчик львовский погрузчик</t>
+          <t>максимальная грузоподъемность вилочного погрузчика</t>
         </is>
       </c>
       <c r="D26" s="28" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E26" s="28" t="n">
         <v>10</v>
@@ -2224,11 +2594,11 @@
       </c>
       <c r="C27" s="29" t="inlineStr">
         <is>
-          <t>погрузчик вилочный как выбрать</t>
+          <t>грузоподъемность вилочного погрузчика в зависимости от высоты</t>
         </is>
       </c>
       <c r="D27" s="28" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E27" s="28" t="n">
         <v>11</v>
@@ -2245,11 +2615,11 @@
       </c>
       <c r="C28" s="29" t="inlineStr">
         <is>
-          <t>рейтинг вилочных погрузчиков</t>
+          <t>грузоподъемность вилочного погрузчика в зависимости от высоты подъема</t>
         </is>
       </c>
       <c r="D28" s="28" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E28" s="28" t="n">
         <v>12</v>
@@ -2455,11 +2825,11 @@
       </c>
       <c r="C38" s="29" t="inlineStr">
         <is>
-          <t>погрузчик вилочный дизельный 5 тонн</t>
+          <t>погрузчики вилочные электрические</t>
         </is>
       </c>
       <c r="D38" s="28" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E38" s="28" t="n">
         <v>10</v>
@@ -2476,11 +2846,11 @@
       </c>
       <c r="C39" s="29" t="inlineStr">
         <is>
-          <t>погрузчики вилочные электрические</t>
+          <t>газовый вилочный погрузчик</t>
         </is>
       </c>
       <c r="D39" s="28" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="E39" s="28" t="n">
         <v>11</v>
@@ -2497,11 +2867,11 @@
       </c>
       <c r="C40" s="29" t="inlineStr">
         <is>
-          <t>газовый вилочный погрузчик</t>
+          <t>погрузчик вилочный электрический 2000 кг</t>
         </is>
       </c>
       <c r="D40" s="28" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E40" s="28" t="n">
         <v>12</v>
@@ -2686,11 +3056,11 @@
       </c>
       <c r="C49" s="29" t="inlineStr">
         <is>
-          <t>вилочный погрузчик маниту внедорожный</t>
+          <t>внедорожный автопогрузчик</t>
         </is>
       </c>
       <c r="D49" s="28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E49" s="28" t="n">
         <v>9</v>
@@ -2707,11 +3077,11 @@
       </c>
       <c r="C50" s="29" t="inlineStr">
         <is>
-          <t>полноприводный вилочный погрузчик 5 тонн</t>
+          <t>погрузчик дизельный вилочный полноприводный</t>
         </is>
       </c>
       <c r="D50" s="28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E50" s="28" t="n">
         <v>10</v>
@@ -2728,7 +3098,7 @@
       </c>
       <c r="C51" s="29" t="inlineStr">
         <is>
-          <t>внедорожный автопогрузчик</t>
+          <t>внедорожный вилочный погрузчик б у</t>
         </is>
       </c>
       <c r="D51" s="28" t="n">
@@ -2749,11 +3119,11 @@
       </c>
       <c r="C52" s="29" t="inlineStr">
         <is>
-          <t>погрузчик дизельный вилочный полноприводный</t>
+          <t>автопогрузчик полноприводный</t>
         </is>
       </c>
       <c r="D52" s="28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E52" s="28" t="n">
         <v>12</v>
@@ -3017,16 +3387,16 @@
       </c>
       <c r="B65" s="29" t="inlineStr">
         <is>
-          <t>Вилочный погрузчик и автопогрузчик — в чём разница с рохлей и штабелёром</t>
+          <t>Мачта, высота подъёма и габариты вилочного погрузчика</t>
         </is>
       </c>
       <c r="C65" s="29" t="inlineStr">
         <is>
-          <t>ручной вилочный погрузчик</t>
+          <t>мачта вилочного погрузчика</t>
         </is>
       </c>
       <c r="D65" s="28" t="n">
-        <v>149</v>
+        <v>36</v>
       </c>
       <c r="E65" s="28" t="n">
         <v>1</v>
@@ -3038,16 +3408,16 @@
       </c>
       <c r="B66" s="29" t="inlineStr">
         <is>
-          <t>Вилочный погрузчик и автопогрузчик — в чём разница с рохлей и штабелёром</t>
+          <t>Мачта, высота подъёма и габариты вилочного погрузчика</t>
         </is>
       </c>
       <c r="C66" s="29" t="inlineStr">
         <is>
-          <t>погрузчик вилочный ручной гидравлический</t>
+          <t>высота погрузчика вилочного</t>
         </is>
       </c>
       <c r="D66" s="28" t="n">
-        <v>69</v>
+        <v>25</v>
       </c>
       <c r="E66" s="28" t="n">
         <v>2</v>
@@ -3059,16 +3429,16 @@
       </c>
       <c r="B67" s="29" t="inlineStr">
         <is>
-          <t>Вилочный погрузчик и автопогрузчик — в чём разница с рохлей и штабелёром</t>
+          <t>Мачта, высота подъёма и габариты вилочного погрузчика</t>
         </is>
       </c>
       <c r="C67" s="29" t="inlineStr">
         <is>
-          <t>погрузчик вилочный ручной гидравлический с поднимающимися вилами</t>
+          <t>класс каретки вилочного погрузчика</t>
         </is>
       </c>
       <c r="D67" s="28" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="E67" s="28" t="n">
         <v>3</v>
@@ -3080,16 +3450,16 @@
       </c>
       <c r="B68" s="29" t="inlineStr">
         <is>
-          <t>Вилочный погрузчик и автопогрузчик — в чём разница с рохлей и штабелёром</t>
+          <t>Мачта, высота подъёма и габариты вилочного погрузчика</t>
         </is>
       </c>
       <c r="C68" s="29" t="inlineStr">
         <is>
-          <t>ручной вилочный погрузчик для складов</t>
+          <t>мачта на вилочный погрузчик</t>
         </is>
       </c>
       <c r="D68" s="28" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="E68" s="28" t="n">
         <v>4</v>
@@ -3101,16 +3471,16 @@
       </c>
       <c r="B69" s="29" t="inlineStr">
         <is>
-          <t>Вилочный погрузчик и автопогрузчик — в чём разница с рохлей и штабелёром</t>
+          <t>Мачта, высота подъёма и габариты вилочного погрузчика</t>
         </is>
       </c>
       <c r="C69" s="29" t="inlineStr">
         <is>
-          <t>ручной вилочный погрузчик для складов 1т</t>
+          <t>высота подъема вилочного погрузчика</t>
         </is>
       </c>
       <c r="D69" s="28" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="E69" s="28" t="n">
         <v>5</v>
@@ -3122,16 +3492,16 @@
       </c>
       <c r="B70" s="29" t="inlineStr">
         <is>
-          <t>Вилочный погрузчик и автопогрузчик — в чём разница с рохлей и штабелёром</t>
+          <t>Мачта, высота подъёма и габариты вилочного погрузчика</t>
         </is>
       </c>
       <c r="C70" s="29" t="inlineStr">
         <is>
-          <t>погрузчик вилочный ручной гидравлический купить</t>
+          <t>вилочного погрузчика габариты</t>
         </is>
       </c>
       <c r="D70" s="28" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="E70" s="28" t="n">
         <v>6</v>
@@ -3143,16 +3513,16 @@
       </c>
       <c r="B71" s="29" t="inlineStr">
         <is>
-          <t>Вилочный погрузчик и автопогрузчик — в чём разница с рохлей и штабелёром</t>
+          <t>Мачта, высота подъёма и габариты вилочного погрузчика</t>
         </is>
       </c>
       <c r="C71" s="29" t="inlineStr">
         <is>
-          <t>вилочный погрузчик это электропогрузчик</t>
+          <t>мачта для вилочного погрузчика</t>
         </is>
       </c>
       <c r="D71" s="28" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E71" s="28" t="n">
         <v>7</v>
@@ -3164,16 +3534,16 @@
       </c>
       <c r="B72" s="29" t="inlineStr">
         <is>
-          <t>Вилочный погрузчик и автопогрузчик — в чём разница с рохлей и штабелёром</t>
+          <t>Мачта, высота подъёма и габариты вилочного погрузчика</t>
         </is>
       </c>
       <c r="C72" s="29" t="inlineStr">
         <is>
-          <t>вилочный погрузчик это кара</t>
+          <t>класс каретки вилочного погрузчика таблица</t>
         </is>
       </c>
       <c r="D72" s="28" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E72" s="28" t="n">
         <v>8</v>
@@ -3185,16 +3555,16 @@
       </c>
       <c r="B73" s="29" t="inlineStr">
         <is>
-          <t>Вилочный погрузчик и автопогрузчик — в чём разница с рохлей и штабелёром</t>
+          <t>Мачта, высота подъёма и габариты вилочного погрузчика</t>
         </is>
       </c>
       <c r="C73" s="29" t="inlineStr">
         <is>
-          <t>гидравлический ручной вилочный погрузчик 1000 кг</t>
+          <t>мачта для погрузчика вилочного погрузчика</t>
         </is>
       </c>
       <c r="D73" s="28" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E73" s="28" t="n">
         <v>9</v>
@@ -3206,16 +3576,16 @@
       </c>
       <c r="B74" s="29" t="inlineStr">
         <is>
-          <t>Вилочный погрузчик и автопогрузчик — в чём разница с рохлей и штабелёром</t>
+          <t>Мачта, высота подъёма и габариты вилочного погрузчика</t>
         </is>
       </c>
       <c r="C74" s="29" t="inlineStr">
         <is>
-          <t>водитель автопогрузчика это как</t>
+          <t>мачта вилочного погрузчика бу купить</t>
         </is>
       </c>
       <c r="D74" s="28" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E74" s="28" t="n">
         <v>10</v>
@@ -3227,16 +3597,16 @@
       </c>
       <c r="B75" s="29" t="inlineStr">
         <is>
-          <t>Вилочный погрузчик и автопогрузчик — в чём разница с рохлей и штабелёром</t>
+          <t>Мачта, высота подъёма и габариты вилочного погрузчика</t>
         </is>
       </c>
       <c r="C75" s="29" t="inlineStr">
         <is>
-          <t>водитель автопогрузчика это кто</t>
+          <t>малогабаритный вилочный погрузчик</t>
         </is>
       </c>
       <c r="D75" s="28" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E75" s="28" t="n">
         <v>11</v>
@@ -3248,16 +3618,16 @@
       </c>
       <c r="B76" s="29" t="inlineStr">
         <is>
-          <t>Вилочный погрузчик и автопогрузчик — в чём разница с рохлей и штабелёром</t>
+          <t>Мачта, высота подъёма и габариты вилочного погрузчика</t>
         </is>
       </c>
       <c r="C76" s="29" t="inlineStr">
         <is>
-          <t>складской погрузчик ручной вилочный</t>
+          <t>габаритные размеры вилочного погрузчика</t>
         </is>
       </c>
       <c r="D76" s="28" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E76" s="28" t="n">
         <v>12</v>
@@ -3269,16 +3639,16 @@
       </c>
       <c r="B77" s="29" t="inlineStr">
         <is>
-          <t>Вилочный погрузчик до 2 тонн: компактные модели для небольшого склада</t>
+          <t>Вилочный погрузчик и автопогрузчик — в чём разница с рохлей и штабелёром</t>
         </is>
       </c>
       <c r="C77" s="29" t="inlineStr">
         <is>
-          <t>погрузчик вилочный 2 тонны</t>
+          <t>ручной вилочный погрузчик</t>
         </is>
       </c>
       <c r="D77" s="28" t="n">
-        <v>29</v>
+        <v>149</v>
       </c>
       <c r="E77" s="28" t="n">
         <v>1</v>
@@ -3290,16 +3660,16 @@
       </c>
       <c r="B78" s="29" t="inlineStr">
         <is>
-          <t>Вилочный погрузчик до 2 тонн: компактные модели для небольшого склада</t>
+          <t>Вилочный погрузчик и автопогрузчик — в чём разница с рохлей и штабелёром</t>
         </is>
       </c>
       <c r="C78" s="29" t="inlineStr">
         <is>
-          <t>вилочный погрузчик 1 тонна</t>
+          <t>автопогрузчик это</t>
         </is>
       </c>
       <c r="D78" s="28" t="n">
-        <v>10</v>
+        <v>129</v>
       </c>
       <c r="E78" s="28" t="n">
         <v>2</v>
@@ -3311,16 +3681,16 @@
       </c>
       <c r="B79" s="29" t="inlineStr">
         <is>
-          <t>Вилочный погрузчик до 2 тонн: компактные модели для небольшого склада</t>
+          <t>Вилочный погрузчик и автопогрузчик — в чём разница с рохлей и штабелёром</t>
         </is>
       </c>
       <c r="C79" s="29" t="inlineStr">
         <is>
-          <t>вилочный погрузчик грузоподъемностью 2 тонны</t>
+          <t>погрузчик вилочный ручной гидравлический</t>
         </is>
       </c>
       <c r="D79" s="28" t="n">
-        <v>4</v>
+        <v>69</v>
       </c>
       <c r="E79" s="28" t="n">
         <v>3</v>
@@ -3332,16 +3702,16 @@
       </c>
       <c r="B80" s="29" t="inlineStr">
         <is>
-          <t>Вилочный погрузчик до 2 тонн: компактные модели для небольшого склада</t>
+          <t>Вилочный погрузчик и автопогрузчик — в чём разница с рохлей и штабелёром</t>
         </is>
       </c>
       <c r="C80" s="29" t="inlineStr">
         <is>
-          <t>погрузчик вилочный 2 тонны бу</t>
+          <t>автопогрузчик это транспортное средство или оборудование</t>
         </is>
       </c>
       <c r="D80" s="28" t="n">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="E80" s="28" t="n">
         <v>4</v>
@@ -3353,16 +3723,16 @@
       </c>
       <c r="B81" s="29" t="inlineStr">
         <is>
-          <t>Вилочный погрузчик до 2 тонн: компактные модели для небольшого склада</t>
+          <t>Вилочный погрузчик и автопогрузчик — в чём разница с рохлей и штабелёром</t>
         </is>
       </c>
       <c r="C81" s="29" t="inlineStr">
         <is>
-          <t>погрузчик вилочный до 2 тонн</t>
+          <t>автопогрузчик это транспортное средство</t>
         </is>
       </c>
       <c r="D81" s="28" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="E81" s="28" t="n">
         <v>5</v>
@@ -3374,16 +3744,16 @@
       </c>
       <c r="B82" s="29" t="inlineStr">
         <is>
-          <t>Вилочный погрузчик до 2 тонн: компактные модели для небольшого склада</t>
+          <t>Вилочный погрузчик и автопогрузчик — в чём разница с рохлей и штабелёром</t>
         </is>
       </c>
       <c r="C82" s="29" t="inlineStr">
         <is>
-          <t>вилочный погрузчик тойота 2 тонны</t>
+          <t>автопогрузчик что это</t>
         </is>
       </c>
       <c r="D82" s="28" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="E82" s="28" t="n">
         <v>6</v>
@@ -3395,16 +3765,16 @@
       </c>
       <c r="B83" s="29" t="inlineStr">
         <is>
-          <t>Вилочный погрузчик до 2 тонн: компактные модели для небольшого склада</t>
+          <t>Вилочный погрузчик и автопогрузчик — в чём разница с рохлей и штабелёром</t>
         </is>
       </c>
       <c r="C83" s="29" t="inlineStr">
         <is>
-          <t>размеры вилочного погрузчика 2 тонны</t>
+          <t>вилочный погрузчик что это</t>
         </is>
       </c>
       <c r="D83" s="28" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E83" s="28" t="n">
         <v>7</v>
@@ -3416,16 +3786,16 @@
       </c>
       <c r="B84" s="29" t="inlineStr">
         <is>
-          <t>Вилочный погрузчик до 2 тонн: компактные модели для небольшого склада</t>
+          <t>Вилочный погрузчик и автопогрузчик — в чём разница с рохлей и штабелёром</t>
         </is>
       </c>
       <c r="C84" s="29" t="inlineStr">
         <is>
-          <t>погрузчик вилочный до 1 тонны</t>
+          <t>погрузчик вилочный ручной гидравлический с поднимающимися вилами</t>
         </is>
       </c>
       <c r="D84" s="28" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E84" s="28" t="n">
         <v>8</v>
@@ -3437,16 +3807,16 @@
       </c>
       <c r="B85" s="29" t="inlineStr">
         <is>
-          <t>Вилочный погрузчик до 2 тонн: компактные модели для небольшого склада</t>
+          <t>Вилочный погрузчик и автопогрузчик — в чём разница с рохлей и штабелёром</t>
         </is>
       </c>
       <c r="C85" s="29" t="inlineStr">
         <is>
-          <t>jac погрузчик вилочный 2 тонны</t>
+          <t>вилочный погрузчик это транспортное средство или машины и оборудование</t>
         </is>
       </c>
       <c r="D85" s="28" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E85" s="28" t="n">
         <v>9</v>
@@ -3458,16 +3828,16 @@
       </c>
       <c r="B86" s="29" t="inlineStr">
         <is>
-          <t>Вилочный погрузчик до 2 тонн: компактные модели для небольшого склада</t>
+          <t>Вилочный погрузчик и автопогрузчик — в чём разница с рохлей и штабелёром</t>
         </is>
       </c>
       <c r="C86" s="29" t="inlineStr">
         <is>
-          <t>вилочный погрузчик на 2 тонны</t>
+          <t>ручной вилочный погрузчик для складов</t>
         </is>
       </c>
       <c r="D86" s="28" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E86" s="28" t="n">
         <v>10</v>
@@ -3479,16 +3849,16 @@
       </c>
       <c r="B87" s="29" t="inlineStr">
         <is>
-          <t>Вилочный погрузчик до 2 тонн: компактные модели для небольшого склада</t>
+          <t>Вилочный погрузчик и автопогрузчик — в чём разница с рохлей и штабелёром</t>
         </is>
       </c>
       <c r="C87" s="29" t="inlineStr">
         <is>
-          <t>погрузчик вилочный 2 тонны аренда</t>
+          <t>вилочный погрузчик это транспортное средство</t>
         </is>
       </c>
       <c r="D87" s="28" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E87" s="28" t="n">
         <v>11</v>
@@ -3500,16 +3870,16 @@
       </c>
       <c r="B88" s="29" t="inlineStr">
         <is>
-          <t>Вилочный погрузчик до 2 тонн: компактные модели для небольшого склада</t>
+          <t>Вилочный погрузчик и автопогрузчик — в чём разница с рохлей и штабелёром</t>
         </is>
       </c>
       <c r="C88" s="29" t="inlineStr">
         <is>
-          <t>вилочный погрузчик heli 2 тонны</t>
+          <t>автопогрузчик это самоходная машина или нет</t>
         </is>
       </c>
       <c r="D88" s="28" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E88" s="28" t="n">
         <v>12</v>
@@ -3521,16 +3891,16 @@
       </c>
       <c r="B89" s="29" t="inlineStr">
         <is>
-          <t>Вилочный погрузчик 3 тонны: какие задачи закрывает</t>
+          <t>Вилочный погрузчик до 2 тонн: компактные модели для небольшого склада</t>
         </is>
       </c>
       <c r="C89" s="29" t="inlineStr">
         <is>
-          <t>вилочный погрузчик 3 тонны</t>
+          <t>погрузчик вилочный 2 тонны</t>
         </is>
       </c>
       <c r="D89" s="28" t="n">
-        <v>172</v>
+        <v>29</v>
       </c>
       <c r="E89" s="28" t="n">
         <v>1</v>
@@ -3542,16 +3912,16 @@
       </c>
       <c r="B90" s="29" t="inlineStr">
         <is>
-          <t>Вилочный погрузчик 3 тонны: какие задачи закрывает</t>
+          <t>Вилочный погрузчик до 2 тонн: компактные модели для небольшого склада</t>
         </is>
       </c>
       <c r="C90" s="29" t="inlineStr">
         <is>
-          <t>давление в шинах погрузчика 3 тонны вилочного</t>
+          <t>погрузчик вилочный дизельный 2 тонны</t>
         </is>
       </c>
       <c r="D90" s="28" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E90" s="28" t="n">
         <v>2</v>
@@ -3563,16 +3933,16 @@
       </c>
       <c r="B91" s="29" t="inlineStr">
         <is>
-          <t>Вилочный погрузчик 3 тонны: какие задачи закрывает</t>
+          <t>Вилочный погрузчик до 2 тонн: компактные модели для небольшого склада</t>
         </is>
       </c>
       <c r="C91" s="29" t="inlineStr">
         <is>
-          <t>погрузчик тойота вилочный 3 тонны</t>
+          <t>дизельный вилочный погрузчик на 1 тонну</t>
         </is>
       </c>
       <c r="D91" s="28" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="E91" s="28" t="n">
         <v>3</v>
@@ -3584,16 +3954,16 @@
       </c>
       <c r="B92" s="29" t="inlineStr">
         <is>
-          <t>Вилочный погрузчик 3 тонны: какие задачи закрывает</t>
+          <t>Вилочный погрузчик до 2 тонн: компактные модели для небольшого склада</t>
         </is>
       </c>
       <c r="C92" s="29" t="inlineStr">
         <is>
-          <t>аренда вилочного погрузчика 3 тонны</t>
+          <t>вилочный погрузчик 1 тонна</t>
         </is>
       </c>
       <c r="D92" s="28" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E92" s="28" t="n">
         <v>4</v>
@@ -3605,16 +3975,16 @@
       </c>
       <c r="B93" s="29" t="inlineStr">
         <is>
-          <t>Вилочный погрузчик 3 тонны: какие задачи закрывает</t>
+          <t>Вилочный погрузчик до 2 тонн: компактные модели для небольшого склада</t>
         </is>
       </c>
       <c r="C93" s="29" t="inlineStr">
         <is>
-          <t>вилочный погрузчик комацу 3 тонны</t>
+          <t>электрический вилочный погрузчик 2 тонны</t>
         </is>
       </c>
       <c r="D93" s="28" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E93" s="28" t="n">
         <v>5</v>
@@ -3626,16 +3996,16 @@
       </c>
       <c r="B94" s="29" t="inlineStr">
         <is>
-          <t>Вилочный погрузчик 3 тонны: какие задачи закрывает</t>
+          <t>Вилочный погрузчик до 2 тонн: компактные модели для небольшого склада</t>
         </is>
       </c>
       <c r="C94" s="29" t="inlineStr">
         <is>
-          <t>лонкинг 3 тонны вилочный погрузчик</t>
+          <t>вилочный погрузчик грузоподъемностью 2 тонны</t>
         </is>
       </c>
       <c r="D94" s="28" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="E94" s="28" t="n">
         <v>6</v>
@@ -3647,16 +4017,16 @@
       </c>
       <c r="B95" s="29" t="inlineStr">
         <is>
-          <t>Вилочный погрузчик 3 тонны: какие задачи закрывает</t>
+          <t>Вилочный погрузчик до 2 тонн: компактные модели для небольшого склада</t>
         </is>
       </c>
       <c r="C95" s="29" t="inlineStr">
         <is>
-          <t>погрузчик вилочный jac 3 тонны</t>
+          <t>погрузчик вилочный 2 тонны бу</t>
         </is>
       </c>
       <c r="D95" s="28" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E95" s="28" t="n">
         <v>7</v>
@@ -3668,16 +4038,16 @@
       </c>
       <c r="B96" s="29" t="inlineStr">
         <is>
-          <t>Вилочный погрузчик 3 тонны: какие задачи закрывает</t>
+          <t>Вилочный погрузчик до 2 тонн: компактные модели для небольшого склада</t>
         </is>
       </c>
       <c r="C96" s="29" t="inlineStr">
         <is>
-          <t>размеры вилочного погрузчика 3 тонны</t>
+          <t>погрузчик вилочный до 2 тонн</t>
         </is>
       </c>
       <c r="D96" s="28" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E96" s="28" t="n">
         <v>8</v>
@@ -3689,16 +4059,16 @@
       </c>
       <c r="B97" s="29" t="inlineStr">
         <is>
-          <t>Вилочный погрузчик 3 тонны: какие задачи закрывает</t>
+          <t>Вилочный погрузчик до 2 тонн: компактные модели для небольшого склада</t>
         </is>
       </c>
       <c r="C97" s="29" t="inlineStr">
         <is>
-          <t>высота вилочного погрузчика 3 тонны</t>
+          <t>размеры вилочного погрузчика 2 тонны</t>
         </is>
       </c>
       <c r="D97" s="28" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E97" s="28" t="n">
         <v>9</v>
@@ -3710,16 +4080,16 @@
       </c>
       <c r="B98" s="29" t="inlineStr">
         <is>
-          <t>Вилочный погрузчик 3 тонны: какие задачи закрывает</t>
+          <t>Вилочный погрузчик до 2 тонн: компактные модели для небольшого склада</t>
         </is>
       </c>
       <c r="C98" s="29" t="inlineStr">
         <is>
-          <t>габариты вилочного погрузчика 3 тонны</t>
+          <t>погрузчик вилочный до 1 тонны</t>
         </is>
       </c>
       <c r="D98" s="28" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="E98" s="28" t="n">
         <v>10</v>
@@ -3731,16 +4101,16 @@
       </c>
       <c r="B99" s="29" t="inlineStr">
         <is>
-          <t>Вилочный погрузчик 3 тонны: какие задачи закрывает</t>
+          <t>Вилочный погрузчик до 2 тонн: компактные модели для небольшого склада</t>
         </is>
       </c>
       <c r="C99" s="29" t="inlineStr">
         <is>
-          <t>погрузчик вилочный 3 тонны heli</t>
+          <t>вилочный электропогрузчик 2 тонны</t>
         </is>
       </c>
       <c r="D99" s="28" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E99" s="28" t="n">
         <v>11</v>
@@ -3752,16 +4122,16 @@
       </c>
       <c r="B100" s="29" t="inlineStr">
         <is>
-          <t>Вилочный погрузчик 3 тонны: какие задачи закрывает</t>
+          <t>Вилочный погрузчик до 2 тонн: компактные модели для небольшого склада</t>
         </is>
       </c>
       <c r="C100" s="29" t="inlineStr">
         <is>
-          <t>вилочный погрузчик хели 3 тонны</t>
+          <t>вилочный погрузчик на 2 тонны</t>
         </is>
       </c>
       <c r="D100" s="28" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E100" s="28" t="n">
         <v>12</v>
@@ -3773,16 +4143,16 @@
       </c>
       <c r="B101" s="29" t="inlineStr">
         <is>
-          <t>Вилочный погрузчик 5 тонн: характеристики и подбор</t>
+          <t>Вилочный погрузчик 3 тонны: какие задачи закрывает</t>
         </is>
       </c>
       <c r="C101" s="29" t="inlineStr">
         <is>
-          <t>вилочный погрузчик 5 тонн</t>
+          <t>вилочный погрузчик 3 тонны</t>
         </is>
       </c>
       <c r="D101" s="28" t="n">
-        <v>138</v>
+        <v>172</v>
       </c>
       <c r="E101" s="28" t="n">
         <v>1</v>
@@ -3794,16 +4164,16 @@
       </c>
       <c r="B102" s="29" t="inlineStr">
         <is>
-          <t>Вилочный погрузчик 5 тонн: характеристики и подбор</t>
+          <t>Вилочный погрузчик 3 тонны: какие задачи закрывает</t>
         </is>
       </c>
       <c r="C102" s="29" t="inlineStr">
         <is>
-          <t>львовский автопогрузчик 5 тонн</t>
+          <t>давление в шинах погрузчика 3 тонны вилочного</t>
         </is>
       </c>
       <c r="D102" s="28" t="n">
-        <v>48</v>
+        <v>23</v>
       </c>
       <c r="E102" s="28" t="n">
         <v>2</v>
@@ -3815,16 +4185,16 @@
       </c>
       <c r="B103" s="29" t="inlineStr">
         <is>
-          <t>Вилочный погрузчик 5 тонн: характеристики и подбор</t>
+          <t>Вилочный погрузчик 3 тонны: какие задачи закрывает</t>
         </is>
       </c>
       <c r="C103" s="29" t="inlineStr">
         <is>
-          <t>аренда вилочного погрузчика 5 тонн</t>
+          <t>аренда вилочного погрузчика 3 тонны</t>
         </is>
       </c>
       <c r="D103" s="28" t="n">
-        <v>46</v>
+        <v>18</v>
       </c>
       <c r="E103" s="28" t="n">
         <v>3</v>
@@ -3836,16 +4206,16 @@
       </c>
       <c r="B104" s="29" t="inlineStr">
         <is>
-          <t>Вилочный погрузчик 5 тонн: характеристики и подбор</t>
+          <t>Вилочный погрузчик 3 тонны: какие задачи закрывает</t>
         </is>
       </c>
       <c r="C104" s="29" t="inlineStr">
         <is>
-          <t>вилочный погрузчик 5 тонн бу</t>
+          <t>вилочный погрузчик 3 тонны дизельный</t>
         </is>
       </c>
       <c r="D104" s="28" t="n">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="E104" s="28" t="n">
         <v>4</v>
@@ -3857,16 +4227,16 @@
       </c>
       <c r="B105" s="29" t="inlineStr">
         <is>
-          <t>Вилочный погрузчик 5 тонн: характеристики и подбор</t>
+          <t>Вилочный погрузчик 3 тонны: какие задачи закрывает</t>
         </is>
       </c>
       <c r="C105" s="29" t="inlineStr">
         <is>
-          <t>автопогрузчик вилочный 5 тонн</t>
+          <t>погрузчик электрический вилочный 3 тонны</t>
         </is>
       </c>
       <c r="D105" s="28" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E105" s="28" t="n">
         <v>5</v>
@@ -3878,16 +4248,16 @@
       </c>
       <c r="B106" s="29" t="inlineStr">
         <is>
-          <t>Вилочный погрузчик 5 тонн: характеристики и подбор</t>
+          <t>Вилочный погрузчик 3 тонны: какие задачи закрывает</t>
         </is>
       </c>
       <c r="C106" s="29" t="inlineStr">
         <is>
-          <t>автопогрузчик 5 тонн</t>
+          <t>сколько весит вилочный погрузчик грузоподъемностью 3 тонны</t>
         </is>
       </c>
       <c r="D106" s="28" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E106" s="28" t="n">
         <v>6</v>
@@ -3899,12 +4269,12 @@
       </c>
       <c r="B107" s="29" t="inlineStr">
         <is>
-          <t>Вилочный погрузчик 5 тонн: характеристики и подбор</t>
+          <t>Вилочный погрузчик 3 тонны: какие задачи закрывает</t>
         </is>
       </c>
       <c r="C107" s="29" t="inlineStr">
         <is>
-          <t>погрузчик вилочный 5 тонн jac</t>
+          <t>размеры вилочного погрузчика 3 тонны</t>
         </is>
       </c>
       <c r="D107" s="28" t="n">
@@ -3920,12 +4290,12 @@
       </c>
       <c r="B108" s="29" t="inlineStr">
         <is>
-          <t>Вилочный погрузчик 5 тонн: характеристики и подбор</t>
+          <t>Вилочный погрузчик 3 тонны: какие задачи закрывает</t>
         </is>
       </c>
       <c r="C108" s="29" t="inlineStr">
         <is>
-          <t>вилочный погрузчик тойота 5 тонн</t>
+          <t>высота вилочного погрузчика 3 тонны</t>
         </is>
       </c>
       <c r="D108" s="28" t="n">
@@ -3941,12 +4311,12 @@
       </c>
       <c r="B109" s="29" t="inlineStr">
         <is>
-          <t>Вилочный погрузчик 5 тонн: характеристики и подбор</t>
+          <t>Вилочный погрузчик 3 тонны: какие задачи закрывает</t>
         </is>
       </c>
       <c r="C109" s="29" t="inlineStr">
         <is>
-          <t>львовский погрузчик вилочный 5 тонн</t>
+          <t>габариты вилочного погрузчика 3 тонны</t>
         </is>
       </c>
       <c r="D109" s="28" t="n">
@@ -3962,12 +4332,12 @@
       </c>
       <c r="B110" s="29" t="inlineStr">
         <is>
-          <t>Вилочный погрузчик 5 тонн: характеристики и подбор</t>
+          <t>Вилочный погрузчик 3 тонны: какие задачи закрывает</t>
         </is>
       </c>
       <c r="C110" s="29" t="inlineStr">
         <is>
-          <t>вилочный погрузчик 1 5 тонны</t>
+          <t>тсм погрузчик вилочный дизельный 3 тонны</t>
         </is>
       </c>
       <c r="D110" s="28" t="n">
@@ -3983,16 +4353,16 @@
       </c>
       <c r="B111" s="29" t="inlineStr">
         <is>
-          <t>Вилочный погрузчик 5 тонн: характеристики и подбор</t>
+          <t>Вилочный погрузчик 3 тонны: какие задачи закрывает</t>
         </is>
       </c>
       <c r="C111" s="29" t="inlineStr">
         <is>
-          <t>вилочный погрузчик грузоподъемность 5 тонн</t>
+          <t>китайский вилочный погрузчик 3 тонны</t>
         </is>
       </c>
       <c r="D111" s="28" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E111" s="28" t="n">
         <v>11</v>
@@ -4004,16 +4374,16 @@
       </c>
       <c r="B112" s="29" t="inlineStr">
         <is>
-          <t>Вилочный погрузчик 5 тонн: характеристики и подбор</t>
+          <t>Вилочный погрузчик 3 тонны: какие задачи закрывает</t>
         </is>
       </c>
       <c r="C112" s="29" t="inlineStr">
         <is>
-          <t>погрузчик вилочный 5 тонн фото</t>
+          <t>китайский вилочный погрузчик 3 тонны дизельный</t>
         </is>
       </c>
       <c r="D112" s="28" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E112" s="28" t="n">
         <v>12</v>
@@ -4025,16 +4395,16 @@
       </c>
       <c r="B113" s="29" t="inlineStr">
         <is>
-          <t>Вилочный погрузчик от 7 тонн: тяжёлый класс для металла и контейнеров</t>
+          <t>Вилочный погрузчик 5 тонн: характеристики и подбор</t>
         </is>
       </c>
       <c r="C113" s="29" t="inlineStr">
         <is>
-          <t>аренда вилочного погрузчика 10 тонн</t>
+          <t>вилочный погрузчик 5 тонн</t>
         </is>
       </c>
       <c r="D113" s="28" t="n">
-        <v>114</v>
+        <v>138</v>
       </c>
       <c r="E113" s="28" t="n">
         <v>1</v>
@@ -4046,16 +4416,16 @@
       </c>
       <c r="B114" s="29" t="inlineStr">
         <is>
-          <t>Вилочный погрузчик от 7 тонн: тяжёлый класс для металла и контейнеров</t>
+          <t>Вилочный погрузчик 5 тонн: характеристики и подбор</t>
         </is>
       </c>
       <c r="C114" s="29" t="inlineStr">
         <is>
-          <t>вилочный погрузчик 10 тонн</t>
+          <t>аренда вилочного погрузчика 5 тонн</t>
         </is>
       </c>
       <c r="D114" s="28" t="n">
-        <v>95</v>
+        <v>46</v>
       </c>
       <c r="E114" s="28" t="n">
         <v>2</v>
@@ -4067,16 +4437,16 @@
       </c>
       <c r="B115" s="29" t="inlineStr">
         <is>
-          <t>Вилочный погрузчик от 7 тонн: тяжёлый класс для металла и контейнеров</t>
+          <t>Вилочный погрузчик 5 тонн: характеристики и подбор</t>
         </is>
       </c>
       <c r="C115" s="29" t="inlineStr">
         <is>
-          <t>вилочный погрузчик 7 тонн</t>
+          <t>вилочный погрузчик 5 тонн бу</t>
         </is>
       </c>
       <c r="D115" s="28" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="E115" s="28" t="n">
         <v>3</v>
@@ -4088,16 +4458,16 @@
       </c>
       <c r="B116" s="29" t="inlineStr">
         <is>
-          <t>Вилочный погрузчик от 7 тонн: тяжёлый класс для металла и контейнеров</t>
+          <t>Вилочный погрузчик 5 тонн: характеристики и подбор</t>
         </is>
       </c>
       <c r="C116" s="29" t="inlineStr">
         <is>
-          <t>аренда погрузчик вилочный 10 тонн аренда</t>
+          <t>погрузчик вилочный дизельный 5 тонн</t>
         </is>
       </c>
       <c r="D116" s="28" t="n">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="E116" s="28" t="n">
         <v>4</v>
@@ -4109,16 +4479,16 @@
       </c>
       <c r="B117" s="29" t="inlineStr">
         <is>
-          <t>Вилочный погрузчик от 7 тонн: тяжёлый класс для металла и контейнеров</t>
+          <t>Вилочный погрузчик 5 тонн: характеристики и подбор</t>
         </is>
       </c>
       <c r="C117" s="29" t="inlineStr">
         <is>
-          <t>аренда вилочного погрузчика 7 тонн</t>
+          <t>автопогрузчик вилочный 5 тонн</t>
         </is>
       </c>
       <c r="D117" s="28" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E117" s="28" t="n">
         <v>5</v>
@@ -4130,16 +4500,16 @@
       </c>
       <c r="B118" s="29" t="inlineStr">
         <is>
-          <t>Вилочный погрузчик от 7 тонн: тяжёлый класс для металла и контейнеров</t>
+          <t>Вилочный погрузчик 5 тонн: характеристики и подбор</t>
         </is>
       </c>
       <c r="C118" s="29" t="inlineStr">
         <is>
-          <t>погрузчик вилочный 16 тонн</t>
+          <t>вилочный электропогрузчик 5 тонн</t>
         </is>
       </c>
       <c r="D118" s="28" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E118" s="28" t="n">
         <v>6</v>
@@ -4151,16 +4521,16 @@
       </c>
       <c r="B119" s="29" t="inlineStr">
         <is>
-          <t>Вилочный погрузчик от 7 тонн: тяжёлый класс для металла и контейнеров</t>
+          <t>Вилочный погрузчик 5 тонн: характеристики и подбор</t>
         </is>
       </c>
       <c r="C119" s="29" t="inlineStr">
         <is>
-          <t>вилочный погрузчик 8 тонн</t>
+          <t>автопогрузчик 5 тонн</t>
         </is>
       </c>
       <c r="D119" s="28" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E119" s="28" t="n">
         <v>7</v>
@@ -4172,16 +4542,16 @@
       </c>
       <c r="B120" s="29" t="inlineStr">
         <is>
-          <t>Вилочный погрузчик от 7 тонн: тяжёлый класс для металла и контейнеров</t>
+          <t>Вилочный погрузчик 5 тонн: характеристики и подбор</t>
         </is>
       </c>
       <c r="C120" s="29" t="inlineStr">
         <is>
-          <t>аренда вилочного погрузчика 8 тонн</t>
+          <t>вилочный погрузчик дизельный 3 5 тонны</t>
         </is>
       </c>
       <c r="D120" s="28" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E120" s="28" t="n">
         <v>8</v>
@@ -4193,16 +4563,16 @@
       </c>
       <c r="B121" s="29" t="inlineStr">
         <is>
-          <t>Вилочный погрузчик от 7 тонн: тяжёлый класс для металла и контейнеров</t>
+          <t>Вилочный погрузчик 5 тонн: характеристики и подбор</t>
         </is>
       </c>
       <c r="C121" s="29" t="inlineStr">
         <is>
-          <t>львовский вилочный погрузчик 10 тонн</t>
+          <t>вилочный погрузчик 1 5 тонны</t>
         </is>
       </c>
       <c r="D121" s="28" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E121" s="28" t="n">
         <v>9</v>
@@ -4214,16 +4584,16 @@
       </c>
       <c r="B122" s="29" t="inlineStr">
         <is>
-          <t>Вилочный погрузчик от 7 тонн: тяжёлый класс для металла и контейнеров</t>
+          <t>Вилочный погрузчик 5 тонн: характеристики и подбор</t>
         </is>
       </c>
       <c r="C122" s="29" t="inlineStr">
         <is>
-          <t>вилочный погрузчик doosan 7 тонн</t>
+          <t>электрический вилочный погрузчик 5 тонн</t>
         </is>
       </c>
       <c r="D122" s="28" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E122" s="28" t="n">
         <v>10</v>
@@ -4235,16 +4605,16 @@
       </c>
       <c r="B123" s="29" t="inlineStr">
         <is>
-          <t>Вилочный погрузчик от 7 тонн: тяжёлый класс для металла и контейнеров</t>
+          <t>Вилочный погрузчик 5 тонн: характеристики и подбор</t>
         </is>
       </c>
       <c r="C123" s="29" t="inlineStr">
         <is>
-          <t>автопогрузчик грузоподъемностью 10 тонн</t>
+          <t>вилочный погрузчик грузоподъемность 5 тонн</t>
         </is>
       </c>
       <c r="D123" s="28" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E123" s="28" t="n">
         <v>11</v>
@@ -4256,16 +4626,16 @@
       </c>
       <c r="B124" s="29" t="inlineStr">
         <is>
-          <t>Вилочный погрузчик от 7 тонн: тяжёлый класс для металла и контейнеров</t>
+          <t>Вилочный погрузчик 5 тонн: характеристики и подбор</t>
         </is>
       </c>
       <c r="C124" s="29" t="inlineStr">
         <is>
-          <t>вилочный погрузчик грузоподъемность 10 тонн</t>
+          <t>погрузчик вилочный 5 тонн фото</t>
         </is>
       </c>
       <c r="D124" s="28" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E124" s="28" t="n">
         <v>12</v>
@@ -4277,16 +4647,16 @@
       </c>
       <c r="B125" s="29" t="inlineStr">
         <is>
-          <t>Купить вилочный погрузчик: как устроена сделка и на что уходит время</t>
+          <t>Вилочный погрузчик от 7 тонн: тяжёлый класс для металла и контейнеров</t>
         </is>
       </c>
       <c r="C125" s="29" t="inlineStr">
         <is>
-          <t>вилочный погрузчик купить</t>
+          <t>аренда вилочного погрузчика 10 тонн</t>
         </is>
       </c>
       <c r="D125" s="28" t="n">
-        <v>1080</v>
+        <v>114</v>
       </c>
       <c r="E125" s="28" t="n">
         <v>1</v>
@@ -4298,16 +4668,16 @@
       </c>
       <c r="B126" s="29" t="inlineStr">
         <is>
-          <t>Купить вилочный погрузчик: как устроена сделка и на что уходит время</t>
+          <t>Вилочный погрузчик от 7 тонн: тяжёлый класс для металла и контейнеров</t>
         </is>
       </c>
       <c r="C126" s="29" t="inlineStr">
         <is>
-          <t>погрузчик вилочный 5 тонн купить</t>
+          <t>вилочный погрузчик 10 тонн</t>
         </is>
       </c>
       <c r="D126" s="28" t="n">
-        <v>280</v>
+        <v>95</v>
       </c>
       <c r="E126" s="28" t="n">
         <v>2</v>
@@ -4319,16 +4689,16 @@
       </c>
       <c r="B127" s="29" t="inlineStr">
         <is>
-          <t>Купить вилочный погрузчик: как устроена сделка и на что уходит время</t>
+          <t>Вилочный погрузчик от 7 тонн: тяжёлый класс для металла и контейнеров</t>
         </is>
       </c>
       <c r="C127" s="29" t="inlineStr">
         <is>
-          <t>вилочный электропогрузчик купить</t>
+          <t>вилочный погрузчик 7 тонн</t>
         </is>
       </c>
       <c r="D127" s="28" t="n">
-        <v>111</v>
+        <v>39</v>
       </c>
       <c r="E127" s="28" t="n">
         <v>3</v>
@@ -4340,16 +4710,16 @@
       </c>
       <c r="B128" s="29" t="inlineStr">
         <is>
-          <t>Купить вилочный погрузчик: как устроена сделка и на что уходит время</t>
+          <t>Вилочный погрузчик от 7 тонн: тяжёлый класс для металла и контейнеров</t>
         </is>
       </c>
       <c r="C128" s="29" t="inlineStr">
         <is>
-          <t>купить электрический вилочный погрузчик</t>
+          <t>аренда погрузчик вилочный 10 тонн аренда</t>
         </is>
       </c>
       <c r="D128" s="28" t="n">
-        <v>107</v>
+        <v>22</v>
       </c>
       <c r="E128" s="28" t="n">
         <v>4</v>
@@ -4361,16 +4731,16 @@
       </c>
       <c r="B129" s="29" t="inlineStr">
         <is>
-          <t>Купить вилочный погрузчик: как устроена сделка и на что уходит время</t>
+          <t>Вилочный погрузчик от 7 тонн: тяжёлый класс для металла и контейнеров</t>
         </is>
       </c>
       <c r="C129" s="29" t="inlineStr">
         <is>
-          <t>купить автопогрузчик</t>
+          <t>аренда вилочного погрузчика 7 тонн</t>
         </is>
       </c>
       <c r="D129" s="28" t="n">
-        <v>75</v>
+        <v>17</v>
       </c>
       <c r="E129" s="28" t="n">
         <v>5</v>
@@ -4382,16 +4752,16 @@
       </c>
       <c r="B130" s="29" t="inlineStr">
         <is>
-          <t>Купить вилочный погрузчик: как устроена сделка и на что уходит время</t>
+          <t>Вилочный погрузчик от 7 тонн: тяжёлый класс для металла и контейнеров</t>
         </is>
       </c>
       <c r="C130" s="29" t="inlineStr">
         <is>
-          <t>погрузчик вилочный цена</t>
+          <t>погрузчик вилочный 16 тонн</t>
         </is>
       </c>
       <c r="D130" s="28" t="n">
-        <v>65</v>
+        <v>16</v>
       </c>
       <c r="E130" s="28" t="n">
         <v>6</v>
@@ -4403,16 +4773,16 @@
       </c>
       <c r="B131" s="29" t="inlineStr">
         <is>
-          <t>Купить вилочный погрузчик: как устроена сделка и на что уходит время</t>
+          <t>Вилочный погрузчик от 7 тонн: тяжёлый класс для металла и контейнеров</t>
         </is>
       </c>
       <c r="C131" s="29" t="inlineStr">
         <is>
-          <t>вилочный погрузчик дизельный купить</t>
+          <t>вилочный погрузчик 8 тонн</t>
         </is>
       </c>
       <c r="D131" s="28" t="n">
-        <v>65</v>
+        <v>14</v>
       </c>
       <c r="E131" s="28" t="n">
         <v>7</v>
@@ -4424,16 +4794,16 @@
       </c>
       <c r="B132" s="29" t="inlineStr">
         <is>
-          <t>Купить вилочный погрузчик: как устроена сделка и на что уходит время</t>
+          <t>Вилочный погрузчик от 7 тонн: тяжёлый класс для металла и контейнеров</t>
         </is>
       </c>
       <c r="C132" s="29" t="inlineStr">
         <is>
-          <t>вилочный погрузчик 3 тонны дизельный купить</t>
+          <t>аренда вилочного погрузчика 8 тонн</t>
         </is>
       </c>
       <c r="D132" s="28" t="n">
-        <v>56</v>
+        <v>7</v>
       </c>
       <c r="E132" s="28" t="n">
         <v>8</v>
@@ -4445,16 +4815,16 @@
       </c>
       <c r="B133" s="29" t="inlineStr">
         <is>
-          <t>Купить вилочный погрузчик: как устроена сделка и на что уходит время</t>
+          <t>Вилочный погрузчик от 7 тонн: тяжёлый класс для металла и контейнеров</t>
         </is>
       </c>
       <c r="C133" s="29" t="inlineStr">
         <is>
-          <t>сиденье на вилочный погрузчик купить</t>
+          <t>автопогрузчик грузоподъемностью 10 тонн</t>
         </is>
       </c>
       <c r="D133" s="28" t="n">
-        <v>45</v>
+        <v>6</v>
       </c>
       <c r="E133" s="28" t="n">
         <v>9</v>
@@ -4466,16 +4836,16 @@
       </c>
       <c r="B134" s="29" t="inlineStr">
         <is>
-          <t>Купить вилочный погрузчик: как устроена сделка и на что уходит время</t>
+          <t>Вилочный погрузчик от 7 тонн: тяжёлый класс для металла и контейнеров</t>
         </is>
       </c>
       <c r="C134" s="29" t="inlineStr">
         <is>
-          <t>вилочный автопогрузчик купить</t>
+          <t>вилочный погрузчик грузоподъемность 10 тонн</t>
         </is>
       </c>
       <c r="D134" s="28" t="n">
-        <v>44</v>
+        <v>4</v>
       </c>
       <c r="E134" s="28" t="n">
         <v>10</v>
@@ -4487,16 +4857,16 @@
       </c>
       <c r="B135" s="29" t="inlineStr">
         <is>
-          <t>Купить вилочный погрузчик: как устроена сделка и на что уходит время</t>
+          <t>Вилочный погрузчик от 7 тонн: тяжёлый класс для металла и контейнеров</t>
         </is>
       </c>
       <c r="C135" s="29" t="inlineStr">
         <is>
-          <t>вилочный погрузчик купить в краснодаре</t>
+          <t>вилочный погрузчик 10 тонн характеристики</t>
         </is>
       </c>
       <c r="D135" s="28" t="n">
-        <v>43</v>
+        <v>4</v>
       </c>
       <c r="E135" s="28" t="n">
         <v>11</v>
@@ -4508,16 +4878,16 @@
       </c>
       <c r="B136" s="29" t="inlineStr">
         <is>
-          <t>Купить вилочный погрузчик: как устроена сделка и на что уходит время</t>
+          <t>Вилочный погрузчик от 7 тонн: тяжёлый класс для металла и контейнеров</t>
         </is>
       </c>
       <c r="C136" s="29" t="inlineStr">
         <is>
-          <t>вилочный погрузчик 5 тонн дизельный купить</t>
+          <t>автопогрузчик 10 тонн</t>
         </is>
       </c>
       <c r="D136" s="28" t="n">
-        <v>43</v>
+        <v>3</v>
       </c>
       <c r="E136" s="28" t="n">
         <v>12</v>
@@ -4529,16 +4899,16 @@
       </c>
       <c r="B137" s="29" t="inlineStr">
         <is>
-          <t>Вилочный погрузчик б/у: на что смотреть при покупке и как проверить перед сделкой</t>
+          <t>Купить вилочный погрузчик: как устроена сделка и на что уходит время</t>
         </is>
       </c>
       <c r="C137" s="29" t="inlineStr">
         <is>
-          <t>вилочный погрузчик купить бу</t>
+          <t>вилочный погрузчик купить</t>
         </is>
       </c>
       <c r="D137" s="28" t="n">
-        <v>252</v>
+        <v>1080</v>
       </c>
       <c r="E137" s="28" t="n">
         <v>1</v>
@@ -4550,16 +4920,16 @@
       </c>
       <c r="B138" s="29" t="inlineStr">
         <is>
-          <t>Вилочный погрузчик б/у: на что смотреть при покупке и как проверить перед сделкой</t>
+          <t>Купить вилочный погрузчик: как устроена сделка и на что уходит время</t>
         </is>
       </c>
       <c r="C138" s="29" t="inlineStr">
         <is>
-          <t>вилочный погрузчик купить бу на авито</t>
+          <t>погрузчик вилочный 5 тонн купить</t>
         </is>
       </c>
       <c r="D138" s="28" t="n">
-        <v>129</v>
+        <v>280</v>
       </c>
       <c r="E138" s="28" t="n">
         <v>2</v>
@@ -4571,16 +4941,16 @@
       </c>
       <c r="B139" s="29" t="inlineStr">
         <is>
-          <t>Вилочный погрузчик б/у: на что смотреть при покупке и как проверить перед сделкой</t>
+          <t>Купить вилочный погрузчик: как устроена сделка и на что уходит время</t>
         </is>
       </c>
       <c r="C139" s="29" t="inlineStr">
         <is>
-          <t>погрузчик вилочный бу</t>
+          <t>вилочный электропогрузчик купить</t>
         </is>
       </c>
       <c r="D139" s="28" t="n">
-        <v>126</v>
+        <v>111</v>
       </c>
       <c r="E139" s="28" t="n">
         <v>3</v>
@@ -4592,16 +4962,16 @@
       </c>
       <c r="B140" s="29" t="inlineStr">
         <is>
-          <t>Вилочный погрузчик б/у: на что смотреть при покупке и как проверить перед сделкой</t>
+          <t>Купить вилочный погрузчик: как устроена сделка и на что уходит время</t>
         </is>
       </c>
       <c r="C140" s="29" t="inlineStr">
         <is>
-          <t>вилочные погрузчики б у</t>
+          <t>купить электрический вилочный погрузчик</t>
         </is>
       </c>
       <c r="D140" s="28" t="n">
-        <v>70</v>
+        <v>107</v>
       </c>
       <c r="E140" s="28" t="n">
         <v>4</v>
@@ -4613,16 +4983,16 @@
       </c>
       <c r="B141" s="29" t="inlineStr">
         <is>
-          <t>Вилочный погрузчик б/у: на что смотреть при покупке и как проверить перед сделкой</t>
+          <t>Купить вилочный погрузчик: как устроена сделка и на что уходит время</t>
         </is>
       </c>
       <c r="C141" s="29" t="inlineStr">
         <is>
-          <t>купить б у погрузчик вилочный</t>
+          <t>купить автопогрузчик</t>
         </is>
       </c>
       <c r="D141" s="28" t="n">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="E141" s="28" t="n">
         <v>5</v>
@@ -4634,16 +5004,16 @@
       </c>
       <c r="B142" s="29" t="inlineStr">
         <is>
-          <t>Вилочный погрузчик б/у: на что смотреть при покупке и как проверить перед сделкой</t>
+          <t>Купить вилочный погрузчик: как устроена сделка и на что уходит время</t>
         </is>
       </c>
       <c r="C142" s="29" t="inlineStr">
         <is>
-          <t>авито вилочный погрузчик б у</t>
+          <t>вилочный погрузчик дизельный купить</t>
         </is>
       </c>
       <c r="D142" s="28" t="n">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="E142" s="28" t="n">
         <v>6</v>
@@ -4655,16 +5025,16 @@
       </c>
       <c r="B143" s="29" t="inlineStr">
         <is>
-          <t>Вилочный погрузчик б/у: на что смотреть при покупке и как проверить перед сделкой</t>
+          <t>Купить вилочный погрузчик: как устроена сделка и на что уходит время</t>
         </is>
       </c>
       <c r="C143" s="29" t="inlineStr">
         <is>
-          <t>продам погрузчик вилочный</t>
+          <t>вилочный погрузчик 3 тонны дизельный купить</t>
         </is>
       </c>
       <c r="D143" s="28" t="n">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="E143" s="28" t="n">
         <v>7</v>
@@ -4676,16 +5046,16 @@
       </c>
       <c r="B144" s="29" t="inlineStr">
         <is>
-          <t>Вилочный погрузчик б/у: на что смотреть при покупке и как проверить перед сделкой</t>
+          <t>Купить вилочный погрузчик: как устроена сделка и на что уходит время</t>
         </is>
       </c>
       <c r="C144" s="29" t="inlineStr">
         <is>
-          <t>продам вилочный погрузчик бу</t>
+          <t>сиденье на вилочный погрузчик купить</t>
         </is>
       </c>
       <c r="D144" s="28" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E144" s="28" t="n">
         <v>8</v>
@@ -4697,16 +5067,16 @@
       </c>
       <c r="B145" s="29" t="inlineStr">
         <is>
-          <t>Вилочный погрузчик б/у: на что смотреть при покупке и как проверить перед сделкой</t>
+          <t>Купить вилочный погрузчик: как устроена сделка и на что уходит время</t>
         </is>
       </c>
       <c r="C145" s="29" t="inlineStr">
         <is>
-          <t>автопогрузчик бу купить</t>
+          <t>вилочный автопогрузчик купить</t>
         </is>
       </c>
       <c r="D145" s="28" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E145" s="28" t="n">
         <v>9</v>
@@ -4718,16 +5088,16 @@
       </c>
       <c r="B146" s="29" t="inlineStr">
         <is>
-          <t>Вилочный погрузчик б/у: на что смотреть при покупке и как проверить перед сделкой</t>
+          <t>Купить вилочный погрузчик: как устроена сделка и на что уходит время</t>
         </is>
       </c>
       <c r="C146" s="29" t="inlineStr">
         <is>
-          <t>авито купить вилочный погрузчик</t>
+          <t>вилочный погрузчик купить в краснодаре</t>
         </is>
       </c>
       <c r="D146" s="28" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="E146" s="28" t="n">
         <v>10</v>
@@ -4739,16 +5109,16 @@
       </c>
       <c r="B147" s="29" t="inlineStr">
         <is>
-          <t>Вилочный погрузчик б/у: на что смотреть при покупке и как проверить перед сделкой</t>
+          <t>Купить вилочный погрузчик: как устроена сделка и на что уходит время</t>
         </is>
       </c>
       <c r="C147" s="29" t="inlineStr">
         <is>
-          <t>автопогрузчик вилочный б у купить</t>
+          <t>вилочный погрузчик 5 тонн дизельный купить</t>
         </is>
       </c>
       <c r="D147" s="28" t="n">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="E147" s="28" t="n">
         <v>11</v>
@@ -4760,16 +5130,16 @@
       </c>
       <c r="B148" s="29" t="inlineStr">
         <is>
-          <t>Вилочный погрузчик б/у: на что смотреть при покупке и как проверить перед сделкой</t>
+          <t>Купить вилочный погрузчик: как устроена сделка и на что уходит время</t>
         </is>
       </c>
       <c r="C148" s="29" t="inlineStr">
         <is>
-          <t>электропогрузчик вилочный б у купить</t>
+          <t>купить погрузчик вилочный новый</t>
         </is>
       </c>
       <c r="D148" s="28" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="E148" s="28" t="n">
         <v>12</v>
@@ -4781,16 +5151,16 @@
       </c>
       <c r="B149" s="29" t="inlineStr">
         <is>
-          <t>Heli: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
+          <t>Вилочный погрузчик б/у: на что смотреть при покупке и как проверить перед сделкой</t>
         </is>
       </c>
       <c r="C149" s="29" t="inlineStr">
         <is>
-          <t>heli вилочный погрузчик</t>
+          <t>вилочный погрузчик купить бу</t>
         </is>
       </c>
       <c r="D149" s="28" t="n">
-        <v>76</v>
+        <v>252</v>
       </c>
       <c r="E149" s="28" t="n">
         <v>1</v>
@@ -4802,16 +5172,16 @@
       </c>
       <c r="B150" s="29" t="inlineStr">
         <is>
-          <t>Heli: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
+          <t>Вилочный погрузчик б/у: на что смотреть при покупке и как проверить перед сделкой</t>
         </is>
       </c>
       <c r="C150" s="29" t="inlineStr">
         <is>
-          <t>heli cpcd30</t>
+          <t>погрузчик вилочный бу</t>
         </is>
       </c>
       <c r="D150" s="28" t="n">
-        <v>68</v>
+        <v>126</v>
       </c>
       <c r="E150" s="28" t="n">
         <v>2</v>
@@ -4823,16 +5193,16 @@
       </c>
       <c r="B151" s="29" t="inlineStr">
         <is>
-          <t>Heli: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
+          <t>Вилочный погрузчик б/у: на что смотреть при покупке и как проверить перед сделкой</t>
         </is>
       </c>
       <c r="C151" s="29" t="inlineStr">
         <is>
-          <t>liugong cpcd30</t>
+          <t>вилочные погрузчики б у</t>
         </is>
       </c>
       <c r="D151" s="28" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="E151" s="28" t="n">
         <v>3</v>
@@ -4844,16 +5214,16 @@
       </c>
       <c r="B152" s="29" t="inlineStr">
         <is>
-          <t>Heli: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
+          <t>Вилочный погрузчик б/у: на что смотреть при покупке и как проверить перед сделкой</t>
         </is>
       </c>
       <c r="C152" s="29" t="inlineStr">
         <is>
-          <t>jac cpcd35</t>
+          <t>купить б у погрузчик вилочный</t>
         </is>
       </c>
       <c r="D152" s="28" t="n">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="E152" s="28" t="n">
         <v>4</v>
@@ -4865,16 +5235,16 @@
       </c>
       <c r="B153" s="29" t="inlineStr">
         <is>
-          <t>Heli: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
+          <t>Вилочный погрузчик б/у: на что смотреть при покупке и как проверить перед сделкой</t>
         </is>
       </c>
       <c r="C153" s="29" t="inlineStr">
         <is>
-          <t>hangcha cpcd30 ag2</t>
+          <t>продам погрузчик вилочный</t>
         </is>
       </c>
       <c r="D153" s="28" t="n">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="E153" s="28" t="n">
         <v>5</v>
@@ -4886,12 +5256,12 @@
       </c>
       <c r="B154" s="29" t="inlineStr">
         <is>
-          <t>Heli: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
+          <t>Вилочный погрузчик б/у: на что смотреть при покупке и как проверить перед сделкой</t>
         </is>
       </c>
       <c r="C154" s="29" t="inlineStr">
         <is>
-          <t>cpcd30</t>
+          <t>продам вилочный погрузчик бу</t>
         </is>
       </c>
       <c r="D154" s="28" t="n">
@@ -4907,12 +5277,12 @@
       </c>
       <c r="B155" s="29" t="inlineStr">
         <is>
-          <t>Heli: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
+          <t>Вилочный погрузчик б/у: на что смотреть при покупке и как проверить перед сделкой</t>
         </is>
       </c>
       <c r="C155" s="29" t="inlineStr">
         <is>
-          <t>cpcd35 heli</t>
+          <t>автопогрузчик бу купить</t>
         </is>
       </c>
       <c r="D155" s="28" t="n">
@@ -4928,16 +5298,16 @@
       </c>
       <c r="B156" s="29" t="inlineStr">
         <is>
-          <t>Heli: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
+          <t>Вилочный погрузчик б/у: на что смотреть при покупке и как проверить перед сделкой</t>
         </is>
       </c>
       <c r="C156" s="29" t="inlineStr">
         <is>
-          <t>heli cpcd50</t>
+          <t>автопогрузчик вилочный б у купить</t>
         </is>
       </c>
       <c r="D156" s="28" t="n">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="E156" s="28" t="n">
         <v>8</v>
@@ -4949,16 +5319,16 @@
       </c>
       <c r="B157" s="29" t="inlineStr">
         <is>
-          <t>Heli: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
+          <t>Вилочный погрузчик б/у: на что смотреть при покупке и как проверить перед сделкой</t>
         </is>
       </c>
       <c r="C157" s="29" t="inlineStr">
         <is>
-          <t>погрузчик вилочный хели</t>
+          <t>электропогрузчик вилочный б у купить</t>
         </is>
       </c>
       <c r="D157" s="28" t="n">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="E157" s="28" t="n">
         <v>9</v>
@@ -4970,16 +5340,16 @@
       </c>
       <c r="B158" s="29" t="inlineStr">
         <is>
-          <t>Heli: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
+          <t>Вилочный погрузчик б/у: на что смотреть при покупке и как проверить перед сделкой</t>
         </is>
       </c>
       <c r="C158" s="29" t="inlineStr">
         <is>
-          <t>cpcd30 погрузчик</t>
+          <t>продажа автопогрузчиков б у</t>
         </is>
       </c>
       <c r="D158" s="28" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="E158" s="28" t="n">
         <v>10</v>
@@ -4991,16 +5361,16 @@
       </c>
       <c r="B159" s="29" t="inlineStr">
         <is>
-          <t>Heli: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
+          <t>Вилочный погрузчик б/у: на что смотреть при покупке и как проверить перед сделкой</t>
         </is>
       </c>
       <c r="C159" s="29" t="inlineStr">
         <is>
-          <t>hangcha cpcd35 ag2</t>
+          <t>продам погрузчик вилочный б у</t>
         </is>
       </c>
       <c r="D159" s="28" t="n">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="E159" s="28" t="n">
         <v>11</v>
@@ -5012,16 +5382,16 @@
       </c>
       <c r="B160" s="29" t="inlineStr">
         <is>
-          <t>Heli: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
+          <t>Вилочный погрузчик б/у: на что смотреть при покупке и как проверить перед сделкой</t>
         </is>
       </c>
       <c r="C160" s="29" t="inlineStr">
         <is>
-          <t>heli cpd15</t>
+          <t>аренда вилочного погрузчика екатеринбург</t>
         </is>
       </c>
       <c r="D160" s="28" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="E160" s="28" t="n">
         <v>12</v>
@@ -5033,16 +5403,16 @@
       </c>
       <c r="B161" s="29" t="inlineStr">
         <is>
-          <t>Toyota: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
+          <t>Из чего складывается цена вилочного погрузчика</t>
         </is>
       </c>
       <c r="C161" s="29" t="inlineStr">
         <is>
-          <t>погрузчик вилочный тойота</t>
+          <t>погрузчик вилочный цена</t>
         </is>
       </c>
       <c r="D161" s="28" t="n">
-        <v>90</v>
+        <v>65</v>
       </c>
       <c r="E161" s="28" t="n">
         <v>1</v>
@@ -5054,16 +5424,16 @@
       </c>
       <c r="B162" s="29" t="inlineStr">
         <is>
-          <t>Toyota: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
+          <t>Из чего складывается цена вилочного погрузчика</t>
         </is>
       </c>
       <c r="C162" s="29" t="inlineStr">
         <is>
-          <t>toyota вилочный погрузчик</t>
+          <t>услуги погрузчика вилочного цена за час</t>
         </is>
       </c>
       <c r="D162" s="28" t="n">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="E162" s="28" t="n">
         <v>2</v>
@@ -5075,12 +5445,12 @@
       </c>
       <c r="B163" s="29" t="inlineStr">
         <is>
-          <t>Toyota: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
+          <t>Из чего складывается цена вилочного погрузчика</t>
         </is>
       </c>
       <c r="C163" s="29" t="inlineStr">
         <is>
-          <t>запчасти для погрузчика тойота вилочного</t>
+          <t>сколько стоит погрузчик вилочный</t>
         </is>
       </c>
       <c r="D163" s="28" t="n">
@@ -5096,16 +5466,16 @@
       </c>
       <c r="B164" s="29" t="inlineStr">
         <is>
-          <t>Toyota: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
+          <t>Из чего складывается цена вилочного погрузчика</t>
         </is>
       </c>
       <c r="C164" s="29" t="inlineStr">
         <is>
-          <t>погрузчики вилочные тойота краснодар</t>
+          <t>погрузчик 5 тонн цена вилочный</t>
         </is>
       </c>
       <c r="D164" s="28" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E164" s="28" t="n">
         <v>4</v>
@@ -5117,16 +5487,16 @@
       </c>
       <c r="B165" s="29" t="inlineStr">
         <is>
-          <t>Toyota: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
+          <t>Из чего складывается цена вилочного погрузчика</t>
         </is>
       </c>
       <c r="C165" s="29" t="inlineStr">
         <is>
-          <t>запчасти на вилочный погрузчик тойота</t>
+          <t>стоимость погрузчика вилочного погрузчика</t>
         </is>
       </c>
       <c r="D165" s="28" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E165" s="28" t="n">
         <v>5</v>
@@ -5138,16 +5508,16 @@
       </c>
       <c r="B166" s="29" t="inlineStr">
         <is>
-          <t>Toyota: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
+          <t>Из чего складывается цена вилочного погрузчика</t>
         </is>
       </c>
       <c r="C166" s="29" t="inlineStr">
         <is>
-          <t>toyota вилочный погрузчик 62 8fd30</t>
+          <t>автопогрузчик цена</t>
         </is>
       </c>
       <c r="D166" s="28" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E166" s="28" t="n">
         <v>6</v>
@@ -5159,16 +5529,16 @@
       </c>
       <c r="B167" s="29" t="inlineStr">
         <is>
-          <t>Toyota: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
+          <t>Из чего складывается цена вилочного погрузчика</t>
         </is>
       </c>
       <c r="C167" s="29" t="inlineStr">
         <is>
-          <t>купить вилочный погрузчик тойота</t>
+          <t>цена электрический вилочный погрузчик</t>
         </is>
       </c>
       <c r="D167" s="28" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E167" s="28" t="n">
         <v>7</v>
@@ -5180,16 +5550,16 @@
       </c>
       <c r="B168" s="29" t="inlineStr">
         <is>
-          <t>Toyota: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
+          <t>Из чего складывается цена вилочного погрузчика</t>
         </is>
       </c>
       <c r="C168" s="29" t="inlineStr">
         <is>
-          <t>тойота автопогрузчик 62 8fd15</t>
+          <t>вилочный погрузчик стоимость</t>
         </is>
       </c>
       <c r="D168" s="28" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E168" s="28" t="n">
         <v>8</v>
@@ -5201,16 +5571,16 @@
       </c>
       <c r="B169" s="29" t="inlineStr">
         <is>
-          <t>Toyota: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
+          <t>Из чего складывается цена вилочного погрузчика</t>
         </is>
       </c>
       <c r="C169" s="29" t="inlineStr">
         <is>
-          <t>toyota 32 8fg15 автопогрузчик</t>
+          <t>купить автопогрузчик вилочный цена</t>
         </is>
       </c>
       <c r="D169" s="28" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E169" s="28" t="n">
         <v>9</v>
@@ -5222,16 +5592,16 @@
       </c>
       <c r="B170" s="29" t="inlineStr">
         <is>
-          <t>Toyota: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
+          <t>Из чего складывается цена вилочного погрузчика</t>
         </is>
       </c>
       <c r="C170" s="29" t="inlineStr">
         <is>
-          <t>запчасти вилочные погрузчики toyota</t>
+          <t>вилочные погрузчики электрические цена</t>
         </is>
       </c>
       <c r="D170" s="28" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E170" s="28" t="n">
         <v>10</v>
@@ -5243,16 +5613,16 @@
       </c>
       <c r="B171" s="29" t="inlineStr">
         <is>
-          <t>Toyota: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
+          <t>Из чего складывается цена вилочного погрузчика</t>
         </is>
       </c>
       <c r="C171" s="29" t="inlineStr">
         <is>
-          <t>купить вилочный погрузчик тойота бу</t>
+          <t>стартер на вилочный погрузчик цена</t>
         </is>
       </c>
       <c r="D171" s="28" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E171" s="28" t="n">
         <v>11</v>
@@ -5264,16 +5634,16 @@
       </c>
       <c r="B172" s="29" t="inlineStr">
         <is>
-          <t>Toyota: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
+          <t>Из чего складывается цена вилочного погрузчика</t>
         </is>
       </c>
       <c r="C172" s="29" t="inlineStr">
         <is>
-          <t>автопогрузчик toyota</t>
+          <t>вилочный электропогрузчик цена</t>
         </is>
       </c>
       <c r="D172" s="28" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E172" s="28" t="n">
         <v>12</v>
@@ -5285,16 +5655,16 @@
       </c>
       <c r="B173" s="29" t="inlineStr">
         <is>
-          <t>Komatsu: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
+          <t>Вилочный погрузчик на Авито: как не купить проблемный</t>
         </is>
       </c>
       <c r="C173" s="29" t="inlineStr">
         <is>
-          <t>погрузчик вилочный komatsu</t>
+          <t>вилочный погрузчик купить бу на авито</t>
         </is>
       </c>
       <c r="D173" s="28" t="n">
-        <v>60</v>
+        <v>129</v>
       </c>
       <c r="E173" s="28" t="n">
         <v>1</v>
@@ -5306,16 +5676,16 @@
       </c>
       <c r="B174" s="29" t="inlineStr">
         <is>
-          <t>Komatsu: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
+          <t>Вилочный погрузчик на Авито: как не купить проблемный</t>
         </is>
       </c>
       <c r="C174" s="29" t="inlineStr">
         <is>
-          <t>вилочный погрузчик коматсу</t>
+          <t>авито вилочный погрузчик</t>
         </is>
       </c>
       <c r="D174" s="28" t="n">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="E174" s="28" t="n">
         <v>2</v>
@@ -5327,16 +5697,16 @@
       </c>
       <c r="B175" s="29" t="inlineStr">
         <is>
-          <t>Komatsu: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
+          <t>Вилочный погрузчик на Авито: как не купить проблемный</t>
         </is>
       </c>
       <c r="C175" s="29" t="inlineStr">
         <is>
-          <t>автопогрузчик komatsu</t>
+          <t>авито вилочный погрузчик б у</t>
         </is>
       </c>
       <c r="D175" s="28" t="n">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="E175" s="28" t="n">
         <v>3</v>
@@ -5348,16 +5718,16 @@
       </c>
       <c r="B176" s="29" t="inlineStr">
         <is>
-          <t>Komatsu: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
+          <t>Вилочный погрузчик на Авито: как не купить проблемный</t>
         </is>
       </c>
       <c r="C176" s="29" t="inlineStr">
         <is>
-          <t>вилочный погрузчик комацу</t>
+          <t>погрузчики вилочные avito</t>
         </is>
       </c>
       <c r="D176" s="28" t="n">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="E176" s="28" t="n">
         <v>4</v>
@@ -5369,16 +5739,16 @@
       </c>
       <c r="B177" s="29" t="inlineStr">
         <is>
-          <t>Komatsu: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
+          <t>Вилочный погрузчик на Авито: как не купить проблемный</t>
         </is>
       </c>
       <c r="C177" s="29" t="inlineStr">
         <is>
-          <t>коматсу погрузчик купить вилочный</t>
+          <t>авито купить вилочный погрузчик</t>
         </is>
       </c>
       <c r="D177" s="28" t="n">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="E177" s="28" t="n">
         <v>5</v>
@@ -5390,16 +5760,16 @@
       </c>
       <c r="B178" s="29" t="inlineStr">
         <is>
-          <t>Komatsu: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
+          <t>Вилочный погрузчик на Авито: как не купить проблемный</t>
         </is>
       </c>
       <c r="C178" s="29" t="inlineStr">
         <is>
-          <t>погрузчик вилочный комацу бу купить</t>
+          <t>купить вилочный погрузчик на авито</t>
         </is>
       </c>
       <c r="D178" s="28" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="E178" s="28" t="n">
         <v>6</v>
@@ -5411,16 +5781,16 @@
       </c>
       <c r="B179" s="29" t="inlineStr">
         <is>
-          <t>Komatsu: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
+          <t>Вилочный погрузчик на Авито: как не купить проблемный</t>
         </is>
       </c>
       <c r="C179" s="29" t="inlineStr">
         <is>
-          <t>запчасти для погрузчиков вилочных komatsu</t>
+          <t>погрузчик вилочный б у купить на авито</t>
         </is>
       </c>
       <c r="D179" s="28" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="E179" s="28" t="n">
         <v>7</v>
@@ -5432,16 +5802,16 @@
       </c>
       <c r="B180" s="29" t="inlineStr">
         <is>
-          <t>Komatsu: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
+          <t>Вилочный погрузчик на Авито: как не купить проблемный</t>
         </is>
       </c>
       <c r="C180" s="29" t="inlineStr">
         <is>
-          <t>погрузчик вилочный komatsu fd15t 21</t>
+          <t>купить вилочный погрузчик б у авито</t>
         </is>
       </c>
       <c r="D180" s="28" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="E180" s="28" t="n">
         <v>8</v>
@@ -5453,16 +5823,16 @@
       </c>
       <c r="B181" s="29" t="inlineStr">
         <is>
-          <t>Komatsu: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
+          <t>Вилочный погрузчик на Авито: как не купить проблемный</t>
         </is>
       </c>
       <c r="C181" s="29" t="inlineStr">
         <is>
-          <t>вилочный погрузчик коматсу 15</t>
+          <t>купить вилочный погрузчик бу купить на авито</t>
         </is>
       </c>
       <c r="D181" s="28" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="E181" s="28" t="n">
         <v>9</v>
@@ -5474,16 +5844,16 @@
       </c>
       <c r="B182" s="29" t="inlineStr">
         <is>
-          <t>Komatsu: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
+          <t>Вилочный погрузчик на Авито: как не купить проблемный</t>
         </is>
       </c>
       <c r="C182" s="29" t="inlineStr">
         <is>
-          <t>вилочный погрузчик komatsu fd25t 17</t>
+          <t>купить на авито вилочный погрузчик бу на авито</t>
         </is>
       </c>
       <c r="D182" s="28" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E182" s="28" t="n">
         <v>10</v>
@@ -5495,16 +5865,16 @@
       </c>
       <c r="B183" s="29" t="inlineStr">
         <is>
-          <t>Komatsu: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
+          <t>Вилочный погрузчик на Авито: как не купить проблемный</t>
         </is>
       </c>
       <c r="C183" s="29" t="inlineStr">
         <is>
-          <t>запчасти на вилочный погрузчик komatsu</t>
+          <t>погрузчик вилочный авито пермь</t>
         </is>
       </c>
       <c r="D183" s="28" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E183" s="28" t="n">
         <v>11</v>
@@ -5516,12 +5886,12 @@
       </c>
       <c r="B184" s="29" t="inlineStr">
         <is>
-          <t>Komatsu: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
+          <t>Вилочный погрузчик на Авито: как не купить проблемный</t>
         </is>
       </c>
       <c r="C184" s="29" t="inlineStr">
         <is>
-          <t>автопогрузчик коматсу</t>
+          <t>авито тверь купить вилочный погрузчик</t>
         </is>
       </c>
       <c r="D184" s="28" t="n">
@@ -5537,16 +5907,16 @@
       </c>
       <c r="B185" s="29" t="inlineStr">
         <is>
-          <t>Львовский, Балканкар, ТВЭКС, Амкодор — советские и постсоветские марки: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
+          <t>Heli: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
         </is>
       </c>
       <c r="C185" s="29" t="inlineStr">
         <is>
-          <t>вилочный погрузчик львовский погрузчик</t>
+          <t>heli вилочный погрузчик</t>
         </is>
       </c>
       <c r="D185" s="28" t="n">
-        <v>95</v>
+        <v>76</v>
       </c>
       <c r="E185" s="28" t="n">
         <v>1</v>
@@ -5558,16 +5928,16 @@
       </c>
       <c r="B186" s="29" t="inlineStr">
         <is>
-          <t>Львовский, Балканкар, ТВЭКС, Амкодор — советские и постсоветские марки: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
+          <t>Heli: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
         </is>
       </c>
       <c r="C186" s="29" t="inlineStr">
         <is>
-          <t>погрузчик вилочный советский</t>
+          <t>heli cpcd30</t>
         </is>
       </c>
       <c r="D186" s="28" t="n">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="E186" s="28" t="n">
         <v>2</v>
@@ -5579,16 +5949,16 @@
       </c>
       <c r="B187" s="29" t="inlineStr">
         <is>
-          <t>Львовский, Балканкар, ТВЭКС, Амкодор — советские и постсоветские марки: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
+          <t>Heli: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
         </is>
       </c>
       <c r="C187" s="29" t="inlineStr">
         <is>
-          <t>львовский автопогрузчик</t>
+          <t>liugong cpcd30</t>
         </is>
       </c>
       <c r="D187" s="28" t="n">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="E187" s="28" t="n">
         <v>3</v>
@@ -5600,16 +5970,16 @@
       </c>
       <c r="B188" s="29" t="inlineStr">
         <is>
-          <t>Львовский, Балканкар, ТВЭКС, Амкодор — советские и постсоветские марки: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
+          <t>Heli: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
         </is>
       </c>
       <c r="C188" s="29" t="inlineStr">
         <is>
-          <t>вилочный погрузчик твэкс вп 05 купить</t>
+          <t>jac cpcd35</t>
         </is>
       </c>
       <c r="D188" s="28" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E188" s="28" t="n">
         <v>4</v>
@@ -5621,16 +5991,16 @@
       </c>
       <c r="B189" s="29" t="inlineStr">
         <is>
-          <t>Львовский, Балканкар, ТВЭКС, Амкодор — советские и постсоветские марки: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
+          <t>Heli: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
         </is>
       </c>
       <c r="C189" s="29" t="inlineStr">
         <is>
-          <t>погрузчик вилочный львовский</t>
+          <t>hangcha cpcd30 ag2</t>
         </is>
       </c>
       <c r="D189" s="28" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="E189" s="28" t="n">
         <v>5</v>
@@ -5642,16 +6012,16 @@
       </c>
       <c r="B190" s="29" t="inlineStr">
         <is>
-          <t>Львовский, Балканкар, ТВЭКС, Амкодор — советские и постсоветские марки: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
+          <t>Heli: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
         </is>
       </c>
       <c r="C190" s="29" t="inlineStr">
         <is>
-          <t>амкодор вилочный погрузчик</t>
+          <t>cpcd30</t>
         </is>
       </c>
       <c r="D190" s="28" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E190" s="28" t="n">
         <v>6</v>
@@ -5663,16 +6033,16 @@
       </c>
       <c r="B191" s="29" t="inlineStr">
         <is>
-          <t>Львовский, Балканкар, ТВЭКС, Амкодор — советские и постсоветские марки: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
+          <t>Heli: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
         </is>
       </c>
       <c r="C191" s="29" t="inlineStr">
         <is>
-          <t>погрузчик вилочный ссср</t>
+          <t>cpcd35 heli</t>
         </is>
       </c>
       <c r="D191" s="28" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="E191" s="28" t="n">
         <v>7</v>
@@ -5684,16 +6054,16 @@
       </c>
       <c r="B192" s="29" t="inlineStr">
         <is>
-          <t>Львовский, Балканкар, ТВЭКС, Амкодор — советские и постсоветские марки: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
+          <t>Heli: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
         </is>
       </c>
       <c r="C192" s="29" t="inlineStr">
         <is>
-          <t>балканкар погрузчик вилочный</t>
+          <t>heli cpcd50</t>
         </is>
       </c>
       <c r="D192" s="28" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="E192" s="28" t="n">
         <v>8</v>
@@ -5705,16 +6075,16 @@
       </c>
       <c r="B193" s="29" t="inlineStr">
         <is>
-          <t>Львовский, Балканкар, ТВЭКС, Амкодор — советские и постсоветские марки: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
+          <t>Heli: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
         </is>
       </c>
       <c r="C193" s="29" t="inlineStr">
         <is>
-          <t>погрузчик вилочный львовский завод</t>
+          <t>погрузчик вилочный хели</t>
         </is>
       </c>
       <c r="D193" s="28" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E193" s="28" t="n">
         <v>9</v>
@@ -5726,16 +6096,16 @@
       </c>
       <c r="B194" s="29" t="inlineStr">
         <is>
-          <t>Львовский, Балканкар, ТВЭКС, Амкодор — советские и постсоветские марки: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
+          <t>Heli: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
         </is>
       </c>
       <c r="C194" s="29" t="inlineStr">
         <is>
-          <t>вп 05 твэкс вилочный погрузчик</t>
+          <t>cpcd30 погрузчик</t>
         </is>
       </c>
       <c r="D194" s="28" t="n">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="E194" s="28" t="n">
         <v>10</v>
@@ -5747,16 +6117,16 @@
       </c>
       <c r="B195" s="29" t="inlineStr">
         <is>
-          <t>Львовский, Балканкар, ТВЭКС, Амкодор — советские и постсоветские марки: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
+          <t>Heli: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
         </is>
       </c>
       <c r="C195" s="29" t="inlineStr">
         <is>
-          <t>вилочный погрузчик львовский купить</t>
+          <t>hangcha cpcd35 ag2</t>
         </is>
       </c>
       <c r="D195" s="28" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="E195" s="28" t="n">
         <v>11</v>
@@ -5768,16 +6138,16 @@
       </c>
       <c r="B196" s="29" t="inlineStr">
         <is>
-          <t>Львовский, Балканкар, ТВЭКС, Амкодор — советские и постсоветские марки: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
+          <t>Heli: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
         </is>
       </c>
       <c r="C196" s="29" t="inlineStr">
         <is>
-          <t>вилочный погрузчик балканкар бу купить</t>
+          <t>heli cpd15</t>
         </is>
       </c>
       <c r="D196" s="28" t="n">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="E196" s="28" t="n">
         <v>12</v>
@@ -5789,16 +6159,16 @@
       </c>
       <c r="B197" s="29" t="inlineStr">
         <is>
-          <t>Still, Linde, Jungheinrich, Yale, Hyster, Doosan, Clark — европейские и корейские марки: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
+          <t>Toyota: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
         </is>
       </c>
       <c r="C197" s="29" t="inlineStr">
         <is>
-          <t>doosan погрузчик вилочный</t>
+          <t>погрузчик вилочный тойота</t>
         </is>
       </c>
       <c r="D197" s="28" t="n">
-        <v>39</v>
+        <v>90</v>
       </c>
       <c r="E197" s="28" t="n">
         <v>1</v>
@@ -5810,16 +6180,16 @@
       </c>
       <c r="B198" s="29" t="inlineStr">
         <is>
-          <t>Still, Linde, Jungheinrich, Yale, Hyster, Doosan, Clark — европейские и корейские марки: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
+          <t>Toyota: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
         </is>
       </c>
       <c r="C198" s="29" t="inlineStr">
         <is>
-          <t>погрузчик дусан вилочный</t>
+          <t>toyota вилочный погрузчик</t>
         </is>
       </c>
       <c r="D198" s="28" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="E198" s="28" t="n">
         <v>2</v>
@@ -5831,12 +6201,12 @@
       </c>
       <c r="B199" s="29" t="inlineStr">
         <is>
-          <t>Still, Linde, Jungheinrich, Yale, Hyster, Doosan, Clark — европейские и корейские марки: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
+          <t>Toyota: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
         </is>
       </c>
       <c r="C199" s="29" t="inlineStr">
         <is>
-          <t>hyster погрузчик вилочный</t>
+          <t>запчасти для погрузчика тойота вилочного</t>
         </is>
       </c>
       <c r="D199" s="28" t="n">
@@ -5852,16 +6222,16 @@
       </c>
       <c r="B200" s="29" t="inlineStr">
         <is>
-          <t>Still, Linde, Jungheinrich, Yale, Hyster, Doosan, Clark — европейские и корейские марки: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
+          <t>Toyota: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
         </is>
       </c>
       <c r="C200" s="29" t="inlineStr">
         <is>
-          <t>jungheinrich вилочный погрузчик</t>
+          <t>погрузчик тойота вилочный 3 тонны</t>
         </is>
       </c>
       <c r="D200" s="28" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E200" s="28" t="n">
         <v>4</v>
@@ -5873,16 +6243,16 @@
       </c>
       <c r="B201" s="29" t="inlineStr">
         <is>
-          <t>Still, Linde, Jungheinrich, Yale, Hyster, Doosan, Clark — европейские и корейские марки: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
+          <t>Toyota: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
         </is>
       </c>
       <c r="C201" s="29" t="inlineStr">
         <is>
-          <t>вилочный погрузчик still</t>
+          <t>погрузчики вилочные тойота краснодар</t>
         </is>
       </c>
       <c r="D201" s="28" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E201" s="28" t="n">
         <v>5</v>
@@ -5894,16 +6264,16 @@
       </c>
       <c r="B202" s="29" t="inlineStr">
         <is>
-          <t>Still, Linde, Jungheinrich, Yale, Hyster, Doosan, Clark — европейские и корейские марки: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
+          <t>Toyota: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
         </is>
       </c>
       <c r="C202" s="29" t="inlineStr">
         <is>
-          <t>погрузчик yale вилочный</t>
+          <t>запчасти на вилочный погрузчик тойота</t>
         </is>
       </c>
       <c r="D202" s="28" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E202" s="28" t="n">
         <v>6</v>
@@ -5915,16 +6285,16 @@
       </c>
       <c r="B203" s="29" t="inlineStr">
         <is>
-          <t>Still, Linde, Jungheinrich, Yale, Hyster, Doosan, Clark — европейские и корейские марки: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
+          <t>Toyota: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
         </is>
       </c>
       <c r="C203" s="29" t="inlineStr">
         <is>
-          <t>вилочный погрузчик юнгхайнрих</t>
+          <t>toyota вилочный погрузчик 62 8fd30</t>
         </is>
       </c>
       <c r="D203" s="28" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E203" s="28" t="n">
         <v>7</v>
@@ -5936,12 +6306,12 @@
       </c>
       <c r="B204" s="29" t="inlineStr">
         <is>
-          <t>Still, Linde, Jungheinrich, Yale, Hyster, Doosan, Clark — европейские и корейские марки: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
+          <t>Toyota: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
         </is>
       </c>
       <c r="C204" s="29" t="inlineStr">
         <is>
-          <t>вилочный погрузчик linde</t>
+          <t>купить вилочный погрузчик тойота</t>
         </is>
       </c>
       <c r="D204" s="28" t="n">
@@ -5957,12 +6327,12 @@
       </c>
       <c r="B205" s="29" t="inlineStr">
         <is>
-          <t>Still, Linde, Jungheinrich, Yale, Hyster, Doosan, Clark — европейские и корейские марки: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
+          <t>Toyota: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
         </is>
       </c>
       <c r="C205" s="29" t="inlineStr">
         <is>
-          <t>вилочный погрузчик linde h30d</t>
+          <t>тойота автопогрузчик 62 8fd15</t>
         </is>
       </c>
       <c r="D205" s="28" t="n">
@@ -5978,16 +6348,16 @@
       </c>
       <c r="B206" s="29" t="inlineStr">
         <is>
-          <t>Still, Linde, Jungheinrich, Yale, Hyster, Doosan, Clark — европейские и корейские марки: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
+          <t>Toyota: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
         </is>
       </c>
       <c r="C206" s="29" t="inlineStr">
         <is>
-          <t>doosan вилочный погрузчик запчасти</t>
+          <t>тойота вилочный электропогрузчик</t>
         </is>
       </c>
       <c r="D206" s="28" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E206" s="28" t="n">
         <v>10</v>
@@ -5999,16 +6369,16 @@
       </c>
       <c r="B207" s="29" t="inlineStr">
         <is>
-          <t>Still, Linde, Jungheinrich, Yale, Hyster, Doosan, Clark — европейские и корейские марки: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
+          <t>Toyota: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
         </is>
       </c>
       <c r="C207" s="29" t="inlineStr">
         <is>
-          <t>автопогрузчик yale</t>
+          <t>toyota 32 8fg15 автопогрузчик</t>
         </is>
       </c>
       <c r="D207" s="28" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E207" s="28" t="n">
         <v>11</v>
@@ -6020,16 +6390,16 @@
       </c>
       <c r="B208" s="29" t="inlineStr">
         <is>
-          <t>Still, Linde, Jungheinrich, Yale, Hyster, Doosan, Clark — европейские и корейские марки: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
+          <t>Toyota: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
         </is>
       </c>
       <c r="C208" s="29" t="inlineStr">
         <is>
-          <t>погрузчик вилочный jungheinrich dfg 320</t>
+          <t>запчасти вилочные погрузчики toyota</t>
         </is>
       </c>
       <c r="D208" s="28" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E208" s="28" t="n">
         <v>12</v>
@@ -6041,16 +6411,16 @@
       </c>
       <c r="B209" s="29" t="inlineStr">
         <is>
-          <t>LiuGong и Lonking: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
+          <t>Komatsu: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
         </is>
       </c>
       <c r="C209" s="29" t="inlineStr">
         <is>
-          <t>liugong погрузчик вилочный</t>
+          <t>погрузчик вилочный komatsu</t>
         </is>
       </c>
       <c r="D209" s="28" t="n">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="E209" s="28" t="n">
         <v>1</v>
@@ -6062,16 +6432,16 @@
       </c>
       <c r="B210" s="29" t="inlineStr">
         <is>
-          <t>LiuGong и Lonking: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
+          <t>Komatsu: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
         </is>
       </c>
       <c r="C210" s="29" t="inlineStr">
         <is>
-          <t>погрузчик вилочный lonking</t>
+          <t>вилочный погрузчик коматсу</t>
         </is>
       </c>
       <c r="D210" s="28" t="n">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="E210" s="28" t="n">
         <v>2</v>
@@ -6083,16 +6453,16 @@
       </c>
       <c r="B211" s="29" t="inlineStr">
         <is>
-          <t>LiuGong и Lonking: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
+          <t>Komatsu: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
         </is>
       </c>
       <c r="C211" s="29" t="inlineStr">
         <is>
-          <t>вилочный погрузчик лонкинг</t>
+          <t>автопогрузчик komatsu</t>
         </is>
       </c>
       <c r="D211" s="28" t="n">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="E211" s="28" t="n">
         <v>3</v>
@@ -6104,16 +6474,16 @@
       </c>
       <c r="B212" s="29" t="inlineStr">
         <is>
-          <t>LiuGong и Lonking: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
+          <t>Komatsu: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
         </is>
       </c>
       <c r="C212" s="29" t="inlineStr">
         <is>
-          <t>погрузчик вилочный lonking lg30dt</t>
+          <t>вилочный погрузчик комацу</t>
         </is>
       </c>
       <c r="D212" s="28" t="n">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="E212" s="28" t="n">
         <v>4</v>
@@ -6125,16 +6495,16 @@
       </c>
       <c r="B213" s="29" t="inlineStr">
         <is>
-          <t>LiuGong и Lonking: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
+          <t>Komatsu: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
         </is>
       </c>
       <c r="C213" s="29" t="inlineStr">
         <is>
-          <t>вилочный погрузчик lonking lg50dt</t>
+          <t>вилочный погрузчик комацу 3 тонны</t>
         </is>
       </c>
       <c r="D213" s="28" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E213" s="28" t="n">
         <v>5</v>
@@ -6146,16 +6516,16 @@
       </c>
       <c r="B214" s="29" t="inlineStr">
         <is>
-          <t>LiuGong и Lonking: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
+          <t>Komatsu: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
         </is>
       </c>
       <c r="C214" s="29" t="inlineStr">
         <is>
-          <t>вилочный погрузчик lonking fd20t</t>
+          <t>коматсу погрузчик купить вилочный</t>
         </is>
       </c>
       <c r="D214" s="28" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E214" s="28" t="n">
         <v>6</v>
@@ -6167,16 +6537,16 @@
       </c>
       <c r="B215" s="29" t="inlineStr">
         <is>
-          <t>LiuGong и Lonking: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
+          <t>Komatsu: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
         </is>
       </c>
       <c r="C215" s="29" t="inlineStr">
         <is>
-          <t>погрузчик вилочный lonking fd15t</t>
+          <t>погрузчик вилочный комацу бу купить</t>
         </is>
       </c>
       <c r="D215" s="28" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E215" s="28" t="n">
         <v>7</v>
@@ -6188,16 +6558,16 @@
       </c>
       <c r="B216" s="29" t="inlineStr">
         <is>
-          <t>LiuGong и Lonking: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
+          <t>Komatsu: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
         </is>
       </c>
       <c r="C216" s="29" t="inlineStr">
         <is>
-          <t>вилочный погрузчик lonking lg35dt</t>
+          <t>запчасти для погрузчиков вилочных komatsu</t>
         </is>
       </c>
       <c r="D216" s="28" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E216" s="28" t="n">
         <v>8</v>
@@ -6209,16 +6579,16 @@
       </c>
       <c r="B217" s="29" t="inlineStr">
         <is>
-          <t>LiuGong и Lonking: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
+          <t>Komatsu: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
         </is>
       </c>
       <c r="C217" s="29" t="inlineStr">
         <is>
-          <t>вилочный погрузчик lonking fd35t</t>
+          <t>погрузчик вилочный komatsu fd15t 21</t>
         </is>
       </c>
       <c r="D217" s="28" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E217" s="28" t="n">
         <v>9</v>
@@ -6230,16 +6600,16 @@
       </c>
       <c r="B218" s="29" t="inlineStr">
         <is>
-          <t>LiuGong и Lonking: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
+          <t>Komatsu: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
         </is>
       </c>
       <c r="C218" s="29" t="inlineStr">
         <is>
-          <t>автопогрузчик лиугонг</t>
+          <t>вилочный погрузчик коматсу 15</t>
         </is>
       </c>
       <c r="D218" s="28" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E218" s="28" t="n">
         <v>10</v>
@@ -6251,16 +6621,16 @@
       </c>
       <c r="B219" s="29" t="inlineStr">
         <is>
-          <t>LiuGong и Lonking: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
+          <t>Komatsu: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
         </is>
       </c>
       <c r="C219" s="29" t="inlineStr">
         <is>
-          <t>автопогрузчик lonking fd15t</t>
+          <t>вилочный погрузчик komatsu fd25t 17</t>
         </is>
       </c>
       <c r="D219" s="28" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E219" s="28" t="n">
         <v>11</v>
@@ -6272,16 +6642,16 @@
       </c>
       <c r="B220" s="29" t="inlineStr">
         <is>
-          <t>LiuGong и Lonking: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
+          <t>Komatsu: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
         </is>
       </c>
       <c r="C220" s="29" t="inlineStr">
         <is>
-          <t>lonking lg25dt вилочный погрузчик</t>
+          <t>запчасти на вилочный погрузчик komatsu</t>
         </is>
       </c>
       <c r="D220" s="28" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E220" s="28" t="n">
         <v>12</v>
@@ -6293,16 +6663,16 @@
       </c>
       <c r="B221" s="29" t="inlineStr">
         <is>
-          <t>Nissan, Mitsubishi, TCM: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
+          <t>Львовский погрузчик: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
         </is>
       </c>
       <c r="C221" s="29" t="inlineStr">
         <is>
-          <t>вилочный погрузчик tcm</t>
+          <t>вилочный погрузчик львовский погрузчик</t>
         </is>
       </c>
       <c r="D221" s="28" t="n">
-        <v>39</v>
+        <v>95</v>
       </c>
       <c r="E221" s="28" t="n">
         <v>1</v>
@@ -6314,16 +6684,16 @@
       </c>
       <c r="B222" s="29" t="inlineStr">
         <is>
-          <t>Nissan, Mitsubishi, TCM: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
+          <t>Львовский погрузчик: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
         </is>
       </c>
       <c r="C222" s="29" t="inlineStr">
         <is>
-          <t>погрузчик вилочный ниссан</t>
+          <t>львовский автопогрузчик</t>
         </is>
       </c>
       <c r="D222" s="28" t="n">
-        <v>24</v>
+        <v>59</v>
       </c>
       <c r="E222" s="28" t="n">
         <v>2</v>
@@ -6335,16 +6705,16 @@
       </c>
       <c r="B223" s="29" t="inlineStr">
         <is>
-          <t>Nissan, Mitsubishi, TCM: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
+          <t>Львовский погрузчик: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
         </is>
       </c>
       <c r="C223" s="29" t="inlineStr">
         <is>
-          <t>погрузчик вилочный nissan</t>
+          <t>погрузчик вилочный львовский</t>
         </is>
       </c>
       <c r="D223" s="28" t="n">
-        <v>14</v>
+        <v>50</v>
       </c>
       <c r="E223" s="28" t="n">
         <v>3</v>
@@ -6356,16 +6726,16 @@
       </c>
       <c r="B224" s="29" t="inlineStr">
         <is>
-          <t>Nissan, Mitsubishi, TCM: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
+          <t>Львовский погрузчик: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
         </is>
       </c>
       <c r="C224" s="29" t="inlineStr">
         <is>
-          <t>mitsubishi вилочный погрузчик</t>
+          <t>львовский автопогрузчик 5 тонн</t>
         </is>
       </c>
       <c r="D224" s="28" t="n">
-        <v>13</v>
+        <v>48</v>
       </c>
       <c r="E224" s="28" t="n">
         <v>4</v>
@@ -6377,16 +6747,16 @@
       </c>
       <c r="B225" s="29" t="inlineStr">
         <is>
-          <t>Nissan, Mitsubishi, TCM: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
+          <t>Львовский погрузчик: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
         </is>
       </c>
       <c r="C225" s="29" t="inlineStr">
         <is>
-          <t>погрузчик вилочный mitsubishi fd15nt</t>
+          <t>погрузчик вилочный львовский завод</t>
         </is>
       </c>
       <c r="D225" s="28" t="n">
-        <v>7</v>
+        <v>36</v>
       </c>
       <c r="E225" s="28" t="n">
         <v>5</v>
@@ -6398,16 +6768,16 @@
       </c>
       <c r="B226" s="29" t="inlineStr">
         <is>
-          <t>Nissan, Mitsubishi, TCM: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
+          <t>Львовский погрузчик: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
         </is>
       </c>
       <c r="C226" s="29" t="inlineStr">
         <is>
-          <t>погрузчик вилочный tcm fd50t9</t>
+          <t>вилочный погрузчик львовский купить</t>
         </is>
       </c>
       <c r="D226" s="28" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E226" s="28" t="n">
         <v>6</v>
@@ -6419,16 +6789,16 @@
       </c>
       <c r="B227" s="29" t="inlineStr">
         <is>
-          <t>Nissan, Mitsubishi, TCM: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
+          <t>Львовский погрузчик: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
         </is>
       </c>
       <c r="C227" s="29" t="inlineStr">
         <is>
-          <t>автопогрузчик mitsubishi fd15nt</t>
+          <t>сколько весит погрузчик вилочный львовский</t>
         </is>
       </c>
       <c r="D227" s="28" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E227" s="28" t="n">
         <v>7</v>
@@ -6440,16 +6810,16 @@
       </c>
       <c r="B228" s="29" t="inlineStr">
         <is>
-          <t>Nissan, Mitsubishi, TCM: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
+          <t>Львовский погрузчик: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
         </is>
       </c>
       <c r="C228" s="29" t="inlineStr">
         <is>
-          <t>вилочный погрузчик мицубиси</t>
+          <t>вилочный погрузчик львовский 5т характеристики</t>
         </is>
       </c>
       <c r="D228" s="28" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E228" s="28" t="n">
         <v>8</v>
@@ -6461,16 +6831,16 @@
       </c>
       <c r="B229" s="29" t="inlineStr">
         <is>
-          <t>Nissan, Mitsubishi, TCM: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
+          <t>Львовский погрузчик: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
         </is>
       </c>
       <c r="C229" s="29" t="inlineStr">
         <is>
-          <t>запчасти на вилочный погрузчик ниссан</t>
+          <t>львовский вилочный погрузчик 5т</t>
         </is>
       </c>
       <c r="D229" s="28" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E229" s="28" t="n">
         <v>9</v>
@@ -6482,16 +6852,16 @@
       </c>
       <c r="B230" s="29" t="inlineStr">
         <is>
-          <t>Nissan, Mitsubishi, TCM: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
+          <t>Львовский погрузчик: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
         </is>
       </c>
       <c r="C230" s="29" t="inlineStr">
         <is>
-          <t>мицубиси автопогрузчик</t>
+          <t>купить вилочный погрузчик львовский бу на авито</t>
         </is>
       </c>
       <c r="D230" s="28" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E230" s="28" t="n">
         <v>10</v>
@@ -6503,16 +6873,16 @@
       </c>
       <c r="B231" s="29" t="inlineStr">
         <is>
-          <t>Nissan, Mitsubishi, TCM: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
+          <t>Львовский погрузчик: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
         </is>
       </c>
       <c r="C231" s="29" t="inlineStr">
         <is>
-          <t>панель приборов вилочного погрузчика ниссан</t>
+          <t>львовский погрузчик вилочный 5 тонн</t>
         </is>
       </c>
       <c r="D231" s="28" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E231" s="28" t="n">
         <v>11</v>
@@ -6524,16 +6894,16 @@
       </c>
       <c r="B232" s="29" t="inlineStr">
         <is>
-          <t>Nissan, Mitsubishi, TCM: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
+          <t>Львовский погрузчик: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
         </is>
       </c>
       <c r="C232" s="29" t="inlineStr">
         <is>
-          <t>вилочный погрузчик mitsubishi fd18nt</t>
+          <t>вилочный погрузчик львовский погрузчик лев ап 40814</t>
         </is>
       </c>
       <c r="D232" s="28" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E232" s="28" t="n">
         <v>12</v>
@@ -6545,16 +6915,16 @@
       </c>
       <c r="B233" s="29" t="inlineStr">
         <is>
-          <t>Hangcha: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
+          <t>JAC: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
         </is>
       </c>
       <c r="C233" s="29" t="inlineStr">
         <is>
-          <t>hangcha вилочный погрузчик</t>
+          <t>jac вилочный погрузчик</t>
         </is>
       </c>
       <c r="D233" s="28" t="n">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="E233" s="28" t="n">
         <v>1</v>
@@ -6566,16 +6936,16 @@
       </c>
       <c r="B234" s="29" t="inlineStr">
         <is>
-          <t>Hangcha: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
+          <t>JAC: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
         </is>
       </c>
       <c r="C234" s="29" t="inlineStr">
         <is>
-          <t>ханча погрузчик вилочный</t>
+          <t>джак погрузчик вилочный</t>
         </is>
       </c>
       <c r="D234" s="28" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E234" s="28" t="n">
         <v>2</v>
@@ -6587,12 +6957,12 @@
       </c>
       <c r="B235" s="29" t="inlineStr">
         <is>
-          <t>Hangcha: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
+          <t>JAC: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
         </is>
       </c>
       <c r="C235" s="29" t="inlineStr">
         <is>
-          <t>вилочный погрузчик hangcha купить</t>
+          <t>jac вилочный погрузчик купить</t>
         </is>
       </c>
       <c r="D235" s="28" t="n">
@@ -6608,16 +6978,16 @@
       </c>
       <c r="B236" s="29" t="inlineStr">
         <is>
-          <t>Hangcha: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
+          <t>JAC: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
         </is>
       </c>
       <c r="C236" s="29" t="inlineStr">
         <is>
-          <t>автопогрузчик hangcha</t>
+          <t>погрузчик вилочный 5 тонн jac</t>
         </is>
       </c>
       <c r="D236" s="28" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E236" s="28" t="n">
         <v>4</v>
@@ -6629,16 +6999,16 @@
       </c>
       <c r="B237" s="29" t="inlineStr">
         <is>
-          <t>Hangcha: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
+          <t>JAC: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
         </is>
       </c>
       <c r="C237" s="29" t="inlineStr">
         <is>
-          <t>вилочные погрузчики хангча</t>
+          <t>погрузчик вилочный jac 3 тонны</t>
         </is>
       </c>
       <c r="D237" s="28" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E237" s="28" t="n">
         <v>5</v>
@@ -6650,16 +7020,16 @@
       </c>
       <c r="B238" s="29" t="inlineStr">
         <is>
-          <t>Hangcha: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
+          <t>JAC: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
         </is>
       </c>
       <c r="C238" s="29" t="inlineStr">
         <is>
-          <t>hangcha cpd20</t>
+          <t>запчасти на вилочный погрузчик jac</t>
         </is>
       </c>
       <c r="D238" s="28" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E238" s="28" t="n">
         <v>6</v>
@@ -6671,16 +7041,16 @@
       </c>
       <c r="B239" s="29" t="inlineStr">
         <is>
-          <t>Hangcha: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
+          <t>JAC: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
         </is>
       </c>
       <c r="C239" s="29" t="inlineStr">
         <is>
-          <t>вилочный погрузчик hangcha отзывы</t>
+          <t>jac автопогрузчик</t>
         </is>
       </c>
       <c r="D239" s="28" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E239" s="28" t="n">
         <v>7</v>
@@ -6692,16 +7062,16 @@
       </c>
       <c r="B240" s="29" t="inlineStr">
         <is>
-          <t>Hangcha: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
+          <t>JAC: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
         </is>
       </c>
       <c r="C240" s="29" t="inlineStr">
         <is>
-          <t>погрузчик вилочный ханча купить</t>
+          <t>cpd20 jac</t>
         </is>
       </c>
       <c r="D240" s="28" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E240" s="28" t="n">
         <v>8</v>
@@ -6713,16 +7083,16 @@
       </c>
       <c r="B241" s="29" t="inlineStr">
         <is>
-          <t>Hangcha: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
+          <t>JAC: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
         </is>
       </c>
       <c r="C241" s="29" t="inlineStr">
         <is>
-          <t>ханча погрузчик вилочный отзывы владельцев</t>
+          <t>дизельный погрузчик вилочный jac</t>
         </is>
       </c>
       <c r="D241" s="28" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E241" s="28" t="n">
         <v>9</v>
@@ -6734,16 +7104,16 @@
       </c>
       <c r="B242" s="29" t="inlineStr">
         <is>
-          <t>Hangcha: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
+          <t>JAC: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
         </is>
       </c>
       <c r="C242" s="29" t="inlineStr">
         <is>
-          <t>запчасти вилочный погрузчик hangcha</t>
+          <t>jac вилочный погрузчик официальный сайт</t>
         </is>
       </c>
       <c r="D242" s="28" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E242" s="28" t="n">
         <v>10</v>
@@ -6755,16 +7125,16 @@
       </c>
       <c r="B243" s="29" t="inlineStr">
         <is>
-          <t>Hangcha: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
+          <t>JAC: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
         </is>
       </c>
       <c r="C243" s="29" t="inlineStr">
         <is>
-          <t>автопогрузчик с вилочным захватом hangcha</t>
+          <t>вилочный погрузчик jac cpd15</t>
         </is>
       </c>
       <c r="D243" s="28" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E243" s="28" t="n">
         <v>11</v>
@@ -6776,16 +7146,16 @@
       </c>
       <c r="B244" s="29" t="inlineStr">
         <is>
-          <t>Hangcha: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
+          <t>JAC: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
         </is>
       </c>
       <c r="C244" s="29" t="inlineStr">
         <is>
-          <t>hangcha cpd25</t>
+          <t>электропогрузчик jac cpd 16</t>
         </is>
       </c>
       <c r="D244" s="28" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E244" s="28" t="n">
         <v>12</v>
@@ -6797,16 +7167,16 @@
       </c>
       <c r="B245" s="29" t="inlineStr">
         <is>
-          <t>JAC: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
+          <t>Hangcha: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
         </is>
       </c>
       <c r="C245" s="29" t="inlineStr">
         <is>
-          <t>jac вилочный погрузчик</t>
+          <t>hangcha вилочный погрузчик</t>
         </is>
       </c>
       <c r="D245" s="28" t="n">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="E245" s="28" t="n">
         <v>1</v>
@@ -6818,16 +7188,16 @@
       </c>
       <c r="B246" s="29" t="inlineStr">
         <is>
-          <t>JAC: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
+          <t>Hangcha: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
         </is>
       </c>
       <c r="C246" s="29" t="inlineStr">
         <is>
-          <t>джак погрузчик вилочный</t>
+          <t>ханча погрузчик вилочный</t>
         </is>
       </c>
       <c r="D246" s="28" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="E246" s="28" t="n">
         <v>2</v>
@@ -6839,12 +7209,12 @@
       </c>
       <c r="B247" s="29" t="inlineStr">
         <is>
-          <t>JAC: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
+          <t>Hangcha: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
         </is>
       </c>
       <c r="C247" s="29" t="inlineStr">
         <is>
-          <t>jac вилочный погрузчик купить</t>
+          <t>вилочный погрузчик hangcha купить</t>
         </is>
       </c>
       <c r="D247" s="28" t="n">
@@ -6860,16 +7230,16 @@
       </c>
       <c r="B248" s="29" t="inlineStr">
         <is>
-          <t>JAC: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
+          <t>Hangcha: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
         </is>
       </c>
       <c r="C248" s="29" t="inlineStr">
         <is>
-          <t>запчасти на вилочный погрузчик jac</t>
+          <t>автопогрузчик hangcha</t>
         </is>
       </c>
       <c r="D248" s="28" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E248" s="28" t="n">
         <v>4</v>
@@ -6881,16 +7251,16 @@
       </c>
       <c r="B249" s="29" t="inlineStr">
         <is>
-          <t>JAC: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
+          <t>Hangcha: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
         </is>
       </c>
       <c r="C249" s="29" t="inlineStr">
         <is>
-          <t>jac автопогрузчик</t>
+          <t>вилочные погрузчики хангча</t>
         </is>
       </c>
       <c r="D249" s="28" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E249" s="28" t="n">
         <v>5</v>
@@ -6902,12 +7272,12 @@
       </c>
       <c r="B250" s="29" t="inlineStr">
         <is>
-          <t>JAC: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
+          <t>Hangcha: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
         </is>
       </c>
       <c r="C250" s="29" t="inlineStr">
         <is>
-          <t>cpd20 jac</t>
+          <t>hangcha cpd20</t>
         </is>
       </c>
       <c r="D250" s="28" t="n">
@@ -6923,12 +7293,12 @@
       </c>
       <c r="B251" s="29" t="inlineStr">
         <is>
-          <t>JAC: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
+          <t>Hangcha: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
         </is>
       </c>
       <c r="C251" s="29" t="inlineStr">
         <is>
-          <t>jac вилочный погрузчик официальный сайт</t>
+          <t>вилочный погрузчик hangcha отзывы</t>
         </is>
       </c>
       <c r="D251" s="28" t="n">
@@ -6944,16 +7314,16 @@
       </c>
       <c r="B252" s="29" t="inlineStr">
         <is>
-          <t>JAC: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
+          <t>Hangcha: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
         </is>
       </c>
       <c r="C252" s="29" t="inlineStr">
         <is>
-          <t>вилочный погрузчик jac cpd15</t>
+          <t>погрузчик вилочный ханча купить</t>
         </is>
       </c>
       <c r="D252" s="28" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E252" s="28" t="n">
         <v>8</v>
@@ -6965,16 +7335,16 @@
       </c>
       <c r="B253" s="29" t="inlineStr">
         <is>
-          <t>JAC: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
+          <t>Hangcha: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
         </is>
       </c>
       <c r="C253" s="29" t="inlineStr">
         <is>
-          <t>вилочный погрузчик jac h35</t>
+          <t>ханча погрузчик вилочный отзывы владельцев</t>
         </is>
       </c>
       <c r="D253" s="28" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E253" s="28" t="n">
         <v>9</v>
@@ -6986,12 +7356,12 @@
       </c>
       <c r="B254" s="29" t="inlineStr">
         <is>
-          <t>JAC: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
+          <t>Hangcha: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
         </is>
       </c>
       <c r="C254" s="29" t="inlineStr">
         <is>
-          <t>лобовое стекло на вилочный погрузчик jac</t>
+          <t>запчасти вилочный погрузчик hangcha</t>
         </is>
       </c>
       <c r="D254" s="28" t="n">
@@ -7007,16 +7377,16 @@
       </c>
       <c r="B255" s="29" t="inlineStr">
         <is>
-          <t>JAC: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
+          <t>Hangcha: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
         </is>
       </c>
       <c r="C255" s="29" t="inlineStr">
         <is>
-          <t>jac cpd15</t>
+          <t>вилочный погрузчик ханча 3 тонны</t>
         </is>
       </c>
       <c r="D255" s="28" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E255" s="28" t="n">
         <v>11</v>
@@ -7028,16 +7398,16 @@
       </c>
       <c r="B256" s="29" t="inlineStr">
         <is>
-          <t>JAC: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
+          <t>Hangcha: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
         </is>
       </c>
       <c r="C256" s="29" t="inlineStr">
         <is>
-          <t>вилочный погрузчик jac запчасти</t>
+          <t>автопогрузчик с вилочным захватом hangcha</t>
         </is>
       </c>
       <c r="D256" s="28" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E256" s="28" t="n">
         <v>12</v>
@@ -7049,16 +7419,16 @@
       </c>
       <c r="B257" s="29" t="inlineStr">
         <is>
-          <t>Manitou, Kalmar, Zoomlion, Shantui: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
+          <t>LiuGong: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
         </is>
       </c>
       <c r="C257" s="29" t="inlineStr">
         <is>
-          <t>автопогрузчик кальмар</t>
+          <t>liugong погрузчик вилочный</t>
         </is>
       </c>
       <c r="D257" s="28" t="n">
-        <v>67</v>
+        <v>52</v>
       </c>
       <c r="E257" s="28" t="n">
         <v>1</v>
@@ -7070,16 +7440,16 @@
       </c>
       <c r="B258" s="29" t="inlineStr">
         <is>
-          <t>Manitou, Kalmar, Zoomlion, Shantui: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
+          <t>LiuGong: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
         </is>
       </c>
       <c r="C258" s="29" t="inlineStr">
         <is>
-          <t>zoomlion вилочный погрузчик</t>
+          <t>автопогрузчик лиугонг</t>
         </is>
       </c>
       <c r="D258" s="28" t="n">
-        <v>62</v>
+        <v>8</v>
       </c>
       <c r="E258" s="28" t="n">
         <v>2</v>
@@ -7091,16 +7461,16 @@
       </c>
       <c r="B259" s="29" t="inlineStr">
         <is>
-          <t>Manitou, Kalmar, Zoomlion, Shantui: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
+          <t>LiuGong: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
         </is>
       </c>
       <c r="C259" s="29" t="inlineStr">
         <is>
-          <t>вилочный погрузчик маниту</t>
+          <t>автопогрузчик liugong</t>
         </is>
       </c>
       <c r="D259" s="28" t="n">
-        <v>55</v>
+        <v>6</v>
       </c>
       <c r="E259" s="28" t="n">
         <v>3</v>
@@ -7112,16 +7482,16 @@
       </c>
       <c r="B260" s="29" t="inlineStr">
         <is>
-          <t>Manitou, Kalmar, Zoomlion, Shantui: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
+          <t>LiuGong: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
         </is>
       </c>
       <c r="C260" s="29" t="inlineStr">
         <is>
-          <t>зумлион погрузчик вилочный</t>
+          <t>liugong cpd15</t>
         </is>
       </c>
       <c r="D260" s="28" t="n">
-        <v>43</v>
+        <v>2</v>
       </c>
       <c r="E260" s="28" t="n">
         <v>4</v>
@@ -7133,16 +7503,16 @@
       </c>
       <c r="B261" s="29" t="inlineStr">
         <is>
-          <t>Manitou, Kalmar, Zoomlion, Shantui: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
+          <t>LiuGong: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
         </is>
       </c>
       <c r="C261" s="29" t="inlineStr">
         <is>
-          <t>shann погрузчик вилочный</t>
+          <t>лиугонг погрузчик вилочный</t>
         </is>
       </c>
       <c r="D261" s="28" t="n">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="E261" s="28" t="n">
         <v>5</v>
@@ -7154,16 +7524,16 @@
       </c>
       <c r="B262" s="29" t="inlineStr">
         <is>
-          <t>Manitou, Kalmar, Zoomlion, Shantui: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
+          <t>LiuGong: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
         </is>
       </c>
       <c r="C262" s="29" t="inlineStr">
         <is>
-          <t>кальмар погрузчик вилочный</t>
+          <t>вилочный погрузчик liugong clg2050h</t>
         </is>
       </c>
       <c r="D262" s="28" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="E262" s="28" t="n">
         <v>6</v>
@@ -7175,16 +7545,16 @@
       </c>
       <c r="B263" s="29" t="inlineStr">
         <is>
-          <t>Manitou, Kalmar, Zoomlion, Shantui: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
+          <t>LiuGong: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
         </is>
       </c>
       <c r="C263" s="29" t="inlineStr">
         <is>
-          <t>погрузчик вилочный zoomlion fd30</t>
+          <t>вилочный погрузчик liugong clg2100h</t>
         </is>
       </c>
       <c r="D263" s="28" t="n">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="E263" s="28" t="n">
         <v>7</v>
@@ -7196,16 +7566,16 @@
       </c>
       <c r="B264" s="29" t="inlineStr">
         <is>
-          <t>Manitou, Kalmar, Zoomlion, Shantui: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
+          <t>LiuGong: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
         </is>
       </c>
       <c r="C264" s="29" t="inlineStr">
         <is>
-          <t>вилочный погрузчик zoomlion fd25</t>
+          <t>погрузчик вилочный liugong цена</t>
         </is>
       </c>
       <c r="D264" s="28" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="E264" s="28" t="n">
         <v>8</v>
@@ -7217,16 +7587,16 @@
       </c>
       <c r="B265" s="29" t="inlineStr">
         <is>
-          <t>Manitou, Kalmar, Zoomlion, Shantui: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
+          <t>LiuGong: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
         </is>
       </c>
       <c r="C265" s="29" t="inlineStr">
         <is>
-          <t>вилочный погрузчик zoomlion fd35</t>
+          <t>вилочный погрузчик liugong 50</t>
         </is>
       </c>
       <c r="D265" s="28" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="E265" s="28" t="n">
         <v>9</v>
@@ -7238,16 +7608,16 @@
       </c>
       <c r="B266" s="29" t="inlineStr">
         <is>
-          <t>Manitou, Kalmar, Zoomlion, Shantui: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
+          <t>LiuGong: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
         </is>
       </c>
       <c r="C266" s="29" t="inlineStr">
         <is>
-          <t>zoomlion вилочный погрузчик купить</t>
+          <t>погрузчик вилочный liugong купить</t>
         </is>
       </c>
       <c r="D266" s="28" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E266" s="28" t="n">
         <v>10</v>
@@ -7259,16 +7629,16 @@
       </c>
       <c r="B267" s="29" t="inlineStr">
         <is>
-          <t>Manitou, Kalmar, Zoomlion, Shantui: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
+          <t>LiuGong: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
         </is>
       </c>
       <c r="C267" s="29" t="inlineStr">
         <is>
-          <t>вилочный погрузчик zoomlion fd18</t>
+          <t>вилочный дизельный погрузчик liugong</t>
         </is>
       </c>
       <c r="D267" s="28" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E267" s="28" t="n">
         <v>11</v>
@@ -7280,16 +7650,16 @@
       </c>
       <c r="B268" s="29" t="inlineStr">
         <is>
-          <t>Manitou, Kalmar, Zoomlion, Shantui: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
+          <t>LiuGong: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
         </is>
       </c>
       <c r="C268" s="29" t="inlineStr">
         <is>
-          <t>вилочный погрузчик zoomlion fd15</t>
+          <t>вилочный погрузчик 3 тонны liugong</t>
         </is>
       </c>
       <c r="D268" s="28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E268" s="28" t="n">
         <v>12</v>
@@ -7301,16 +7671,16 @@
       </c>
       <c r="B269" s="29" t="inlineStr">
         <is>
-          <t>Погрузчик «кара»: что это за техника и чем она отличается от современных моделей</t>
+          <t>Lonking: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
         </is>
       </c>
       <c r="C269" s="29" t="inlineStr">
         <is>
-          <t>вилочный погрузчик кара</t>
+          <t>погрузчик вилочный lonking</t>
         </is>
       </c>
       <c r="D269" s="28" t="n">
-        <v>71</v>
+        <v>47</v>
       </c>
       <c r="E269" s="28" t="n">
         <v>1</v>
@@ -7322,16 +7692,16 @@
       </c>
       <c r="B270" s="29" t="inlineStr">
         <is>
-          <t>Погрузчик «кара»: что это за техника и чем она отличается от современных моделей</t>
+          <t>Lonking: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
         </is>
       </c>
       <c r="C270" s="29" t="inlineStr">
         <is>
-          <t>автопогрузчик кара</t>
+          <t>вилочный погрузчик лонкинг</t>
         </is>
       </c>
       <c r="D270" s="28" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="E270" s="28" t="n">
         <v>2</v>
@@ -7343,16 +7713,16 @@
       </c>
       <c r="B271" s="29" t="inlineStr">
         <is>
-          <t>Погрузчик «кара»: что это за техника и чем она отличается от современных моделей</t>
+          <t>Lonking: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
         </is>
       </c>
       <c r="C271" s="29" t="inlineStr">
         <is>
-          <t>почему погрузчик называют кара вилочный</t>
+          <t>погрузчик вилочный lonking lg30dt</t>
         </is>
       </c>
       <c r="D271" s="28" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E271" s="28" t="n">
         <v>3</v>
@@ -7364,12 +7734,12 @@
       </c>
       <c r="B272" s="29" t="inlineStr">
         <is>
-          <t>Погрузчик «кара»: что это за техника и чем она отличается от современных моделей</t>
+          <t>Lonking: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
         </is>
       </c>
       <c r="C272" s="29" t="inlineStr">
         <is>
-          <t>вилочный погрузчик кара бу купить</t>
+          <t>вилочный погрузчик lonking lg50dt</t>
         </is>
       </c>
       <c r="D272" s="28" t="n">
@@ -7385,16 +7755,16 @@
       </c>
       <c r="B273" s="29" t="inlineStr">
         <is>
-          <t>Погрузчик «кара»: что это за техника и чем она отличается от современных моделей</t>
+          <t>Lonking: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
         </is>
       </c>
       <c r="C273" s="29" t="inlineStr">
         <is>
-          <t>кара вилочный погрузчик фото</t>
+          <t>вилочный погрузчик lonking fd20t</t>
         </is>
       </c>
       <c r="D273" s="28" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="E273" s="28" t="n">
         <v>5</v>
@@ -7406,16 +7776,16 @@
       </c>
       <c r="B274" s="29" t="inlineStr">
         <is>
-          <t>Погрузчик «кара»: что это за техника и чем она отличается от современных моделей</t>
+          <t>Lonking: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
         </is>
       </c>
       <c r="C274" s="29" t="inlineStr">
         <is>
-          <t>вилочный погрузчик кара купить</t>
+          <t>погрузчик вилочный lonking fd15t</t>
         </is>
       </c>
       <c r="D274" s="28" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="E274" s="28" t="n">
         <v>6</v>
@@ -7427,16 +7797,16 @@
       </c>
       <c r="B275" s="29" t="inlineStr">
         <is>
-          <t>Погрузчик «кара»: что это за техника и чем она отличается от современных моделей</t>
+          <t>Lonking: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
         </is>
       </c>
       <c r="C275" s="29" t="inlineStr">
         <is>
-          <t>вилочный погрузчик бу кара</t>
+          <t>лонкинг 3 тонны вилочный погрузчик</t>
         </is>
       </c>
       <c r="D275" s="28" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="E275" s="28" t="n">
         <v>7</v>
@@ -7448,16 +7818,16 @@
       </c>
       <c r="B276" s="29" t="inlineStr">
         <is>
-          <t>Погрузчик «кара»: что это за техника и чем она отличается от современных моделей</t>
+          <t>Lonking: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
         </is>
       </c>
       <c r="C276" s="29" t="inlineStr">
         <is>
-          <t>кара и вилочный погрузчик</t>
+          <t>вилочный погрузчик lonking lg35dt</t>
         </is>
       </c>
       <c r="D276" s="28" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E276" s="28" t="n">
         <v>8</v>
@@ -7469,16 +7839,16 @@
       </c>
       <c r="B277" s="29" t="inlineStr">
         <is>
-          <t>Погрузчик «кара»: что это за техника и чем она отличается от современных моделей</t>
+          <t>Lonking: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
         </is>
       </c>
       <c r="C277" s="29" t="inlineStr">
         <is>
-          <t>автопогрузчик вилочный кара</t>
+          <t>вилочный погрузчик lonking fd35t</t>
         </is>
       </c>
       <c r="D277" s="28" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E277" s="28" t="n">
         <v>9</v>
@@ -7490,16 +7860,16 @@
       </c>
       <c r="B278" s="29" t="inlineStr">
         <is>
-          <t>Погрузчик «кара»: что это за техника и чем она отличается от современных моделей</t>
+          <t>Lonking: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
         </is>
       </c>
       <c r="C278" s="29" t="inlineStr">
         <is>
-          <t>вилочный погрузчик кара характеристики</t>
+          <t>автопогрузчик lonking fd15t</t>
         </is>
       </c>
       <c r="D278" s="28" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E278" s="28" t="n">
         <v>10</v>
@@ -7511,16 +7881,16 @@
       </c>
       <c r="B279" s="29" t="inlineStr">
         <is>
-          <t>Погрузчик «кара»: что это за техника и чем она отличается от современных моделей</t>
+          <t>Lonking: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
         </is>
       </c>
       <c r="C279" s="29" t="inlineStr">
         <is>
-          <t>кара вилочный погрузчик аренда</t>
+          <t>lonking lg25dt вилочный погрузчик</t>
         </is>
       </c>
       <c r="D279" s="28" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E279" s="28" t="n">
         <v>11</v>
@@ -7532,16 +7902,16 @@
       </c>
       <c r="B280" s="29" t="inlineStr">
         <is>
-          <t>Погрузчик «кара»: что это за техника и чем она отличается от современных моделей</t>
+          <t>Lonking: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
         </is>
       </c>
       <c r="C280" s="29" t="inlineStr">
         <is>
-          <t>кара автопогрузчик авито</t>
+          <t>купить вилочный погрузчик лонкинг</t>
         </is>
       </c>
       <c r="D280" s="28" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E280" s="28" t="n">
         <v>12</v>
@@ -7553,16 +7923,16 @@
       </c>
       <c r="B281" s="29" t="inlineStr">
         <is>
-          <t>Навесное оборудование для вилочного погрузчика: какое бывает и зачем</t>
+          <t>Zoomlion: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
         </is>
       </c>
       <c r="C281" s="29" t="inlineStr">
         <is>
-          <t>удлинители вил для вилочного погрузчика</t>
+          <t>zoomlion вилочный погрузчик</t>
         </is>
       </c>
       <c r="D281" s="28" t="n">
-        <v>81</v>
+        <v>62</v>
       </c>
       <c r="E281" s="28" t="n">
         <v>1</v>
@@ -7574,16 +7944,16 @@
       </c>
       <c r="B282" s="29" t="inlineStr">
         <is>
-          <t>Навесное оборудование для вилочного погрузчика: какое бывает и зачем</t>
+          <t>Zoomlion: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
         </is>
       </c>
       <c r="C282" s="29" t="inlineStr">
         <is>
-          <t>ковш для вилочного погрузчика</t>
+          <t>зумлион погрузчик вилочный</t>
         </is>
       </c>
       <c r="D282" s="28" t="n">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="E282" s="28" t="n">
         <v>2</v>
@@ -7595,16 +7965,16 @@
       </c>
       <c r="B283" s="29" t="inlineStr">
         <is>
-          <t>Навесное оборудование для вилочного погрузчика: какое бывает и зачем</t>
+          <t>Zoomlion: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
         </is>
       </c>
       <c r="C283" s="29" t="inlineStr">
         <is>
-          <t>навесное оборудование на вилочный погрузчик</t>
+          <t>погрузчик вилочный zoomlion fd30</t>
         </is>
       </c>
       <c r="D283" s="28" t="n">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="E283" s="28" t="n">
         <v>3</v>
@@ -7616,16 +7986,16 @@
       </c>
       <c r="B284" s="29" t="inlineStr">
         <is>
-          <t>Навесное оборудование для вилочного погрузчика: какое бывает и зачем</t>
+          <t>Zoomlion: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
         </is>
       </c>
       <c r="C284" s="29" t="inlineStr">
         <is>
-          <t>монтажная платформа для вилочного погрузчика</t>
+          <t>вилочный погрузчик zoomlion fd25</t>
         </is>
       </c>
       <c r="D284" s="28" t="n">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="E284" s="28" t="n">
         <v>4</v>
@@ -7637,16 +8007,16 @@
       </c>
       <c r="B285" s="29" t="inlineStr">
         <is>
-          <t>Навесное оборудование для вилочного погрузчика: какое бывает и зачем</t>
+          <t>Zoomlion: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
         </is>
       </c>
       <c r="C285" s="29" t="inlineStr">
         <is>
-          <t>ротатор для вилочного погрузчика</t>
+          <t>вилочный погрузчик zoomlion fd35</t>
         </is>
       </c>
       <c r="D285" s="28" t="n">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="E285" s="28" t="n">
         <v>5</v>
@@ -7658,16 +8028,16 @@
       </c>
       <c r="B286" s="29" t="inlineStr">
         <is>
-          <t>Навесное оборудование для вилочного погрузчика: какое бывает и зачем</t>
+          <t>Zoomlion: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
         </is>
       </c>
       <c r="C286" s="29" t="inlineStr">
         <is>
-          <t>навесное оборудование для вилочного погрузчика</t>
+          <t>zoomlion вилочный погрузчик купить</t>
         </is>
       </c>
       <c r="D286" s="28" t="n">
-        <v>36</v>
+        <v>6</v>
       </c>
       <c r="E286" s="28" t="n">
         <v>6</v>
@@ -7679,16 +8049,16 @@
       </c>
       <c r="B287" s="29" t="inlineStr">
         <is>
-          <t>Навесное оборудование для вилочного погрузчика: какое бывает и зачем</t>
+          <t>Zoomlion: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
         </is>
       </c>
       <c r="C287" s="29" t="inlineStr">
         <is>
-          <t>удлинитель вил для вилочного погрузчика</t>
+          <t>вилочный погрузчик zoomlion fd18</t>
         </is>
       </c>
       <c r="D287" s="28" t="n">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="E287" s="28" t="n">
         <v>7</v>
@@ -7700,16 +8070,16 @@
       </c>
       <c r="B288" s="29" t="inlineStr">
         <is>
-          <t>Навесное оборудование для вилочного погрузчика: какое бывает и зачем</t>
+          <t>Zoomlion: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
         </is>
       </c>
       <c r="C288" s="29" t="inlineStr">
         <is>
-          <t>удлинитель для погрузчика вилочного</t>
+          <t>zoomlion вилочный погрузчик 3 тонны</t>
         </is>
       </c>
       <c r="D288" s="28" t="n">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="E288" s="28" t="n">
         <v>8</v>
@@ -7721,16 +8091,16 @@
       </c>
       <c r="B289" s="29" t="inlineStr">
         <is>
-          <t>Навесное оборудование для вилочного погрузчика: какое бывает и зачем</t>
+          <t>Zoomlion: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
         </is>
       </c>
       <c r="C289" s="29" t="inlineStr">
         <is>
-          <t>каретка вилочного погрузчика</t>
+          <t>вилочный дизельный погрузчик zoomlion fd30</t>
         </is>
       </c>
       <c r="D289" s="28" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="E289" s="28" t="n">
         <v>9</v>
@@ -7742,16 +8112,16 @@
       </c>
       <c r="B290" s="29" t="inlineStr">
         <is>
-          <t>Навесное оборудование для вилочного погрузчика: какое бывает и зачем</t>
+          <t>Zoomlion: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
         </is>
       </c>
       <c r="C290" s="29" t="inlineStr">
         <is>
-          <t>удлинители для вилочного погрузчика</t>
+          <t>вилочный погрузчик zoomlion fd15</t>
         </is>
       </c>
       <c r="D290" s="28" t="n">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="E290" s="28" t="n">
         <v>10</v>
@@ -7763,16 +8133,16 @@
       </c>
       <c r="B291" s="29" t="inlineStr">
         <is>
-          <t>Навесное оборудование для вилочного погрузчика: какое бывает и зачем</t>
+          <t>Zoomlion: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
         </is>
       </c>
       <c r="C291" s="29" t="inlineStr">
         <is>
-          <t>ковш для вилочного погрузчика ковш</t>
+          <t>купить погрузчик вилочный зумлион</t>
         </is>
       </c>
       <c r="D291" s="28" t="n">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="E291" s="28" t="n">
         <v>11</v>
@@ -7784,16 +8154,16 @@
       </c>
       <c r="B292" s="29" t="inlineStr">
         <is>
-          <t>Навесное оборудование для вилочного погрузчика: какое бывает и зачем</t>
+          <t>Zoomlion: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
         </is>
       </c>
       <c r="C292" s="29" t="inlineStr">
         <is>
-          <t>навесное оборудование для вилочных погрузчиков</t>
+          <t>вилочный погрузчик zoomlion fd18 отзывы</t>
         </is>
       </c>
       <c r="D292" s="28" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="E292" s="28" t="n">
         <v>12</v>
@@ -7805,16 +8175,16 @@
       </c>
       <c r="B293" s="29" t="inlineStr">
         <is>
-          <t>Запчасти для вилочного погрузчика: что изнашивается быстрее всего</t>
+          <t>Doosan: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
         </is>
       </c>
       <c r="C293" s="29" t="inlineStr">
         <is>
-          <t>запчасти для вилочных погрузчиков</t>
+          <t>doosan погрузчик вилочный</t>
         </is>
       </c>
       <c r="D293" s="28" t="n">
-        <v>98</v>
+        <v>39</v>
       </c>
       <c r="E293" s="28" t="n">
         <v>1</v>
@@ -7826,16 +8196,16 @@
       </c>
       <c r="B294" s="29" t="inlineStr">
         <is>
-          <t>Запчасти для вилочного погрузчика: что изнашивается быстрее всего</t>
+          <t>Doosan: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
         </is>
       </c>
       <c r="C294" s="29" t="inlineStr">
         <is>
-          <t>ремонт вилочного погрузчика</t>
+          <t>погрузчик дусан вилочный</t>
         </is>
       </c>
       <c r="D294" s="28" t="n">
-        <v>58</v>
+        <v>28</v>
       </c>
       <c r="E294" s="28" t="n">
         <v>2</v>
@@ -7847,16 +8217,16 @@
       </c>
       <c r="B295" s="29" t="inlineStr">
         <is>
-          <t>Запчасти для вилочного погрузчика: что изнашивается быстрее всего</t>
+          <t>Doosan: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
         </is>
       </c>
       <c r="C295" s="29" t="inlineStr">
         <is>
-          <t>ремонт вилочных погрузчиков</t>
+          <t>doosan вилочный погрузчик запчасти</t>
         </is>
       </c>
       <c r="D295" s="28" t="n">
-        <v>45</v>
+        <v>11</v>
       </c>
       <c r="E295" s="28" t="n">
         <v>3</v>
@@ -7868,16 +8238,16 @@
       </c>
       <c r="B296" s="29" t="inlineStr">
         <is>
-          <t>Запчасти для вилочного погрузчика: что изнашивается быстрее всего</t>
+          <t>Doosan: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
         </is>
       </c>
       <c r="C296" s="29" t="inlineStr">
         <is>
-          <t>мачта вилочного погрузчика</t>
+          <t>дусан погрузчик вилочный купить</t>
         </is>
       </c>
       <c r="D296" s="28" t="n">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="E296" s="28" t="n">
         <v>4</v>
@@ -7889,16 +8259,16 @@
       </c>
       <c r="B297" s="29" t="inlineStr">
         <is>
-          <t>Запчасти для вилочного погрузчика: что изнашивается быстрее всего</t>
+          <t>Doosan: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
         </is>
       </c>
       <c r="C297" s="29" t="inlineStr">
         <is>
-          <t>шины для вилочных погрузчиков</t>
+          <t>вилочный погрузчик doosan 7 тонн</t>
         </is>
       </c>
       <c r="D297" s="28" t="n">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="E297" s="28" t="n">
         <v>5</v>
@@ -7910,16 +8280,16 @@
       </c>
       <c r="B298" s="29" t="inlineStr">
         <is>
-          <t>Запчасти для вилочного погрузчика: что изнашивается быстрее всего</t>
+          <t>Doosan: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
         </is>
       </c>
       <c r="C298" s="29" t="inlineStr">
         <is>
-          <t>запчасти на вилочный погрузчик</t>
+          <t>новый вилочный погрузчик дусан</t>
         </is>
       </c>
       <c r="D298" s="28" t="n">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="E298" s="28" t="n">
         <v>6</v>
@@ -7931,16 +8301,16 @@
       </c>
       <c r="B299" s="29" t="inlineStr">
         <is>
-          <t>Запчасти для вилочного погрузчика: что изнашивается быстрее всего</t>
+          <t>Doosan: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
         </is>
       </c>
       <c r="C299" s="29" t="inlineStr">
         <is>
-          <t>запчасти для вилочного погрузчика</t>
+          <t>автопогрузчик doosan d30s 5</t>
         </is>
       </c>
       <c r="D299" s="28" t="n">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="E299" s="28" t="n">
         <v>7</v>
@@ -7952,16 +8322,16 @@
       </c>
       <c r="B300" s="29" t="inlineStr">
         <is>
-          <t>Запчасти для вилочного погрузчика: что изнашивается быстрее всего</t>
+          <t>Doosan: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
         </is>
       </c>
       <c r="C300" s="29" t="inlineStr">
         <is>
-          <t>гидроцилиндр погрузчика вилочного погрузчика</t>
+          <t>диагностика вилочного погрузчика doosan</t>
         </is>
       </c>
       <c r="D300" s="28" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="E300" s="28" t="n">
         <v>8</v>
@@ -7973,16 +8343,16 @@
       </c>
       <c r="B301" s="29" t="inlineStr">
         <is>
-          <t>Запчасти для вилочного погрузчика: что изнашивается быстрее всего</t>
+          <t>Doosan: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
         </is>
       </c>
       <c r="C301" s="29" t="inlineStr">
         <is>
-          <t>гидравлическое масло для погрузчика вилочного</t>
+          <t>погрузчик вилочный doosan купить</t>
         </is>
       </c>
       <c r="D301" s="28" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="E301" s="28" t="n">
         <v>9</v>
@@ -7994,16 +8364,16 @@
       </c>
       <c r="B302" s="29" t="inlineStr">
         <is>
-          <t>Запчасти для вилочного погрузчика: что изнашивается быстрее всего</t>
+          <t>Doosan: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
         </is>
       </c>
       <c r="C302" s="29" t="inlineStr">
         <is>
-          <t>сиденье для вилочного погрузчика</t>
+          <t>автопогрузчик doosan</t>
         </is>
       </c>
       <c r="D302" s="28" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="E302" s="28" t="n">
         <v>10</v>
@@ -8015,16 +8385,16 @@
       </c>
       <c r="B303" s="29" t="inlineStr">
         <is>
-          <t>Запчасти для вилочного погрузчика: что изнашивается быстрее всего</t>
+          <t>Doosan: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
         </is>
       </c>
       <c r="C303" s="29" t="inlineStr">
         <is>
-          <t>обслуживание и ремонт вилочных погрузчиков</t>
+          <t>автопогрузчик doosan d70s 5</t>
         </is>
       </c>
       <c r="D303" s="28" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="E303" s="28" t="n">
         <v>11</v>
@@ -8036,16 +8406,16 @@
       </c>
       <c r="B304" s="29" t="inlineStr">
         <is>
-          <t>Запчасти для вилочного погрузчика: что изнашивается быстрее всего</t>
+          <t>Doosan: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
         </is>
       </c>
       <c r="C304" s="29" t="inlineStr">
         <is>
-          <t>запчасти к вилочным погрузчикам</t>
+          <t>запчасти для вилочных погрузчиков doosan</t>
         </is>
       </c>
       <c r="D304" s="28" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="E304" s="28" t="n">
         <v>12</v>
@@ -8057,16 +8427,16 @@
       </c>
       <c r="B305" s="29" t="inlineStr">
         <is>
-          <t>Регистрация вилочного погрузчика в Гостехнадзоре: что нужно знать владельцу</t>
+          <t>Балканкар и «Кара»: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
         </is>
       </c>
       <c r="C305" s="29" t="inlineStr">
         <is>
-          <t>какие права нужны на вилочный погрузчик</t>
+          <t>балканкар погрузчик вилочный</t>
         </is>
       </c>
       <c r="D305" s="28" t="n">
-        <v>119</v>
+        <v>37</v>
       </c>
       <c r="E305" s="28" t="n">
         <v>1</v>
@@ -8078,16 +8448,16 @@
       </c>
       <c r="B306" s="29" t="inlineStr">
         <is>
-          <t>Регистрация вилочного погрузчика в Гостехнадзоре: что нужно знать владельцу</t>
+          <t>Балканкар и «Кара»: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
         </is>
       </c>
       <c r="C306" s="29" t="inlineStr">
         <is>
-          <t>к какой группе ос относится вилочный погрузчик</t>
+          <t>вилочный погрузчик балканкар бу купить</t>
         </is>
       </c>
       <c r="D306" s="28" t="n">
-        <v>70</v>
+        <v>13</v>
       </c>
       <c r="E306" s="28" t="n">
         <v>2</v>
@@ -8099,16 +8469,16 @@
       </c>
       <c r="B307" s="29" t="inlineStr">
         <is>
-          <t>Регистрация вилочного погрузчика в Гостехнадзоре: что нужно знать владельцу</t>
+          <t>Балканкар и «Кара»: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
         </is>
       </c>
       <c r="C307" s="29" t="inlineStr">
         <is>
-          <t>какие права нужны для вилочного погрузчика</t>
+          <t>запчасти на вилочный погрузчик балканкар</t>
         </is>
       </c>
       <c r="D307" s="28" t="n">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="E307" s="28" t="n">
         <v>3</v>
@@ -8120,16 +8490,16 @@
       </c>
       <c r="B308" s="29" t="inlineStr">
         <is>
-          <t>Регистрация вилочного погрузчика в Гостехнадзоре: что нужно знать владельцу</t>
+          <t>Балканкар и «Кара»: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
         </is>
       </c>
       <c r="C308" s="29" t="inlineStr">
         <is>
-          <t>как поставить на учет вилочный погрузчик</t>
+          <t>запчасти для вилочного погрузчика балканкар</t>
         </is>
       </c>
       <c r="D308" s="28" t="n">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="E308" s="28" t="n">
         <v>4</v>
@@ -8141,16 +8511,16 @@
       </c>
       <c r="B309" s="29" t="inlineStr">
         <is>
-          <t>Регистрация вилочного погрузчика в Гостехнадзоре: что нужно знать владельцу</t>
+          <t>Балканкар и «Кара»: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
         </is>
       </c>
       <c r="C309" s="29" t="inlineStr">
         <is>
-          <t>какие права нужны на кару вилочный погрузчик</t>
+          <t>стартер на вилочный погрузчик балканкар</t>
         </is>
       </c>
       <c r="D309" s="28" t="n">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="E309" s="28" t="n">
         <v>5</v>
@@ -8162,16 +8532,16 @@
       </c>
       <c r="B310" s="29" t="inlineStr">
         <is>
-          <t>Регистрация вилочного погрузчика в Гостехнадзоре: что нужно знать владельцу</t>
+          <t>Балканкар и «Кара»: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
         </is>
       </c>
       <c r="C310" s="29" t="inlineStr">
         <is>
-          <t>какие права нужны для управления погрузчиком вилочным</t>
+          <t>купить запчасти на вилочный погрузчик балканкар</t>
         </is>
       </c>
       <c r="D310" s="28" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="E310" s="28" t="n">
         <v>6</v>
@@ -8183,16 +8553,16 @@
       </c>
       <c r="B311" s="29" t="inlineStr">
         <is>
-          <t>Регистрация вилочного погрузчика в Гостехнадзоре: что нужно знать владельцу</t>
+          <t>Балканкар и «Кара»: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
         </is>
       </c>
       <c r="C311" s="29" t="inlineStr">
         <is>
-          <t>какие права нужны на вилочный погрузчик на складе</t>
+          <t>автопогрузчик балканкар</t>
         </is>
       </c>
       <c r="D311" s="28" t="n">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="E311" s="28" t="n">
         <v>7</v>
@@ -8204,16 +8574,16 @@
       </c>
       <c r="B312" s="29" t="inlineStr">
         <is>
-          <t>Регистрация вилочного погрузчика в Гостехнадзоре: что нужно знать владельцу</t>
+          <t>Балканкар и «Кара»: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
         </is>
       </c>
       <c r="C312" s="29" t="inlineStr">
         <is>
-          <t>как поставить вилочный погрузчик на учет в гостехнадзоре</t>
+          <t>вилочный погрузчик балканкар купить</t>
         </is>
       </c>
       <c r="D312" s="28" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E312" s="28" t="n">
         <v>8</v>
@@ -8225,16 +8595,16 @@
       </c>
       <c r="B313" s="29" t="inlineStr">
         <is>
-          <t>Регистрация вилочного погрузчика в Гостехнадзоре: что нужно знать владельцу</t>
+          <t>Балканкар и «Кара»: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
         </is>
       </c>
       <c r="C313" s="29" t="inlineStr">
         <is>
-          <t>нужно ли ставить на учет вилочный погрузчик</t>
+          <t>вилочный погрузчик балканкар дв 1792</t>
         </is>
       </c>
       <c r="D313" s="28" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E313" s="28" t="n">
         <v>9</v>
@@ -8246,16 +8616,16 @@
       </c>
       <c r="B314" s="29" t="inlineStr">
         <is>
-          <t>Регистрация вилочного погрузчика в Гостехнадзоре: что нужно знать владельцу</t>
+          <t>Балканкар и «Кара»: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
         </is>
       </c>
       <c r="C314" s="29" t="inlineStr">
         <is>
-          <t>вилочный погрузчик какие права нужны</t>
+          <t>погрузчик вилочный балканкар 5 тонн</t>
         </is>
       </c>
       <c r="D314" s="28" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E314" s="28" t="n">
         <v>10</v>
@@ -8267,16 +8637,16 @@
       </c>
       <c r="B315" s="29" t="inlineStr">
         <is>
-          <t>Регистрация вилочного погрузчика в Гостехнадзоре: что нужно знать владельцу</t>
+          <t>Балканкар и «Кара»: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
         </is>
       </c>
       <c r="C315" s="29" t="inlineStr">
         <is>
-          <t>постановка вилочного погрузчика на учет</t>
+          <t>балканкар вилочный погрузчик 1661</t>
         </is>
       </c>
       <c r="D315" s="28" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E315" s="28" t="n">
         <v>11</v>
@@ -8288,16 +8658,16 @@
       </c>
       <c r="B316" s="29" t="inlineStr">
         <is>
-          <t>Регистрация вилочного погрузчика в Гостехнадзоре: что нужно знать владельцу</t>
+          <t>Балканкар и «Кара»: вилочные погрузчики — модельный ряд и что учесть при покупке</t>
         </is>
       </c>
       <c r="C316" s="29" t="inlineStr">
         <is>
-          <t>какие права нужны на автопогрузчик</t>
+          <t>балканкар электрический вилочный погрузчик</t>
         </is>
       </c>
       <c r="D316" s="28" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E316" s="28" t="n">
         <v>12</v>
@@ -8309,16 +8679,16 @@
       </c>
       <c r="B317" s="29" t="inlineStr">
         <is>
-          <t>Аренда вилочного погрузчика: когда выгоднее покупки</t>
+          <t>Погрузчик «кара» без привязки к марке: что это за техника</t>
         </is>
       </c>
       <c r="C317" s="29" t="inlineStr">
         <is>
-          <t>аренда вилочного погрузчика</t>
+          <t>вилочный погрузчик кара</t>
         </is>
       </c>
       <c r="D317" s="28" t="n">
-        <v>270</v>
+        <v>71</v>
       </c>
       <c r="E317" s="28" t="n">
         <v>1</v>
@@ -8330,16 +8700,16 @@
       </c>
       <c r="B318" s="29" t="inlineStr">
         <is>
-          <t>Аренда вилочного погрузчика: когда выгоднее покупки</t>
+          <t>Погрузчик «кара» без привязки к марке: что это за техника</t>
         </is>
       </c>
       <c r="C318" s="29" t="inlineStr">
         <is>
-          <t>аренда погрузчика вилочного цена</t>
+          <t>автопогрузчик кара</t>
         </is>
       </c>
       <c r="D318" s="28" t="n">
-        <v>65</v>
+        <v>24</v>
       </c>
       <c r="E318" s="28" t="n">
         <v>2</v>
@@ -8351,16 +8721,16 @@
       </c>
       <c r="B319" s="29" t="inlineStr">
         <is>
-          <t>Аренда вилочного погрузчика: когда выгоднее покупки</t>
+          <t>Погрузчик «кара» без привязки к марке: что это за техника</t>
         </is>
       </c>
       <c r="C319" s="29" t="inlineStr">
         <is>
-          <t>погрузчик вилочный в аренду</t>
+          <t>почему погрузчик называют кара вилочный</t>
         </is>
       </c>
       <c r="D319" s="28" t="n">
-        <v>64</v>
+        <v>18</v>
       </c>
       <c r="E319" s="28" t="n">
         <v>3</v>
@@ -8372,16 +8742,16 @@
       </c>
       <c r="B320" s="29" t="inlineStr">
         <is>
-          <t>Аренда вилочного погрузчика: когда выгоднее покупки</t>
+          <t>Погрузчик «кара» без привязки к марке: что это за техника</t>
         </is>
       </c>
       <c r="C320" s="29" t="inlineStr">
         <is>
-          <t>аренда вилочных погрузчиков</t>
+          <t>вилочный погрузчик кара бу купить</t>
         </is>
       </c>
       <c r="D320" s="28" t="n">
-        <v>57</v>
+        <v>12</v>
       </c>
       <c r="E320" s="28" t="n">
         <v>4</v>
@@ -8393,16 +8763,16 @@
       </c>
       <c r="B321" s="29" t="inlineStr">
         <is>
-          <t>Аренда вилочного погрузчика: когда выгоднее покупки</t>
+          <t>Погрузчик «кара» без привязки к марке: что это за техника</t>
         </is>
       </c>
       <c r="C321" s="29" t="inlineStr">
         <is>
-          <t>аренда погрузчика вилочного в спб</t>
+          <t>кара вилочный погрузчик фото</t>
         </is>
       </c>
       <c r="D321" s="28" t="n">
-        <v>49</v>
+        <v>3</v>
       </c>
       <c r="E321" s="28" t="n">
         <v>5</v>
@@ -8414,16 +8784,16 @@
       </c>
       <c r="B322" s="29" t="inlineStr">
         <is>
-          <t>Аренда вилочного погрузчика: когда выгоднее покупки</t>
+          <t>Погрузчик «кара» без привязки к марке: что это за техника</t>
         </is>
       </c>
       <c r="C322" s="29" t="inlineStr">
         <is>
-          <t>аренда вилочного погрузчика спб</t>
+          <t>вилочный погрузчик кара купить</t>
         </is>
       </c>
       <c r="D322" s="28" t="n">
-        <v>44</v>
+        <v>3</v>
       </c>
       <c r="E322" s="28" t="n">
         <v>6</v>
@@ -8435,16 +8805,16 @@
       </c>
       <c r="B323" s="29" t="inlineStr">
         <is>
-          <t>Аренда вилочного погрузчика: когда выгоднее покупки</t>
+          <t>Погрузчик «кара» без привязки к марке: что это за техника</t>
         </is>
       </c>
       <c r="C323" s="29" t="inlineStr">
         <is>
-          <t>аренда погрузчика вилочного москва</t>
+          <t>вилочный погрузчик бу кара</t>
         </is>
       </c>
       <c r="D323" s="28" t="n">
-        <v>42</v>
+        <v>2</v>
       </c>
       <c r="E323" s="28" t="n">
         <v>7</v>
@@ -8456,16 +8826,16 @@
       </c>
       <c r="B324" s="29" t="inlineStr">
         <is>
-          <t>Аренда вилочного погрузчика: когда выгоднее покупки</t>
+          <t>Погрузчик «кара» без привязки к марке: что это за техника</t>
         </is>
       </c>
       <c r="C324" s="29" t="inlineStr">
         <is>
-          <t>аренда вилочных погрузчиков в москве и московской области</t>
+          <t>кара и вилочный погрузчик</t>
         </is>
       </c>
       <c r="D324" s="28" t="n">
-        <v>35</v>
+        <v>2</v>
       </c>
       <c r="E324" s="28" t="n">
         <v>8</v>
@@ -8477,16 +8847,16 @@
       </c>
       <c r="B325" s="29" t="inlineStr">
         <is>
-          <t>Аренда вилочного погрузчика: когда выгоднее покупки</t>
+          <t>Погрузчик «кара» без привязки к марке: что это за техника</t>
         </is>
       </c>
       <c r="C325" s="29" t="inlineStr">
         <is>
-          <t>аренда вилочных погрузчиков в москве</t>
+          <t>вилочный погрузчик это кара</t>
         </is>
       </c>
       <c r="D325" s="28" t="n">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="E325" s="28" t="n">
         <v>9</v>
@@ -8498,16 +8868,16 @@
       </c>
       <c r="B326" s="29" t="inlineStr">
         <is>
-          <t>Аренда вилочного погрузчика: когда выгоднее покупки</t>
+          <t>Погрузчик «кара» без привязки к марке: что это за техника</t>
         </is>
       </c>
       <c r="C326" s="29" t="inlineStr">
         <is>
-          <t>аренда вилочного погрузчика с оператором</t>
+          <t>автопогрузчик вилочный кара</t>
         </is>
       </c>
       <c r="D326" s="28" t="n">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="E326" s="28" t="n">
         <v>10</v>
@@ -8519,16 +8889,16 @@
       </c>
       <c r="B327" s="29" t="inlineStr">
         <is>
-          <t>Аренда вилочного погрузчика: когда выгоднее покупки</t>
+          <t>Погрузчик «кара» без привязки к марке: что это за техника</t>
         </is>
       </c>
       <c r="C327" s="29" t="inlineStr">
         <is>
-          <t>аренда вилочного погрузчика в новосибирске</t>
+          <t>вилочный погрузчик кара характеристики</t>
         </is>
       </c>
       <c r="D327" s="28" t="n">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="E327" s="28" t="n">
         <v>11</v>
@@ -8540,18 +8910,2538 @@
       </c>
       <c r="B328" s="29" t="inlineStr">
         <is>
+          <t>Погрузчик «кара» без привязки к марке: что это за техника</t>
+        </is>
+      </c>
+      <c r="C328" s="29" t="inlineStr">
+        <is>
+          <t>погрузчик кара вилочный дизельный</t>
+        </is>
+      </c>
+      <c r="D328" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="E328" s="28" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" s="28" t="n">
+        <v>28</v>
+      </c>
+      <c r="B329" s="29" t="inlineStr">
+        <is>
+          <t>ТВЭКС и Амкодор: вилочные погрузчики российского и белорусского производства</t>
+        </is>
+      </c>
+      <c r="C329" s="29" t="inlineStr">
+        <is>
+          <t>вилочный погрузчик твэкс вп 05 купить</t>
+        </is>
+      </c>
+      <c r="D329" s="28" t="n">
+        <v>55</v>
+      </c>
+      <c r="E329" s="28" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" s="28" t="n">
+        <v>28</v>
+      </c>
+      <c r="B330" s="29" t="inlineStr">
+        <is>
+          <t>ТВЭКС и Амкодор: вилочные погрузчики российского и белорусского производства</t>
+        </is>
+      </c>
+      <c r="C330" s="29" t="inlineStr">
+        <is>
+          <t>амкодор вилочный погрузчик</t>
+        </is>
+      </c>
+      <c r="D330" s="28" t="n">
+        <v>48</v>
+      </c>
+      <c r="E330" s="28" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" s="28" t="n">
+        <v>28</v>
+      </c>
+      <c r="B331" s="29" t="inlineStr">
+        <is>
+          <t>ТВЭКС и Амкодор: вилочные погрузчики российского и белорусского производства</t>
+        </is>
+      </c>
+      <c r="C331" s="29" t="inlineStr">
+        <is>
+          <t>вп 05 твэкс вилочный погрузчик</t>
+        </is>
+      </c>
+      <c r="D331" s="28" t="n">
+        <v>18</v>
+      </c>
+      <c r="E331" s="28" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" s="28" t="n">
+        <v>28</v>
+      </c>
+      <c r="B332" s="29" t="inlineStr">
+        <is>
+          <t>ТВЭКС и Амкодор: вилочные погрузчики российского и белорусского производства</t>
+        </is>
+      </c>
+      <c r="C332" s="29" t="inlineStr">
+        <is>
+          <t>погрузчик вилочный амкодор 451а</t>
+        </is>
+      </c>
+      <c r="D332" s="28" t="n">
+        <v>10</v>
+      </c>
+      <c r="E332" s="28" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" s="28" t="n">
+        <v>28</v>
+      </c>
+      <c r="B333" s="29" t="inlineStr">
+        <is>
+          <t>ТВЭКС и Амкодор: вилочные погрузчики российского и белорусского производства</t>
+        </is>
+      </c>
+      <c r="C333" s="29" t="inlineStr">
+        <is>
+          <t>погрузчик твэкс вилочный</t>
+        </is>
+      </c>
+      <c r="D333" s="28" t="n">
+        <v>10</v>
+      </c>
+      <c r="E333" s="28" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" s="28" t="n">
+        <v>28</v>
+      </c>
+      <c r="B334" s="29" t="inlineStr">
+        <is>
+          <t>ТВЭКС и Амкодор: вилочные погрузчики российского и белорусского производства</t>
+        </is>
+      </c>
+      <c r="C334" s="29" t="inlineStr">
+        <is>
+          <t>вилочный автопогрузчик амкодор 451а</t>
+        </is>
+      </c>
+      <c r="D334" s="28" t="n">
+        <v>5</v>
+      </c>
+      <c r="E334" s="28" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" s="28" t="n">
+        <v>28</v>
+      </c>
+      <c r="B335" s="29" t="inlineStr">
+        <is>
+          <t>ТВЭКС и Амкодор: вилочные погрузчики российского и белорусского производства</t>
+        </is>
+      </c>
+      <c r="C335" s="29" t="inlineStr">
+        <is>
+          <t>амкодор автопогрузчик</t>
+        </is>
+      </c>
+      <c r="D335" s="28" t="n">
+        <v>4</v>
+      </c>
+      <c r="E335" s="28" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" s="28" t="n">
+        <v>28</v>
+      </c>
+      <c r="B336" s="29" t="inlineStr">
+        <is>
+          <t>ТВЭКС и Амкодор: вилочные погрузчики российского и белорусского производства</t>
+        </is>
+      </c>
+      <c r="C336" s="29" t="inlineStr">
+        <is>
+          <t>вилочный погрузчик твэкс вп 05 запчасти</t>
+        </is>
+      </c>
+      <c r="D336" s="28" t="n">
+        <v>4</v>
+      </c>
+      <c r="E336" s="28" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" s="28" t="n">
+        <v>28</v>
+      </c>
+      <c r="B337" s="29" t="inlineStr">
+        <is>
+          <t>ТВЭКС и Амкодор: вилочные погрузчики российского и белорусского производства</t>
+        </is>
+      </c>
+      <c r="C337" s="29" t="inlineStr">
+        <is>
+          <t>вилочный погрузчик твэкс вп 05 купить бу</t>
+        </is>
+      </c>
+      <c r="D337" s="28" t="n">
+        <v>4</v>
+      </c>
+      <c r="E337" s="28" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" s="28" t="n">
+        <v>28</v>
+      </c>
+      <c r="B338" s="29" t="inlineStr">
+        <is>
+          <t>ТВЭКС и Амкодор: вилочные погрузчики российского и белорусского производства</t>
+        </is>
+      </c>
+      <c r="C338" s="29" t="inlineStr">
+        <is>
+          <t>вилочный погрузчик твэкс вп 05 купить новый</t>
+        </is>
+      </c>
+      <c r="D338" s="28" t="n">
+        <v>4</v>
+      </c>
+      <c r="E338" s="28" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" s="28" t="n">
+        <v>28</v>
+      </c>
+      <c r="B339" s="29" t="inlineStr">
+        <is>
+          <t>ТВЭКС и Амкодор: вилочные погрузчики российского и белорусского производства</t>
+        </is>
+      </c>
+      <c r="C339" s="29" t="inlineStr">
+        <is>
+          <t>вилочный погрузчик твэкс вп 05 технические характеристики</t>
+        </is>
+      </c>
+      <c r="D339" s="28" t="n">
+        <v>4</v>
+      </c>
+      <c r="E339" s="28" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" s="28" t="n">
+        <v>28</v>
+      </c>
+      <c r="B340" s="29" t="inlineStr">
+        <is>
+          <t>ТВЭКС и Амкодор: вилочные погрузчики российского и белорусского производства</t>
+        </is>
+      </c>
+      <c r="C340" s="29" t="inlineStr">
+        <is>
+          <t>погрузчик вилочный твэкс 5 тонн</t>
+        </is>
+      </c>
+      <c r="D340" s="28" t="n">
+        <v>3</v>
+      </c>
+      <c r="E340" s="28" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" s="28" t="n">
+        <v>29</v>
+      </c>
+      <c r="B341" s="29" t="inlineStr">
+        <is>
+          <t>Советские и постсоветские вилочные погрузчики: обзор марок</t>
+        </is>
+      </c>
+      <c r="C341" s="29" t="inlineStr">
+        <is>
+          <t>погрузчик вилочный советский</t>
+        </is>
+      </c>
+      <c r="D341" s="28" t="n">
+        <v>76</v>
+      </c>
+      <c r="E341" s="28" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" s="28" t="n">
+        <v>29</v>
+      </c>
+      <c r="B342" s="29" t="inlineStr">
+        <is>
+          <t>Советские и постсоветские вилочные погрузчики: обзор марок</t>
+        </is>
+      </c>
+      <c r="C342" s="29" t="inlineStr">
+        <is>
+          <t>погрузчик вилочный ссср</t>
+        </is>
+      </c>
+      <c r="D342" s="28" t="n">
+        <v>39</v>
+      </c>
+      <c r="E342" s="28" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" s="28" t="n">
+        <v>29</v>
+      </c>
+      <c r="B343" s="29" t="inlineStr">
+        <is>
+          <t>Советские и постсоветские вилочные погрузчики: обзор марок</t>
+        </is>
+      </c>
+      <c r="C343" s="29" t="inlineStr">
+        <is>
+          <t>советские вилочные погрузчики</t>
+        </is>
+      </c>
+      <c r="D343" s="28" t="n">
+        <v>8</v>
+      </c>
+      <c r="E343" s="28" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" s="28" t="n">
+        <v>29</v>
+      </c>
+      <c r="B344" s="29" t="inlineStr">
+        <is>
+          <t>Советские и постсоветские вилочные погрузчики: обзор марок</t>
+        </is>
+      </c>
+      <c r="C344" s="29" t="inlineStr">
+        <is>
+          <t>ссср погрузчик вилочный погрузчик</t>
+        </is>
+      </c>
+      <c r="D344" s="28" t="n">
+        <v>7</v>
+      </c>
+      <c r="E344" s="28" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" s="28" t="n">
+        <v>29</v>
+      </c>
+      <c r="B345" s="29" t="inlineStr">
+        <is>
+          <t>Советские и постсоветские вилочные погрузчики: обзор марок</t>
+        </is>
+      </c>
+      <c r="C345" s="29" t="inlineStr">
+        <is>
+          <t>автопогрузчики ссср</t>
+        </is>
+      </c>
+      <c r="D345" s="28" t="n">
+        <v>6</v>
+      </c>
+      <c r="E345" s="28" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" s="28" t="n">
+        <v>29</v>
+      </c>
+      <c r="B346" s="29" t="inlineStr">
+        <is>
+          <t>Советские и постсоветские вилочные погрузчики: обзор марок</t>
+        </is>
+      </c>
+      <c r="C346" s="29" t="inlineStr">
+        <is>
+          <t>советские автопогрузчики</t>
+        </is>
+      </c>
+      <c r="D346" s="28" t="n">
+        <v>6</v>
+      </c>
+      <c r="E346" s="28" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" s="28" t="n">
+        <v>29</v>
+      </c>
+      <c r="B347" s="29" t="inlineStr">
+        <is>
+          <t>Советские и постсоветские вилочные погрузчики: обзор марок</t>
+        </is>
+      </c>
+      <c r="C347" s="29" t="inlineStr">
+        <is>
+          <t>вилочный погрузчик ссср 5 тонн</t>
+        </is>
+      </c>
+      <c r="D347" s="28" t="n">
+        <v>5</v>
+      </c>
+      <c r="E347" s="28" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" s="28" t="n">
+        <v>29</v>
+      </c>
+      <c r="B348" s="29" t="inlineStr">
+        <is>
+          <t>Советские и постсоветские вилочные погрузчики: обзор марок</t>
+        </is>
+      </c>
+      <c r="C348" s="29" t="inlineStr">
+        <is>
+          <t>электропогрузчик ссср вилочный</t>
+        </is>
+      </c>
+      <c r="D348" s="28" t="n">
+        <v>3</v>
+      </c>
+      <c r="E348" s="28" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" s="28" t="n">
+        <v>29</v>
+      </c>
+      <c r="B349" s="29" t="inlineStr">
+        <is>
+          <t>Советские и постсоветские вилочные погрузчики: обзор марок</t>
+        </is>
+      </c>
+      <c r="C349" s="29" t="inlineStr">
+        <is>
+          <t>советский автопогрузчик</t>
+        </is>
+      </c>
+      <c r="D349" s="28" t="n">
+        <v>2</v>
+      </c>
+      <c r="E349" s="28" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" s="28" t="n">
+        <v>29</v>
+      </c>
+      <c r="B350" s="29" t="inlineStr">
+        <is>
+          <t>Советские и постсоветские вилочные погрузчики: обзор марок</t>
+        </is>
+      </c>
+      <c r="C350" s="29" t="inlineStr">
+        <is>
+          <t>вилочный погрузчик в ссср</t>
+        </is>
+      </c>
+      <c r="D350" s="28" t="n">
+        <v>2</v>
+      </c>
+      <c r="E350" s="28" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" s="28" t="n">
+        <v>29</v>
+      </c>
+      <c r="B351" s="29" t="inlineStr">
+        <is>
+          <t>Советские и постсоветские вилочные погрузчики: обзор марок</t>
+        </is>
+      </c>
+      <c r="C351" s="29" t="inlineStr">
+        <is>
+          <t>советский вилочный автопогрузчик</t>
+        </is>
+      </c>
+      <c r="D351" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="E351" s="28" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" s="28" t="n">
+        <v>29</v>
+      </c>
+      <c r="B352" s="29" t="inlineStr">
+        <is>
+          <t>Советские и постсоветские вилочные погрузчики: обзор марок</t>
+        </is>
+      </c>
+      <c r="C352" s="29" t="inlineStr">
+        <is>
+          <t>погрузчик вилочный ссср модель</t>
+        </is>
+      </c>
+      <c r="D352" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="E352" s="28" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" s="28" t="n">
+        <v>30</v>
+      </c>
+      <c r="B353" s="29" t="inlineStr">
+        <is>
+          <t>Nissan, Mitsubishi, TCM, Manitou, Kalmar, Shantui: редкие бренды на вторичном рынке</t>
+        </is>
+      </c>
+      <c r="C353" s="29" t="inlineStr">
+        <is>
+          <t>автопогрузчик кальмар</t>
+        </is>
+      </c>
+      <c r="D353" s="28" t="n">
+        <v>67</v>
+      </c>
+      <c r="E353" s="28" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" s="28" t="n">
+        <v>30</v>
+      </c>
+      <c r="B354" s="29" t="inlineStr">
+        <is>
+          <t>Nissan, Mitsubishi, TCM, Manitou, Kalmar, Shantui: редкие бренды на вторичном рынке</t>
+        </is>
+      </c>
+      <c r="C354" s="29" t="inlineStr">
+        <is>
+          <t>вилочный погрузчик маниту</t>
+        </is>
+      </c>
+      <c r="D354" s="28" t="n">
+        <v>55</v>
+      </c>
+      <c r="E354" s="28" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" s="28" t="n">
+        <v>30</v>
+      </c>
+      <c r="B355" s="29" t="inlineStr">
+        <is>
+          <t>Nissan, Mitsubishi, TCM, Manitou, Kalmar, Shantui: редкие бренды на вторичном рынке</t>
+        </is>
+      </c>
+      <c r="C355" s="29" t="inlineStr">
+        <is>
+          <t>shann погрузчик вилочный</t>
+        </is>
+      </c>
+      <c r="D355" s="28" t="n">
+        <v>41</v>
+      </c>
+      <c r="E355" s="28" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" s="28" t="n">
+        <v>30</v>
+      </c>
+      <c r="B356" s="29" t="inlineStr">
+        <is>
+          <t>Nissan, Mitsubishi, TCM, Manitou, Kalmar, Shantui: редкие бренды на вторичном рынке</t>
+        </is>
+      </c>
+      <c r="C356" s="29" t="inlineStr">
+        <is>
+          <t>вилочный погрузчик tcm</t>
+        </is>
+      </c>
+      <c r="D356" s="28" t="n">
+        <v>39</v>
+      </c>
+      <c r="E356" s="28" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" s="28" t="n">
+        <v>30</v>
+      </c>
+      <c r="B357" s="29" t="inlineStr">
+        <is>
+          <t>Nissan, Mitsubishi, TCM, Manitou, Kalmar, Shantui: редкие бренды на вторичном рынке</t>
+        </is>
+      </c>
+      <c r="C357" s="29" t="inlineStr">
+        <is>
+          <t>кальмар погрузчик вилочный</t>
+        </is>
+      </c>
+      <c r="D357" s="28" t="n">
+        <v>26</v>
+      </c>
+      <c r="E357" s="28" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" s="28" t="n">
+        <v>30</v>
+      </c>
+      <c r="B358" s="29" t="inlineStr">
+        <is>
+          <t>Nissan, Mitsubishi, TCM, Manitou, Kalmar, Shantui: редкие бренды на вторичном рынке</t>
+        </is>
+      </c>
+      <c r="C358" s="29" t="inlineStr">
+        <is>
+          <t>погрузчик вилочный ниссан</t>
+        </is>
+      </c>
+      <c r="D358" s="28" t="n">
+        <v>24</v>
+      </c>
+      <c r="E358" s="28" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" s="28" t="n">
+        <v>30</v>
+      </c>
+      <c r="B359" s="29" t="inlineStr">
+        <is>
+          <t>Nissan, Mitsubishi, TCM, Manitou, Kalmar, Shantui: редкие бренды на вторичном рынке</t>
+        </is>
+      </c>
+      <c r="C359" s="29" t="inlineStr">
+        <is>
+          <t>погрузчик вилочный nissan</t>
+        </is>
+      </c>
+      <c r="D359" s="28" t="n">
+        <v>14</v>
+      </c>
+      <c r="E359" s="28" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" s="28" t="n">
+        <v>30</v>
+      </c>
+      <c r="B360" s="29" t="inlineStr">
+        <is>
+          <t>Nissan, Mitsubishi, TCM, Manitou, Kalmar, Shantui: редкие бренды на вторичном рынке</t>
+        </is>
+      </c>
+      <c r="C360" s="29" t="inlineStr">
+        <is>
+          <t>mitsubishi вилочный погрузчик</t>
+        </is>
+      </c>
+      <c r="D360" s="28" t="n">
+        <v>13</v>
+      </c>
+      <c r="E360" s="28" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" s="28" t="n">
+        <v>30</v>
+      </c>
+      <c r="B361" s="29" t="inlineStr">
+        <is>
+          <t>Nissan, Mitsubishi, TCM, Manitou, Kalmar, Shantui: редкие бренды на вторичном рынке</t>
+        </is>
+      </c>
+      <c r="C361" s="29" t="inlineStr">
+        <is>
+          <t>погрузчик вилочный mitsubishi fd15nt</t>
+        </is>
+      </c>
+      <c r="D361" s="28" t="n">
+        <v>7</v>
+      </c>
+      <c r="E361" s="28" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" s="28" t="n">
+        <v>30</v>
+      </c>
+      <c r="B362" s="29" t="inlineStr">
+        <is>
+          <t>Nissan, Mitsubishi, TCM, Manitou, Kalmar, Shantui: редкие бренды на вторичном рынке</t>
+        </is>
+      </c>
+      <c r="C362" s="29" t="inlineStr">
+        <is>
+          <t>погрузчик вилочный tcm fd50t9</t>
+        </is>
+      </c>
+      <c r="D362" s="28" t="n">
+        <v>7</v>
+      </c>
+      <c r="E362" s="28" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" s="28" t="n">
+        <v>30</v>
+      </c>
+      <c r="B363" s="29" t="inlineStr">
+        <is>
+          <t>Nissan, Mitsubishi, TCM, Manitou, Kalmar, Shantui: редкие бренды на вторичном рынке</t>
+        </is>
+      </c>
+      <c r="C363" s="29" t="inlineStr">
+        <is>
+          <t>автопогрузчик mitsubishi fd15nt</t>
+        </is>
+      </c>
+      <c r="D363" s="28" t="n">
+        <v>7</v>
+      </c>
+      <c r="E363" s="28" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" s="28" t="n">
+        <v>30</v>
+      </c>
+      <c r="B364" s="29" t="inlineStr">
+        <is>
+          <t>Nissan, Mitsubishi, TCM, Manitou, Kalmar, Shantui: редкие бренды на вторичном рынке</t>
+        </is>
+      </c>
+      <c r="C364" s="29" t="inlineStr">
+        <is>
+          <t>вилочный погрузчик мицубиси</t>
+        </is>
+      </c>
+      <c r="D364" s="28" t="n">
+        <v>7</v>
+      </c>
+      <c r="E364" s="28" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" s="28" t="n">
+        <v>31</v>
+      </c>
+      <c r="B365" s="29" t="inlineStr">
+        <is>
+          <t>Still, Linde, Jungheinrich, Yale, Hyster, Clark: европейские бренды на вторичном рынке</t>
+        </is>
+      </c>
+      <c r="C365" s="29" t="inlineStr">
+        <is>
+          <t>hyster погрузчик вилочный</t>
+        </is>
+      </c>
+      <c r="D365" s="28" t="n">
+        <v>24</v>
+      </c>
+      <c r="E365" s="28" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" s="28" t="n">
+        <v>31</v>
+      </c>
+      <c r="B366" s="29" t="inlineStr">
+        <is>
+          <t>Still, Linde, Jungheinrich, Yale, Hyster, Clark: европейские бренды на вторичном рынке</t>
+        </is>
+      </c>
+      <c r="C366" s="29" t="inlineStr">
+        <is>
+          <t>jungheinrich вилочный погрузчик</t>
+        </is>
+      </c>
+      <c r="D366" s="28" t="n">
+        <v>20</v>
+      </c>
+      <c r="E366" s="28" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" s="28" t="n">
+        <v>31</v>
+      </c>
+      <c r="B367" s="29" t="inlineStr">
+        <is>
+          <t>Still, Linde, Jungheinrich, Yale, Hyster, Clark: европейские бренды на вторичном рынке</t>
+        </is>
+      </c>
+      <c r="C367" s="29" t="inlineStr">
+        <is>
+          <t>вилочный погрузчик still</t>
+        </is>
+      </c>
+      <c r="D367" s="28" t="n">
+        <v>18</v>
+      </c>
+      <c r="E367" s="28" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" s="28" t="n">
+        <v>31</v>
+      </c>
+      <c r="B368" s="29" t="inlineStr">
+        <is>
+          <t>Still, Linde, Jungheinrich, Yale, Hyster, Clark: европейские бренды на вторичном рынке</t>
+        </is>
+      </c>
+      <c r="C368" s="29" t="inlineStr">
+        <is>
+          <t>погрузчик yale вилочный</t>
+        </is>
+      </c>
+      <c r="D368" s="28" t="n">
+        <v>16</v>
+      </c>
+      <c r="E368" s="28" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" s="28" t="n">
+        <v>31</v>
+      </c>
+      <c r="B369" s="29" t="inlineStr">
+        <is>
+          <t>Still, Linde, Jungheinrich, Yale, Hyster, Clark: европейские бренды на вторичном рынке</t>
+        </is>
+      </c>
+      <c r="C369" s="29" t="inlineStr">
+        <is>
+          <t>вилочный погрузчик юнгхайнрих</t>
+        </is>
+      </c>
+      <c r="D369" s="28" t="n">
+        <v>15</v>
+      </c>
+      <c r="E369" s="28" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" s="28" t="n">
+        <v>31</v>
+      </c>
+      <c r="B370" s="29" t="inlineStr">
+        <is>
+          <t>Still, Linde, Jungheinrich, Yale, Hyster, Clark: европейские бренды на вторичном рынке</t>
+        </is>
+      </c>
+      <c r="C370" s="29" t="inlineStr">
+        <is>
+          <t>вилочный погрузчик linde</t>
+        </is>
+      </c>
+      <c r="D370" s="28" t="n">
+        <v>13</v>
+      </c>
+      <c r="E370" s="28" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" s="28" t="n">
+        <v>31</v>
+      </c>
+      <c r="B371" s="29" t="inlineStr">
+        <is>
+          <t>Still, Linde, Jungheinrich, Yale, Hyster, Clark: европейские бренды на вторичном рынке</t>
+        </is>
+      </c>
+      <c r="C371" s="29" t="inlineStr">
+        <is>
+          <t>вилочный погрузчик linde h30d</t>
+        </is>
+      </c>
+      <c r="D371" s="28" t="n">
+        <v>13</v>
+      </c>
+      <c r="E371" s="28" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" s="28" t="n">
+        <v>31</v>
+      </c>
+      <c r="B372" s="29" t="inlineStr">
+        <is>
+          <t>Still, Linde, Jungheinrich, Yale, Hyster, Clark: европейские бренды на вторичном рынке</t>
+        </is>
+      </c>
+      <c r="C372" s="29" t="inlineStr">
+        <is>
+          <t>автопогрузчик yale</t>
+        </is>
+      </c>
+      <c r="D372" s="28" t="n">
+        <v>11</v>
+      </c>
+      <c r="E372" s="28" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" s="28" t="n">
+        <v>31</v>
+      </c>
+      <c r="B373" s="29" t="inlineStr">
+        <is>
+          <t>Still, Linde, Jungheinrich, Yale, Hyster, Clark: европейские бренды на вторичном рынке</t>
+        </is>
+      </c>
+      <c r="C373" s="29" t="inlineStr">
+        <is>
+          <t>вилочный электрический погрузчик jungheinrich</t>
+        </is>
+      </c>
+      <c r="D373" s="28" t="n">
+        <v>10</v>
+      </c>
+      <c r="E373" s="28" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" s="28" t="n">
+        <v>31</v>
+      </c>
+      <c r="B374" s="29" t="inlineStr">
+        <is>
+          <t>Still, Linde, Jungheinrich, Yale, Hyster, Clark: европейские бренды на вторичном рынке</t>
+        </is>
+      </c>
+      <c r="C374" s="29" t="inlineStr">
+        <is>
+          <t>погрузчик вилочный jungheinrich dfg 320</t>
+        </is>
+      </c>
+      <c r="D374" s="28" t="n">
+        <v>10</v>
+      </c>
+      <c r="E374" s="28" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" s="28" t="n">
+        <v>31</v>
+      </c>
+      <c r="B375" s="29" t="inlineStr">
+        <is>
+          <t>Still, Linde, Jungheinrich, Yale, Hyster, Clark: европейские бренды на вторичном рынке</t>
+        </is>
+      </c>
+      <c r="C375" s="29" t="inlineStr">
+        <is>
+          <t>погрузчик вилочный кларк</t>
+        </is>
+      </c>
+      <c r="D375" s="28" t="n">
+        <v>9</v>
+      </c>
+      <c r="E375" s="28" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" s="28" t="n">
+        <v>31</v>
+      </c>
+      <c r="B376" s="29" t="inlineStr">
+        <is>
+          <t>Still, Linde, Jungheinrich, Yale, Hyster, Clark: европейские бренды на вторичном рынке</t>
+        </is>
+      </c>
+      <c r="C376" s="29" t="inlineStr">
+        <is>
+          <t>погрузчик вилочный still rx 60 25</t>
+        </is>
+      </c>
+      <c r="D376" s="28" t="n">
+        <v>6</v>
+      </c>
+      <c r="E376" s="28" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" s="28" t="n">
+        <v>32</v>
+      </c>
+      <c r="B377" s="29" t="inlineStr">
+        <is>
+          <t>Навесное оборудование для вилочного погрузчика: какое бывает и зачем</t>
+        </is>
+      </c>
+      <c r="C377" s="29" t="inlineStr">
+        <is>
+          <t>щетка на вилочный погрузчик</t>
+        </is>
+      </c>
+      <c r="D377" s="28" t="n">
+        <v>131</v>
+      </c>
+      <c r="E377" s="28" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" s="28" t="n">
+        <v>32</v>
+      </c>
+      <c r="B378" s="29" t="inlineStr">
+        <is>
+          <t>Навесное оборудование для вилочного погрузчика: какое бывает и зачем</t>
+        </is>
+      </c>
+      <c r="C378" s="29" t="inlineStr">
+        <is>
+          <t>удлинители вил для вилочного погрузчика</t>
+        </is>
+      </c>
+      <c r="D378" s="28" t="n">
+        <v>81</v>
+      </c>
+      <c r="E378" s="28" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" s="28" t="n">
+        <v>32</v>
+      </c>
+      <c r="B379" s="29" t="inlineStr">
+        <is>
+          <t>Навесное оборудование для вилочного погрузчика: какое бывает и зачем</t>
+        </is>
+      </c>
+      <c r="C379" s="29" t="inlineStr">
+        <is>
+          <t>ковш на вилочный погрузчик</t>
+        </is>
+      </c>
+      <c r="D379" s="28" t="n">
+        <v>72</v>
+      </c>
+      <c r="E379" s="28" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" s="28" t="n">
+        <v>32</v>
+      </c>
+      <c r="B380" s="29" t="inlineStr">
+        <is>
+          <t>Навесное оборудование для вилочного погрузчика: какое бывает и зачем</t>
+        </is>
+      </c>
+      <c r="C380" s="29" t="inlineStr">
+        <is>
+          <t>отвал на вилочный погрузчик</t>
+        </is>
+      </c>
+      <c r="D380" s="28" t="n">
+        <v>59</v>
+      </c>
+      <c r="E380" s="28" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" s="28" t="n">
+        <v>32</v>
+      </c>
+      <c r="B381" s="29" t="inlineStr">
+        <is>
+          <t>Навесное оборудование для вилочного погрузчика: какое бывает и зачем</t>
+        </is>
+      </c>
+      <c r="C381" s="29" t="inlineStr">
+        <is>
+          <t>ковш для вилочного погрузчика</t>
+        </is>
+      </c>
+      <c r="D381" s="28" t="n">
+        <v>48</v>
+      </c>
+      <c r="E381" s="28" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" s="28" t="n">
+        <v>32</v>
+      </c>
+      <c r="B382" s="29" t="inlineStr">
+        <is>
+          <t>Навесное оборудование для вилочного погрузчика: какое бывает и зачем</t>
+        </is>
+      </c>
+      <c r="C382" s="29" t="inlineStr">
+        <is>
+          <t>навесное оборудование на вилочный погрузчик</t>
+        </is>
+      </c>
+      <c r="D382" s="28" t="n">
+        <v>44</v>
+      </c>
+      <c r="E382" s="28" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" s="28" t="n">
+        <v>32</v>
+      </c>
+      <c r="B383" s="29" t="inlineStr">
+        <is>
+          <t>Навесное оборудование для вилочного погрузчика: какое бывает и зачем</t>
+        </is>
+      </c>
+      <c r="C383" s="29" t="inlineStr">
+        <is>
+          <t>монтажная платформа для вилочного погрузчика</t>
+        </is>
+      </c>
+      <c r="D383" s="28" t="n">
+        <v>43</v>
+      </c>
+      <c r="E383" s="28" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" s="28" t="n">
+        <v>32</v>
+      </c>
+      <c r="B384" s="29" t="inlineStr">
+        <is>
+          <t>Навесное оборудование для вилочного погрузчика: какое бывает и зачем</t>
+        </is>
+      </c>
+      <c r="C384" s="29" t="inlineStr">
+        <is>
+          <t>ротатор на вилочный погрузчик</t>
+        </is>
+      </c>
+      <c r="D384" s="28" t="n">
+        <v>37</v>
+      </c>
+      <c r="E384" s="28" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" s="28" t="n">
+        <v>32</v>
+      </c>
+      <c r="B385" s="29" t="inlineStr">
+        <is>
+          <t>Навесное оборудование для вилочного погрузчика: какое бывает и зачем</t>
+        </is>
+      </c>
+      <c r="C385" s="29" t="inlineStr">
+        <is>
+          <t>ротатор для вилочного погрузчика</t>
+        </is>
+      </c>
+      <c r="D385" s="28" t="n">
+        <v>36</v>
+      </c>
+      <c r="E385" s="28" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" s="28" t="n">
+        <v>32</v>
+      </c>
+      <c r="B386" s="29" t="inlineStr">
+        <is>
+          <t>Навесное оборудование для вилочного погрузчика: какое бывает и зачем</t>
+        </is>
+      </c>
+      <c r="C386" s="29" t="inlineStr">
+        <is>
+          <t>навесное оборудование для вилочного погрузчика</t>
+        </is>
+      </c>
+      <c r="D386" s="28" t="n">
+        <v>36</v>
+      </c>
+      <c r="E386" s="28" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" s="28" t="n">
+        <v>32</v>
+      </c>
+      <c r="B387" s="29" t="inlineStr">
+        <is>
+          <t>Навесное оборудование для вилочного погрузчика: какое бывает и зачем</t>
+        </is>
+      </c>
+      <c r="C387" s="29" t="inlineStr">
+        <is>
+          <t>удлинитель вил для вилочного погрузчика</t>
+        </is>
+      </c>
+      <c r="D387" s="28" t="n">
+        <v>30</v>
+      </c>
+      <c r="E387" s="28" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" s="28" t="n">
+        <v>32</v>
+      </c>
+      <c r="B388" s="29" t="inlineStr">
+        <is>
+          <t>Навесное оборудование для вилочного погрузчика: какое бывает и зачем</t>
+        </is>
+      </c>
+      <c r="C388" s="29" t="inlineStr">
+        <is>
+          <t>удлинитель для погрузчика вилочного</t>
+        </is>
+      </c>
+      <c r="D388" s="28" t="n">
+        <v>28</v>
+      </c>
+      <c r="E388" s="28" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" s="28" t="n">
+        <v>33</v>
+      </c>
+      <c r="B389" s="29" t="inlineStr">
+        <is>
+          <t>Шины для вилочного погрузчика: какие бывают и как выбрать</t>
+        </is>
+      </c>
+      <c r="C389" s="29" t="inlineStr">
+        <is>
+          <t>шины для вилочных погрузчиков</t>
+        </is>
+      </c>
+      <c r="D389" s="28" t="n">
+        <v>32</v>
+      </c>
+      <c r="E389" s="28" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" s="28" t="n">
+        <v>33</v>
+      </c>
+      <c r="B390" s="29" t="inlineStr">
+        <is>
+          <t>Шины для вилочного погрузчика: какие бывают и как выбрать</t>
+        </is>
+      </c>
+      <c r="C390" s="29" t="inlineStr">
+        <is>
+          <t>шины на кару вилочный погрузчик</t>
+        </is>
+      </c>
+      <c r="D390" s="28" t="n">
+        <v>20</v>
+      </c>
+      <c r="E390" s="28" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" s="28" t="n">
+        <v>33</v>
+      </c>
+      <c r="B391" s="29" t="inlineStr">
+        <is>
+          <t>Шины для вилочного погрузчика: какие бывают и как выбрать</t>
+        </is>
+      </c>
+      <c r="C391" s="29" t="inlineStr">
+        <is>
+          <t>шины на вилочный погрузчик</t>
+        </is>
+      </c>
+      <c r="D391" s="28" t="n">
+        <v>19</v>
+      </c>
+      <c r="E391" s="28" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" s="28" t="n">
+        <v>33</v>
+      </c>
+      <c r="B392" s="29" t="inlineStr">
+        <is>
+          <t>Шины для вилочного погрузчика: какие бывают и как выбрать</t>
+        </is>
+      </c>
+      <c r="C392" s="29" t="inlineStr">
+        <is>
+          <t>цельнолитые шины для вилочных погрузчиков</t>
+        </is>
+      </c>
+      <c r="D392" s="28" t="n">
+        <v>16</v>
+      </c>
+      <c r="E392" s="28" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" s="28" t="n">
+        <v>33</v>
+      </c>
+      <c r="B393" s="29" t="inlineStr">
+        <is>
+          <t>Шины для вилочного погрузчика: какие бывают и как выбрать</t>
+        </is>
+      </c>
+      <c r="C393" s="29" t="inlineStr">
+        <is>
+          <t>шины для вилочного погрузчика</t>
+        </is>
+      </c>
+      <c r="D393" s="28" t="n">
+        <v>13</v>
+      </c>
+      <c r="E393" s="28" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" s="28" t="n">
+        <v>33</v>
+      </c>
+      <c r="B394" s="29" t="inlineStr">
+        <is>
+          <t>Шины для вилочного погрузчика: какие бывают и как выбрать</t>
+        </is>
+      </c>
+      <c r="C394" s="29" t="inlineStr">
+        <is>
+          <t>каким приспособлением должны быть оснащены автомашины и автопогрузчики при работе с опасными грузами</t>
+        </is>
+      </c>
+      <c r="D394" s="28" t="n">
+        <v>11</v>
+      </c>
+      <c r="E394" s="28" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" s="28" t="n">
+        <v>33</v>
+      </c>
+      <c r="B395" s="29" t="inlineStr">
+        <is>
+          <t>Шины для вилочного погрузчика: какие бывают и как выбрать</t>
+        </is>
+      </c>
+      <c r="C395" s="29" t="inlineStr">
+        <is>
+          <t>шины для вилочного погрузчика 28х9 15</t>
+        </is>
+      </c>
+      <c r="D395" s="28" t="n">
+        <v>10</v>
+      </c>
+      <c r="E395" s="28" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" s="28" t="n">
+        <v>33</v>
+      </c>
+      <c r="B396" s="29" t="inlineStr">
+        <is>
+          <t>Шины для вилочного погрузчика: какие бывают и как выбрать</t>
+        </is>
+      </c>
+      <c r="C396" s="29" t="inlineStr">
+        <is>
+          <t>зимние шины для погрузчика вилочного</t>
+        </is>
+      </c>
+      <c r="D396" s="28" t="n">
+        <v>6</v>
+      </c>
+      <c r="E396" s="28" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" s="28" t="n">
+        <v>33</v>
+      </c>
+      <c r="B397" s="29" t="inlineStr">
+        <is>
+          <t>Шины для вилочного погрузчика: какие бывают и как выбрать</t>
+        </is>
+      </c>
+      <c r="C397" s="29" t="inlineStr">
+        <is>
+          <t>шины цельнолитые для вилочного погрузчика</t>
+        </is>
+      </c>
+      <c r="D397" s="28" t="n">
+        <v>5</v>
+      </c>
+      <c r="E397" s="28" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" s="28" t="n">
+        <v>33</v>
+      </c>
+      <c r="B398" s="29" t="inlineStr">
+        <is>
+          <t>Шины для вилочного погрузчика: какие бывают и как выбрать</t>
+        </is>
+      </c>
+      <c r="C398" s="29" t="inlineStr">
+        <is>
+          <t>вилочный погрузчик шины</t>
+        </is>
+      </c>
+      <c r="D398" s="28" t="n">
+        <v>4</v>
+      </c>
+      <c r="E398" s="28" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" s="28" t="n">
+        <v>33</v>
+      </c>
+      <c r="B399" s="29" t="inlineStr">
+        <is>
+          <t>Шины для вилочного погрузчика: какие бывают и как выбрать</t>
+        </is>
+      </c>
+      <c r="C399" s="29" t="inlineStr">
+        <is>
+          <t>шины для автопогрузчиков в новосибирске</t>
+        </is>
+      </c>
+      <c r="D399" s="28" t="n">
+        <v>3</v>
+      </c>
+      <c r="E399" s="28" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" s="28" t="n">
+        <v>33</v>
+      </c>
+      <c r="B400" s="29" t="inlineStr">
+        <is>
+          <t>Шины для вилочного погрузчика: какие бывают и как выбрать</t>
+        </is>
+      </c>
+      <c r="C400" s="29" t="inlineStr">
+        <is>
+          <t>шины автопогрузчика</t>
+        </is>
+      </c>
+      <c r="D400" s="28" t="n">
+        <v>2</v>
+      </c>
+      <c r="E400" s="28" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" s="28" t="n">
+        <v>34</v>
+      </c>
+      <c r="B401" s="29" t="inlineStr">
+        <is>
+          <t>Ремонт и диагностика неисправностей вилочного погрузчика</t>
+        </is>
+      </c>
+      <c r="C401" s="29" t="inlineStr">
+        <is>
+          <t>ремонт вилочного погрузчика</t>
+        </is>
+      </c>
+      <c r="D401" s="28" t="n">
+        <v>58</v>
+      </c>
+      <c r="E401" s="28" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" s="28" t="n">
+        <v>34</v>
+      </c>
+      <c r="B402" s="29" t="inlineStr">
+        <is>
+          <t>Ремонт и диагностика неисправностей вилочного погрузчика</t>
+        </is>
+      </c>
+      <c r="C402" s="29" t="inlineStr">
+        <is>
+          <t>ремонт вилочных погрузчиков</t>
+        </is>
+      </c>
+      <c r="D402" s="28" t="n">
+        <v>45</v>
+      </c>
+      <c r="E402" s="28" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" s="28" t="n">
+        <v>34</v>
+      </c>
+      <c r="B403" s="29" t="inlineStr">
+        <is>
+          <t>Ремонт и диагностика неисправностей вилочного погрузчика</t>
+        </is>
+      </c>
+      <c r="C403" s="29" t="inlineStr">
+        <is>
+          <t>гидроцилиндр погрузчика вилочного погрузчика</t>
+        </is>
+      </c>
+      <c r="D403" s="28" t="n">
+        <v>22</v>
+      </c>
+      <c r="E403" s="28" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" s="28" t="n">
+        <v>34</v>
+      </c>
+      <c r="B404" s="29" t="inlineStr">
+        <is>
+          <t>Ремонт и диагностика неисправностей вилочного погрузчика</t>
+        </is>
+      </c>
+      <c r="C404" s="29" t="inlineStr">
+        <is>
+          <t>обслуживание и ремонт вилочных погрузчиков</t>
+        </is>
+      </c>
+      <c r="D404" s="28" t="n">
+        <v>20</v>
+      </c>
+      <c r="E404" s="28" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" s="28" t="n">
+        <v>34</v>
+      </c>
+      <c r="B405" s="29" t="inlineStr">
+        <is>
+          <t>Ремонт и диагностика неисправностей вилочного погрузчика</t>
+        </is>
+      </c>
+      <c r="C405" s="29" t="inlineStr">
+        <is>
+          <t>ремонт автопогрузчиков</t>
+        </is>
+      </c>
+      <c r="D405" s="28" t="n">
+        <v>16</v>
+      </c>
+      <c r="E405" s="28" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" s="28" t="n">
+        <v>34</v>
+      </c>
+      <c r="B406" s="29" t="inlineStr">
+        <is>
+          <t>Ремонт и диагностика неисправностей вилочного погрузчика</t>
+        </is>
+      </c>
+      <c r="C406" s="29" t="inlineStr">
+        <is>
+          <t>ремонт вилочных погрузчиков минск</t>
+        </is>
+      </c>
+      <c r="D406" s="28" t="n">
+        <v>15</v>
+      </c>
+      <c r="E406" s="28" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" s="28" t="n">
+        <v>34</v>
+      </c>
+      <c r="B407" s="29" t="inlineStr">
+        <is>
+          <t>Ремонт и диагностика неисправностей вилочного погрузчика</t>
+        </is>
+      </c>
+      <c r="C407" s="29" t="inlineStr">
+        <is>
+          <t>ремонт погрузчиков в москве и московской области вилочных</t>
+        </is>
+      </c>
+      <c r="D407" s="28" t="n">
+        <v>15</v>
+      </c>
+      <c r="E407" s="28" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" s="28" t="n">
+        <v>34</v>
+      </c>
+      <c r="B408" s="29" t="inlineStr">
+        <is>
+          <t>Ремонт и диагностика неисправностей вилочного погрузчика</t>
+        </is>
+      </c>
+      <c r="C408" s="29" t="inlineStr">
+        <is>
+          <t>ремонт вилочных погрузчиков ростов на дону</t>
+        </is>
+      </c>
+      <c r="D408" s="28" t="n">
+        <v>14</v>
+      </c>
+      <c r="E408" s="28" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" s="28" t="n">
+        <v>34</v>
+      </c>
+      <c r="B409" s="29" t="inlineStr">
+        <is>
+          <t>Ремонт и диагностика неисправностей вилочного погрузчика</t>
+        </is>
+      </c>
+      <c r="C409" s="29" t="inlineStr">
+        <is>
+          <t>ремонт вилочных погрузчиков москва</t>
+        </is>
+      </c>
+      <c r="D409" s="28" t="n">
+        <v>12</v>
+      </c>
+      <c r="E409" s="28" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" s="28" t="n">
+        <v>34</v>
+      </c>
+      <c r="B410" s="29" t="inlineStr">
+        <is>
+          <t>Ремонт и диагностика неисправностей вилочного погрузчика</t>
+        </is>
+      </c>
+      <c r="C410" s="29" t="inlineStr">
+        <is>
+          <t>гидроцилиндр вилочного погрузчика</t>
+        </is>
+      </c>
+      <c r="D410" s="28" t="n">
+        <v>9</v>
+      </c>
+      <c r="E410" s="28" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" s="28" t="n">
+        <v>34</v>
+      </c>
+      <c r="B411" s="29" t="inlineStr">
+        <is>
+          <t>Ремонт и диагностика неисправностей вилочного погрузчика</t>
+        </is>
+      </c>
+      <c r="C411" s="29" t="inlineStr">
+        <is>
+          <t>ремонт вилочных погрузчиков в москве</t>
+        </is>
+      </c>
+      <c r="D411" s="28" t="n">
+        <v>7</v>
+      </c>
+      <c r="E411" s="28" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" s="28" t="n">
+        <v>34</v>
+      </c>
+      <c r="B412" s="29" t="inlineStr">
+        <is>
+          <t>Ремонт и диагностика неисправностей вилочного погрузчика</t>
+        </is>
+      </c>
+      <c r="C412" s="29" t="inlineStr">
+        <is>
+          <t>ремонт вилочных погрузчиков нижний новгород</t>
+        </is>
+      </c>
+      <c r="D412" s="28" t="n">
+        <v>7</v>
+      </c>
+      <c r="E412" s="28" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" s="28" t="n">
+        <v>35</v>
+      </c>
+      <c r="B413" s="29" t="inlineStr">
+        <is>
+          <t>Запчасти для вилочного погрузчика: что изнашивается быстрее всего</t>
+        </is>
+      </c>
+      <c r="C413" s="29" t="inlineStr">
+        <is>
+          <t>запчасти для вилочных погрузчиков</t>
+        </is>
+      </c>
+      <c r="D413" s="28" t="n">
+        <v>98</v>
+      </c>
+      <c r="E413" s="28" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" s="28" t="n">
+        <v>35</v>
+      </c>
+      <c r="B414" s="29" t="inlineStr">
+        <is>
+          <t>Запчасти для вилочного погрузчика: что изнашивается быстрее всего</t>
+        </is>
+      </c>
+      <c r="C414" s="29" t="inlineStr">
+        <is>
+          <t>воздушный фильтр на вилочный погрузчик</t>
+        </is>
+      </c>
+      <c r="D414" s="28" t="n">
+        <v>39</v>
+      </c>
+      <c r="E414" s="28" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" s="28" t="n">
+        <v>35</v>
+      </c>
+      <c r="B415" s="29" t="inlineStr">
+        <is>
+          <t>Запчасти для вилочного погрузчика: что изнашивается быстрее всего</t>
+        </is>
+      </c>
+      <c r="C415" s="29" t="inlineStr">
+        <is>
+          <t>запчасти на вилочный погрузчик</t>
+        </is>
+      </c>
+      <c r="D415" s="28" t="n">
+        <v>31</v>
+      </c>
+      <c r="E415" s="28" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" s="28" t="n">
+        <v>35</v>
+      </c>
+      <c r="B416" s="29" t="inlineStr">
+        <is>
+          <t>Запчасти для вилочного погрузчика: что изнашивается быстрее всего</t>
+        </is>
+      </c>
+      <c r="C416" s="29" t="inlineStr">
+        <is>
+          <t>запчасти для вилочного погрузчика</t>
+        </is>
+      </c>
+      <c r="D416" s="28" t="n">
+        <v>26</v>
+      </c>
+      <c r="E416" s="28" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" s="28" t="n">
+        <v>35</v>
+      </c>
+      <c r="B417" s="29" t="inlineStr">
+        <is>
+          <t>Запчасти для вилочного погрузчика: что изнашивается быстрее всего</t>
+        </is>
+      </c>
+      <c r="C417" s="29" t="inlineStr">
+        <is>
+          <t>гидравлическое масло для погрузчика вилочного</t>
+        </is>
+      </c>
+      <c r="D417" s="28" t="n">
+        <v>21</v>
+      </c>
+      <c r="E417" s="28" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" s="28" t="n">
+        <v>35</v>
+      </c>
+      <c r="B418" s="29" t="inlineStr">
+        <is>
+          <t>Запчасти для вилочного погрузчика: что изнашивается быстрее всего</t>
+        </is>
+      </c>
+      <c r="C418" s="29" t="inlineStr">
+        <is>
+          <t>сиденье для вилочного погрузчика</t>
+        </is>
+      </c>
+      <c r="D418" s="28" t="n">
+        <v>20</v>
+      </c>
+      <c r="E418" s="28" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" s="28" t="n">
+        <v>35</v>
+      </c>
+      <c r="B419" s="29" t="inlineStr">
+        <is>
+          <t>Запчасти для вилочного погрузчика: что изнашивается быстрее всего</t>
+        </is>
+      </c>
+      <c r="C419" s="29" t="inlineStr">
+        <is>
+          <t>кабина на вилочный погрузчик</t>
+        </is>
+      </c>
+      <c r="D419" s="28" t="n">
+        <v>20</v>
+      </c>
+      <c r="E419" s="28" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" s="28" t="n">
+        <v>35</v>
+      </c>
+      <c r="B420" s="29" t="inlineStr">
+        <is>
+          <t>Запчасти для вилочного погрузчика: что изнашивается быстрее всего</t>
+        </is>
+      </c>
+      <c r="C420" s="29" t="inlineStr">
+        <is>
+          <t>главный тормозной цилиндр на вилочный погрузчик</t>
+        </is>
+      </c>
+      <c r="D420" s="28" t="n">
+        <v>20</v>
+      </c>
+      <c r="E420" s="28" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" s="28" t="n">
+        <v>35</v>
+      </c>
+      <c r="B421" s="29" t="inlineStr">
+        <is>
+          <t>Запчасти для вилочного погрузчика: что изнашивается быстрее всего</t>
+        </is>
+      </c>
+      <c r="C421" s="29" t="inlineStr">
+        <is>
+          <t>запчасти к вилочным погрузчикам</t>
+        </is>
+      </c>
+      <c r="D421" s="28" t="n">
+        <v>16</v>
+      </c>
+      <c r="E421" s="28" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" s="28" t="n">
+        <v>35</v>
+      </c>
+      <c r="B422" s="29" t="inlineStr">
+        <is>
+          <t>Запчасти для вилочного погрузчика: что изнашивается быстрее всего</t>
+        </is>
+      </c>
+      <c r="C422" s="29" t="inlineStr">
+        <is>
+          <t>сиденье на вилочный погрузчик</t>
+        </is>
+      </c>
+      <c r="D422" s="28" t="n">
+        <v>16</v>
+      </c>
+      <c r="E422" s="28" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" s="28" t="n">
+        <v>35</v>
+      </c>
+      <c r="B423" s="29" t="inlineStr">
+        <is>
+          <t>Запчасти для вилочного погрузчика: что изнашивается быстрее всего</t>
+        </is>
+      </c>
+      <c r="C423" s="29" t="inlineStr">
+        <is>
+          <t>фильтр воздушный для вилочного погрузчика</t>
+        </is>
+      </c>
+      <c r="D423" s="28" t="n">
+        <v>16</v>
+      </c>
+      <c r="E423" s="28" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" s="28" t="n">
+        <v>35</v>
+      </c>
+      <c r="B424" s="29" t="inlineStr">
+        <is>
+          <t>Запчасти для вилочного погрузчика: что изнашивается быстрее всего</t>
+        </is>
+      </c>
+      <c r="C424" s="29" t="inlineStr">
+        <is>
+          <t>тормозные колодки на вилочный погрузчик</t>
+        </is>
+      </c>
+      <c r="D424" s="28" t="n">
+        <v>14</v>
+      </c>
+      <c r="E424" s="28" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" s="28" t="n">
+        <v>36</v>
+      </c>
+      <c r="B425" s="29" t="inlineStr">
+        <is>
+          <t>Регистрация вилочного погрузчика в Гостехнадзоре: что нужно знать владельцу</t>
+        </is>
+      </c>
+      <c r="C425" s="29" t="inlineStr">
+        <is>
+          <t>какие права нужны на вилочный погрузчик</t>
+        </is>
+      </c>
+      <c r="D425" s="28" t="n">
+        <v>119</v>
+      </c>
+      <c r="E425" s="28" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" s="28" t="n">
+        <v>36</v>
+      </c>
+      <c r="B426" s="29" t="inlineStr">
+        <is>
+          <t>Регистрация вилочного погрузчика в Гостехнадзоре: что нужно знать владельцу</t>
+        </is>
+      </c>
+      <c r="C426" s="29" t="inlineStr">
+        <is>
+          <t>к какой группе ос относится вилочный погрузчик</t>
+        </is>
+      </c>
+      <c r="D426" s="28" t="n">
+        <v>70</v>
+      </c>
+      <c r="E426" s="28" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" s="28" t="n">
+        <v>36</v>
+      </c>
+      <c r="B427" s="29" t="inlineStr">
+        <is>
+          <t>Регистрация вилочного погрузчика в Гостехнадзоре: что нужно знать владельцу</t>
+        </is>
+      </c>
+      <c r="C427" s="29" t="inlineStr">
+        <is>
+          <t>какие права нужны для вилочного погрузчика</t>
+        </is>
+      </c>
+      <c r="D427" s="28" t="n">
+        <v>37</v>
+      </c>
+      <c r="E427" s="28" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" s="28" t="n">
+        <v>36</v>
+      </c>
+      <c r="B428" s="29" t="inlineStr">
+        <is>
+          <t>Регистрация вилочного погрузчика в Гостехнадзоре: что нужно знать владельцу</t>
+        </is>
+      </c>
+      <c r="C428" s="29" t="inlineStr">
+        <is>
+          <t>как поставить на учет вилочный погрузчик</t>
+        </is>
+      </c>
+      <c r="D428" s="28" t="n">
+        <v>27</v>
+      </c>
+      <c r="E428" s="28" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" s="28" t="n">
+        <v>36</v>
+      </c>
+      <c r="B429" s="29" t="inlineStr">
+        <is>
+          <t>Регистрация вилочного погрузчика в Гостехнадзоре: что нужно знать владельцу</t>
+        </is>
+      </c>
+      <c r="C429" s="29" t="inlineStr">
+        <is>
+          <t>какие права нужны на кару вилочный погрузчик</t>
+        </is>
+      </c>
+      <c r="D429" s="28" t="n">
+        <v>27</v>
+      </c>
+      <c r="E429" s="28" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" s="28" t="n">
+        <v>36</v>
+      </c>
+      <c r="B430" s="29" t="inlineStr">
+        <is>
+          <t>Регистрация вилочного погрузчика в Гостехнадзоре: что нужно знать владельцу</t>
+        </is>
+      </c>
+      <c r="C430" s="29" t="inlineStr">
+        <is>
+          <t>какие права нужны для управления погрузчиком вилочным</t>
+        </is>
+      </c>
+      <c r="D430" s="28" t="n">
+        <v>25</v>
+      </c>
+      <c r="E430" s="28" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" s="28" t="n">
+        <v>36</v>
+      </c>
+      <c r="B431" s="29" t="inlineStr">
+        <is>
+          <t>Регистрация вилочного погрузчика в Гостехнадзоре: что нужно знать владельцу</t>
+        </is>
+      </c>
+      <c r="C431" s="29" t="inlineStr">
+        <is>
+          <t>какие права нужны на вилочный погрузчик на складе</t>
+        </is>
+      </c>
+      <c r="D431" s="28" t="n">
+        <v>23</v>
+      </c>
+      <c r="E431" s="28" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" s="28" t="n">
+        <v>36</v>
+      </c>
+      <c r="B432" s="29" t="inlineStr">
+        <is>
+          <t>Регистрация вилочного погрузчика в Гостехнадзоре: что нужно знать владельцу</t>
+        </is>
+      </c>
+      <c r="C432" s="29" t="inlineStr">
+        <is>
+          <t>как поставить вилочный погрузчик на учет в гостехнадзоре</t>
+        </is>
+      </c>
+      <c r="D432" s="28" t="n">
+        <v>16</v>
+      </c>
+      <c r="E432" s="28" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" s="28" t="n">
+        <v>36</v>
+      </c>
+      <c r="B433" s="29" t="inlineStr">
+        <is>
+          <t>Регистрация вилочного погрузчика в Гостехнадзоре: что нужно знать владельцу</t>
+        </is>
+      </c>
+      <c r="C433" s="29" t="inlineStr">
+        <is>
+          <t>нужно ли ставить на учет вилочный погрузчик</t>
+        </is>
+      </c>
+      <c r="D433" s="28" t="n">
+        <v>12</v>
+      </c>
+      <c r="E433" s="28" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" s="28" t="n">
+        <v>36</v>
+      </c>
+      <c r="B434" s="29" t="inlineStr">
+        <is>
+          <t>Регистрация вилочного погрузчика в Гостехнадзоре: что нужно знать владельцу</t>
+        </is>
+      </c>
+      <c r="C434" s="29" t="inlineStr">
+        <is>
+          <t>вилочный погрузчик какие права нужны</t>
+        </is>
+      </c>
+      <c r="D434" s="28" t="n">
+        <v>9</v>
+      </c>
+      <c r="E434" s="28" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" s="28" t="n">
+        <v>36</v>
+      </c>
+      <c r="B435" s="29" t="inlineStr">
+        <is>
+          <t>Регистрация вилочного погрузчика в Гостехнадзоре: что нужно знать владельцу</t>
+        </is>
+      </c>
+      <c r="C435" s="29" t="inlineStr">
+        <is>
+          <t>постановка вилочного погрузчика на учет</t>
+        </is>
+      </c>
+      <c r="D435" s="28" t="n">
+        <v>9</v>
+      </c>
+      <c r="E435" s="28" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" s="28" t="n">
+        <v>36</v>
+      </c>
+      <c r="B436" s="29" t="inlineStr">
+        <is>
+          <t>Регистрация вилочного погрузчика в Гостехнадзоре: что нужно знать владельцу</t>
+        </is>
+      </c>
+      <c r="C436" s="29" t="inlineStr">
+        <is>
+          <t>какие права нужны на автопогрузчик</t>
+        </is>
+      </c>
+      <c r="D436" s="28" t="n">
+        <v>8</v>
+      </c>
+      <c r="E436" s="28" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" s="28" t="n">
+        <v>37</v>
+      </c>
+      <c r="B437" s="29" t="inlineStr">
+        <is>
           <t>Аренда вилочного погрузчика: когда выгоднее покупки</t>
         </is>
       </c>
-      <c r="C328" s="29" t="inlineStr">
+      <c r="C437" s="29" t="inlineStr">
+        <is>
+          <t>аренда вилочного погрузчика</t>
+        </is>
+      </c>
+      <c r="D437" s="28" t="n">
+        <v>270</v>
+      </c>
+      <c r="E437" s="28" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" s="28" t="n">
+        <v>37</v>
+      </c>
+      <c r="B438" s="29" t="inlineStr">
+        <is>
+          <t>Аренда вилочного погрузчика: когда выгоднее покупки</t>
+        </is>
+      </c>
+      <c r="C438" s="29" t="inlineStr">
+        <is>
+          <t>аренда погрузчика вилочного цена</t>
+        </is>
+      </c>
+      <c r="D438" s="28" t="n">
+        <v>65</v>
+      </c>
+      <c r="E438" s="28" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" s="28" t="n">
+        <v>37</v>
+      </c>
+      <c r="B439" s="29" t="inlineStr">
+        <is>
+          <t>Аренда вилочного погрузчика: когда выгоднее покупки</t>
+        </is>
+      </c>
+      <c r="C439" s="29" t="inlineStr">
+        <is>
+          <t>погрузчик вилочный в аренду</t>
+        </is>
+      </c>
+      <c r="D439" s="28" t="n">
+        <v>64</v>
+      </c>
+      <c r="E439" s="28" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" s="28" t="n">
+        <v>37</v>
+      </c>
+      <c r="B440" s="29" t="inlineStr">
+        <is>
+          <t>Аренда вилочного погрузчика: когда выгоднее покупки</t>
+        </is>
+      </c>
+      <c r="C440" s="29" t="inlineStr">
+        <is>
+          <t>аренда вилочных погрузчиков</t>
+        </is>
+      </c>
+      <c r="D440" s="28" t="n">
+        <v>57</v>
+      </c>
+      <c r="E440" s="28" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" s="28" t="n">
+        <v>37</v>
+      </c>
+      <c r="B441" s="29" t="inlineStr">
+        <is>
+          <t>Аренда вилочного погрузчика: когда выгоднее покупки</t>
+        </is>
+      </c>
+      <c r="C441" s="29" t="inlineStr">
+        <is>
+          <t>аренда погрузчика вилочного в спб</t>
+        </is>
+      </c>
+      <c r="D441" s="28" t="n">
+        <v>49</v>
+      </c>
+      <c r="E441" s="28" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" s="28" t="n">
+        <v>37</v>
+      </c>
+      <c r="B442" s="29" t="inlineStr">
+        <is>
+          <t>Аренда вилочного погрузчика: когда выгоднее покупки</t>
+        </is>
+      </c>
+      <c r="C442" s="29" t="inlineStr">
+        <is>
+          <t>аренда вилочного погрузчика спб</t>
+        </is>
+      </c>
+      <c r="D442" s="28" t="n">
+        <v>44</v>
+      </c>
+      <c r="E442" s="28" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" s="28" t="n">
+        <v>37</v>
+      </c>
+      <c r="B443" s="29" t="inlineStr">
+        <is>
+          <t>Аренда вилочного погрузчика: когда выгоднее покупки</t>
+        </is>
+      </c>
+      <c r="C443" s="29" t="inlineStr">
+        <is>
+          <t>аренда погрузчика вилочного москва</t>
+        </is>
+      </c>
+      <c r="D443" s="28" t="n">
+        <v>42</v>
+      </c>
+      <c r="E443" s="28" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" s="28" t="n">
+        <v>37</v>
+      </c>
+      <c r="B444" s="29" t="inlineStr">
+        <is>
+          <t>Аренда вилочного погрузчика: когда выгоднее покупки</t>
+        </is>
+      </c>
+      <c r="C444" s="29" t="inlineStr">
+        <is>
+          <t>аренда вилочных погрузчиков в москве и московской области</t>
+        </is>
+      </c>
+      <c r="D444" s="28" t="n">
+        <v>35</v>
+      </c>
+      <c r="E444" s="28" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" s="28" t="n">
+        <v>37</v>
+      </c>
+      <c r="B445" s="29" t="inlineStr">
+        <is>
+          <t>Аренда вилочного погрузчика: когда выгоднее покупки</t>
+        </is>
+      </c>
+      <c r="C445" s="29" t="inlineStr">
+        <is>
+          <t>аренда вилочных погрузчиков в москве</t>
+        </is>
+      </c>
+      <c r="D445" s="28" t="n">
+        <v>34</v>
+      </c>
+      <c r="E445" s="28" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" s="28" t="n">
+        <v>37</v>
+      </c>
+      <c r="B446" s="29" t="inlineStr">
+        <is>
+          <t>Аренда вилочного погрузчика: когда выгоднее покупки</t>
+        </is>
+      </c>
+      <c r="C446" s="29" t="inlineStr">
+        <is>
+          <t>аренда вилочного погрузчика с оператором</t>
+        </is>
+      </c>
+      <c r="D446" s="28" t="n">
+        <v>31</v>
+      </c>
+      <c r="E446" s="28" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" s="28" t="n">
+        <v>37</v>
+      </c>
+      <c r="B447" s="29" t="inlineStr">
+        <is>
+          <t>Аренда вилочного погрузчика: когда выгоднее покупки</t>
+        </is>
+      </c>
+      <c r="C447" s="29" t="inlineStr">
+        <is>
+          <t>аренда вилочного погрузчика в новосибирске</t>
+        </is>
+      </c>
+      <c r="D447" s="28" t="n">
+        <v>27</v>
+      </c>
+      <c r="E447" s="28" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" s="28" t="n">
+        <v>37</v>
+      </c>
+      <c r="B448" s="29" t="inlineStr">
+        <is>
+          <t>Аренда вилочного погрузчика: когда выгоднее покупки</t>
+        </is>
+      </c>
+      <c r="C448" s="29" t="inlineStr">
         <is>
           <t>аренда вилочного погрузчика в твери</t>
         </is>
       </c>
-      <c r="D328" s="28" t="n">
+      <c r="D448" s="28" t="n">
         <v>27</v>
       </c>
-      <c r="E328" s="28" t="n">
+      <c r="E448" s="28" t="n">
         <v>12</v>
       </c>
     </row>
@@ -8570,7 +11460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A24"/>
+  <dimension ref="A1:A26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -8579,7 +11469,7 @@
     <row r="1">
       <c r="A1" s="30" t="inlineStr">
         <is>
-          <t>Вилочные погрузчики — план статей</t>
+          <t>Вилочные погрузчики — план статей (v2)</t>
         </is>
       </c>
     </row>
@@ -8589,14 +11479,14 @@
     <row r="3">
       <c r="A3" s="32" t="inlineStr">
         <is>
-          <t>ЧТО ЭТО</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="45" customHeight="1">
+          <t>ЧТО ИЗМЕНИЛОСЬ С ПЕРВОЙ ВЕРСИИ</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="60" customHeight="1">
       <c r="A4" s="31" t="inlineStr">
         <is>
-          <t>26 статей только про вилочные погрузчики — вы сказали заниматься ими одними, остальная складская техника (рохли, штабелёры, ричтраки) из плана убрана, хотя в выгрузке её было втрое больше по объёму.</t>
+          <t>Было 26 статей — я специально укрупнил бренды и тоннаж, чтобы каждая статья опиралась на солидный объём показов. Это было консервативное решение, а не предел данных: длинный хвост по вилочным погрузчикам реально большой, и его можно раскрыть глубже. В этой версии — 37 статей: бренды разбиты по отдельности (было 10 сборных статей, стало 16, включая пару небольших групповых для совсем тонких марок), добавлена статья про мачту и габариты, покупка разделена на «сделка», «б/у», «цена» и «Авито» отдельно, эксплуатация — на «навесное», «шины», «ремонт» и «запчасти» по отдельности.</t>
         </is>
       </c>
     </row>
@@ -8610,10 +11500,10 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="45" customHeight="1">
+    <row r="7" ht="60" customHeight="1">
       <c r="A7" s="31" t="inlineStr">
         <is>
-          <t>19 CSV-файлов из Букварикса, 644 225 строк. Схлопнул перестановки слов и словоформы («купить вилочный погрузчик» = «вилочный погрузчик купить» — для Яндекса это один запрос) — получилось 214 644 уникальных запроса. Отсеял вакансии, обучение на права, игрушки и инфо-мусор. Из оставшегося вилочные погрузчики — 19 411 запросов, 38 727 показов. План закрывает 33 093 показа (85%) статьями; 5 632 показа (15%) — это очень длинный хвост (вакансии водителей, единичные технические вопросы), под него отдельные статьи не оправданы.</t>
+          <t>19 CSV-файлов из Букварикса, 644 225 строк. Схлопнул перестановки слов и словоформы («купить вилочный погрузчик» = «вилочный погрузчик купить» — для Яндекса это один запрос) — получилось 214 644 уникальных запроса. Отсеял вакансии, обучение на права, игрушки и инфо-мусор. Вилочные погрузчики — 19 407 запросов, 38 725 показов. План закрывает 33 392 показа (86%); 5 333 показа (14%) — очень длинный хвост (вакансии водителей, единичные технические вопросы вроде «окоф амортизационная группа»), под него отдельные статьи не оправданы даже при таком темпе дробления.</t>
         </is>
       </c>
     </row>
@@ -8623,96 +11513,106 @@
     <row r="9">
       <c r="A9" s="32" t="inlineStr">
         <is>
+          <t>ПОРЯДОК РАЗБОРА ФРАЗ</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="60" customHeight="1">
+      <c r="A10" s="31" t="inlineStr">
+        <is>
+          <t>Сначала распределялись фразы с названием конкретного бренда или модельного кода («heli 5 тонн» уходит в статью про Heli, а не в статью про тоннаж) — так более редкая и ценная для покупателя информация не растворяется в общей статье. Затем — тоннаж, мачта и тип привода без привязки к бренду. Затем — воронка покупки. Хаб идёт последним и забирает всё, что содержит «вилочный погрузчик» или «автопогрузчик» и не подошло ни в одну специализированную статью — в основном это сам головной запрос «вилочный погрузчик» (4234 показа) и его общие формы.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="31" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="32" t="inlineStr">
+        <is>
+          <t>ПОЧЕМУ НЕКОТОРЫЕ БРЕНДЫ ВСЁ ЕЩЁ В ГРУППАХ</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="60" customHeight="1">
+      <c r="A13" s="31" t="inlineStr">
+        <is>
+          <t>Nissan, Mitsubishi, TCM, Manitou, Kalmar и Shantui по отдельности — от 40 до 110 показов каждый, слишком тонко для самостоятельной статьи. Вместе — 469, полноценный объём. То же с европейской группой (Still, Linde, Jungheinrich, Yale, Hyster, Clark) — 273 показа на шестерых. Если по итогам публикации увидите, что конкретный бренд из группы явно тянет собственный трафик — выделите его в отдельную статью позже, это не потребует пересборки остального плана.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="31" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="32" t="inlineStr">
+        <is>
           <t>ДВЕ ВАЖНЫЕ ОГОВОРКИ</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="45" customHeight="1">
-      <c r="A10" s="31" t="inlineStr">
-        <is>
-          <t>1. Регион в выгрузке — «Весь мир», а не Россия. Порядок и соотношение кластеров верные, но абсолютные цифры по России будут ниже. Если сможете переснять с регионом «Россия» — пришлите, пересчитаю.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="45" customHeight="1">
-      <c r="A11" s="31" t="inlineStr">
-        <is>
-          <t>2. Конкуренция не снята. Всё в плане отранжировано по спросу, а не по тому, что реально легко занять. Прогоните лист «Целевые фразы» через Мутаген (или другой чекер) — тогда порядок недель можно будет уточнить в пользу более лёгких тем.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="31" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="32" t="inlineStr">
-        <is>
-          <t>КАК УСТРОЕНА ПЕРВАЯ СТРАНИЦА</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="45" customHeight="1">
-      <c r="A14" s="31" t="inlineStr">
-        <is>
-          <t>Статьи сгруппированы в 7 кластеров и разложены по неделям — по 2 статьи в неделю, кроме первой недели (только хаб — на него ссылаются все остальные статьи, поэтому он должен появиться первым). При таком темпе весь план закроется за 14 недель, это чуть больше трёх месяцев. Если хотите публиковать ещё осторожнее — растяните тот же порядок на 1 статью в неделю, будет 26 недель.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="45" customHeight="1">
-      <c r="A15" s="31" t="inlineStr">
-        <is>
-          <t>Колонка «Слаг» — предложенный адрес страницы, можно менять под свою структуру сайта. Колонка «Статус» — выпадающий список, отмечайте прогресс прямо в файле.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="31" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="32" t="inlineStr">
-        <is>
-          <t>ПОЧЕМУ ИМЕННО ТАКОЙ ПОРЯДОК</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="45" customHeight="1">
-      <c r="A18" s="31" t="inlineStr">
-        <is>
-          <t>Сначала — статьи, которые нужны для навигации и перелинковки (хаб, выбор, виды и приводы). Затем — тоннаж и оформление сделки: это то, что реально приводит заявку. Бренды — самый длинный раздел (10 статей) — идут по одной-две в неделю в середине и конце плана: у каждой из них небольшой собственный объём, но вместе они дают 6 646 показов длинного хвоста, и растянутая публикация выглядит для поисковика органичным ростом сайта, а не заливкой контента.</t>
-        </is>
-      </c>
+    <row r="16" ht="60" customHeight="1">
+      <c r="A16" s="31" t="inlineStr">
+        <is>
+          <t>1. Регион в выгрузке — «Весь мир», а не Россия. Порядок и соотношение кластеров верные, но абсолютные цифры по России будут ниже. Пересниму, если пришлёте выгрузку с регионом «Россия».</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="60" customHeight="1">
+      <c r="A17" s="31" t="inlineStr">
+        <is>
+          <t>2. Конкуренция не снята. План отранжирован по спросу, не по лёгкости продвижения. Прогоните лист «Целевые фразы» через Мутаген — тогда порядок недель можно уточнить в пользу более лёгких тем.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="31" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="31" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="32" t="inlineStr">
-        <is>
-          <t>ЧТО НЕ ВОШЛО В ПЛАН И ПОЧЕМУ</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="45" customHeight="1">
-      <c r="A21" s="31" t="inlineStr">
-        <is>
-          <t>«Водитель вилочного погрузчика» / вакансии — это поиск работы, а не покупки, при любой формулировке в запросе. Мелкие технические вопросы (наклон каретки, конкретные модели типа CPD15) — слишком узкие для отдельной статьи, но упомяните их в статьях по бренду или по эксплуатации, если пишете вручную и видите, что подходит по смыслу.</t>
-        </is>
-      </c>
+      <c r="A19" s="32" t="inlineStr">
+        <is>
+          <t>ТЕМП ПУБЛИКАЦИИ</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="60" customHeight="1">
+      <c r="A20" s="31" t="inlineStr">
+        <is>
+          <t>2 статьи в неделю, кроме первой (только хаб — на него ссылаются все остальные, он должен выйти первым). При таком темпе весь план закроется за 19 недель — чуть больше четырёх месяцев. Если хотите быстрее — 3 статьи в неделю сократят план до 13 недель и всё ещё будут выглядеть органичным ростом сайта, а не заливкой контента; профиль публикаций у мелкого локального сайта, который прирастает на 2–3 страницы в неделю несколько месяцев подряд, не похож на паттерн, который вызывает лишнее внимание.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="31" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="31" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="32" t="inlineStr">
+      <c r="A22" s="32" t="inlineStr">
+        <is>
+          <t>ГЕОГРАФИЯ ЗА ПРЕДЕЛАМИ УРАЛА</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="60" customHeight="1">
+      <c r="A23" s="31" t="inlineStr">
+        <is>
+          <t>Отдельной статьи под Москву/СПб/Новосибирск и другие города не делал — большая часть таких запросов («купить в москве», «аренда в спб») уже разобрана статьями «Купить вилочный погрузчик» и «Аренда вилочного погрузчика»: упомяните там, что работаете не только по Свердловской области. Отдельные посадочные страницы по городам (как уже есть для 6 городов области) — это не статьи, а коммерческие лендинги; если решите расширять географию, это отдельная задача со своим шаблоном, не часть блога.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="31" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="32" t="inlineStr">
         <is>
           <t>КАННИБАЛИЗАЦИЯ</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="45" customHeight="1">
-      <c r="A24" s="31" t="inlineStr">
-        <is>
-          <t>Каждая фраза закреплена ровно за одной статьёй — проверено программно, дублей нет. Если будете добавлять свои темы, держите то же правило: один смысловой запрос — одна страница.</t>
+    <row r="26" ht="60" customHeight="1">
+      <c r="A26" s="31" t="inlineStr">
+        <is>
+          <t>Каждая фраза закреплена ровно за одной статьёй — проверено программно на всех 37 статьях, дублей нет. Если добавляете свои темы — держите то же правило: один смысловой запрос — одна страница.</t>
         </is>
       </c>
     </row>

--- a/_semantics/plan-vilochnye-pogruzchiki.xlsx
+++ b/_semantics/plan-vilochnye-pogruzchiki.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="План публикаций" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Структура и объём" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Целевые фразы" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Как читать этот файл" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="План публикаций" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Структура и объём" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Целевые фразы" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Как читать этот файл" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -582,7 +582,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J82"/>
+  <dimension ref="A1:J85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -607,7 +607,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>77 статей — одна на каждый различимый интент, без учёта тонкости объёма. Источник: 19 файлов Букварикса, точная частотность, регион «Весь мир» (см. лист «Как читать»).</t>
+          <t>80 статей — одна на каждый различимый интент, без учёта тонкости объёма. Источник: 19 файлов Букварикса, точная частотность, регион «Весь мир» (см. лист «Как читать»).</t>
         </is>
       </c>
     </row>
@@ -691,10 +691,10 @@
         </is>
       </c>
       <c r="F5" s="4" t="n">
-        <v>10378</v>
+        <v>10376</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>5955</v>
+        <v>5947</v>
       </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
@@ -740,7 +740,7 @@
         <v>197</v>
       </c>
       <c r="G6" s="7" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="H6" s="8" t="inlineStr">
         <is>
@@ -824,7 +824,7 @@
         <v>1592</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H8" s="8" t="inlineStr">
         <is>
@@ -1157,10 +1157,10 @@
         </is>
       </c>
       <c r="F16" s="7" t="n">
-        <v>220</v>
+        <v>190</v>
       </c>
       <c r="G16" s="7" t="n">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="H16" s="8" t="inlineStr">
         <is>
@@ -1661,10 +1661,10 @@
         </is>
       </c>
       <c r="F28" s="13" t="n">
-        <v>3211</v>
+        <v>3207</v>
       </c>
       <c r="G28" s="13" t="n">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="H28" s="14" t="inlineStr">
         <is>
@@ -3008,7 +3008,7 @@
         <v>397</v>
       </c>
       <c r="G60" s="19" t="n">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H60" s="20" t="inlineStr">
         <is>
@@ -3089,10 +3089,10 @@
         </is>
       </c>
       <c r="F62" s="19" t="n">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="G62" s="19" t="n">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H62" s="20" t="inlineStr">
         <is>
@@ -3542,19 +3542,19 @@
       </c>
       <c r="D73" s="21" t="inlineStr">
         <is>
-          <t>Монтажная платформа и корзина для вилочного погрузчика</t>
+          <t>Каретка вилочного погрузчика: устройство, класс и расширитель</t>
         </is>
       </c>
       <c r="E73" s="21" t="inlineStr">
         <is>
-          <t>/articles/montazhnaya-platforma-i-korzina-dlya-vilochnogo-pogruzchika/</t>
+          <t>/articles/karetka-vilochnogo-pogruzchika/</t>
         </is>
       </c>
       <c r="F73" s="19" t="n">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="G73" s="19" t="n">
-        <v>9</v>
+        <v>47</v>
       </c>
       <c r="H73" s="20" t="inlineStr">
         <is>
@@ -3584,19 +3584,19 @@
       </c>
       <c r="D74" s="21" t="inlineStr">
         <is>
-          <t>Вилы для вилочного погрузчика: какие бывают</t>
+          <t>Монтажная платформа и корзина для вилочного погрузчика</t>
         </is>
       </c>
       <c r="E74" s="21" t="inlineStr">
         <is>
-          <t>/articles/vily-dlya-vilochnogo-pogruzchika/</t>
+          <t>/articles/montazhnaya-platforma-i-korzina-dlya-vilochnogo-pogruzchika/</t>
         </is>
       </c>
       <c r="F74" s="19" t="n">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="G74" s="19" t="n">
-        <v>57</v>
+        <v>9</v>
       </c>
       <c r="H74" s="20" t="inlineStr">
         <is>
@@ -3626,19 +3626,19 @@
       </c>
       <c r="D75" s="21" t="inlineStr">
         <is>
-          <t>Двигатель вилочного погрузчика: ресурс и обслуживание</t>
+          <t>Вилы для вилочного погрузчика: какие бывают</t>
         </is>
       </c>
       <c r="E75" s="21" t="inlineStr">
         <is>
-          <t>/articles/dvigatel-vilochnogo-pogruzchika/</t>
+          <t>/articles/vily-dlya-vilochnogo-pogruzchika/</t>
         </is>
       </c>
       <c r="F75" s="19" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="G75" s="19" t="n">
-        <v>153</v>
+        <v>57</v>
       </c>
       <c r="H75" s="20" t="inlineStr">
         <is>
@@ -3668,19 +3668,19 @@
       </c>
       <c r="D76" s="21" t="inlineStr">
         <is>
-          <t>Каретка бокового смещения (сайдшифт) для вилочного погрузчика</t>
+          <t>Двигатель вилочного погрузчика: ресурс и обслуживание</t>
         </is>
       </c>
       <c r="E76" s="21" t="inlineStr">
         <is>
-          <t>/articles/karetka-bokovogo-smescheniya-saydshift-dlya-vilochnogo-pogruzchika/</t>
+          <t>/articles/dvigatel-vilochnogo-pogruzchika/</t>
         </is>
       </c>
       <c r="F76" s="19" t="n">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="G76" s="19" t="n">
-        <v>24</v>
+        <v>153</v>
       </c>
       <c r="H76" s="20" t="inlineStr">
         <is>
@@ -3794,19 +3794,19 @@
       </c>
       <c r="D79" s="21" t="inlineStr">
         <is>
-          <t>Цепь и ролики мачты вилочного погрузчика</t>
+          <t>Рама и шасси вилочного погрузчика</t>
         </is>
       </c>
       <c r="E79" s="21" t="inlineStr">
         <is>
-          <t>/articles/cep-i-roliki-machty-vilochnogo-pogruzchika/</t>
+          <t>/articles/rama-i-shassi-vilochnogo-pogruzchika/</t>
         </is>
       </c>
       <c r="F79" s="19" t="n">
         <v>26</v>
       </c>
       <c r="G79" s="19" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H79" s="20" t="inlineStr">
         <is>
@@ -3836,91 +3836,217 @@
       </c>
       <c r="D80" s="21" t="inlineStr">
         <is>
+          <t>Цепь и ролики мачты вилочного погрузчика</t>
+        </is>
+      </c>
+      <c r="E80" s="21" t="inlineStr">
+        <is>
+          <t>/articles/cep-i-roliki-machty-vilochnogo-pogruzchika/</t>
+        </is>
+      </c>
+      <c r="F80" s="19" t="n">
+        <v>26</v>
+      </c>
+      <c r="G80" s="19" t="n">
+        <v>19</v>
+      </c>
+      <c r="H80" s="20" t="inlineStr">
+        <is>
+          <t>500–800</t>
+        </is>
+      </c>
+      <c r="I80" s="20" t="inlineStr">
+        <is>
+          <t>Не начато</t>
+        </is>
+      </c>
+      <c r="J80" s="21" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="19" t="n">
+        <v>77</v>
+      </c>
+      <c r="B81" s="20" t="inlineStr">
+        <is>
+          <t>Неделя 27</t>
+        </is>
+      </c>
+      <c r="C81" s="20" t="inlineStr">
+        <is>
+          <t>Эксплуатация</t>
+        </is>
+      </c>
+      <c r="D81" s="21" t="inlineStr">
+        <is>
+          <t>Противовес вилочного погрузчика</t>
+        </is>
+      </c>
+      <c r="E81" s="21" t="inlineStr">
+        <is>
+          <t>/articles/protivoves-vilochnogo-pogruzchika/</t>
+        </is>
+      </c>
+      <c r="F81" s="19" t="n">
+        <v>21</v>
+      </c>
+      <c r="G81" s="19" t="n">
+        <v>20</v>
+      </c>
+      <c r="H81" s="20" t="inlineStr">
+        <is>
+          <t>500–800</t>
+        </is>
+      </c>
+      <c r="I81" s="20" t="inlineStr">
+        <is>
+          <t>Не начато</t>
+        </is>
+      </c>
+      <c r="J81" s="21" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="19" t="n">
+        <v>78</v>
+      </c>
+      <c r="B82" s="20" t="inlineStr">
+        <is>
+          <t>Неделя 27</t>
+        </is>
+      </c>
+      <c r="C82" s="20" t="inlineStr">
+        <is>
+          <t>Эксплуатация</t>
+        </is>
+      </c>
+      <c r="D82" s="21" t="inlineStr">
+        <is>
+          <t>Каретка бокового смещения (сайдшифт) для вилочного погрузчика</t>
+        </is>
+      </c>
+      <c r="E82" s="21" t="inlineStr">
+        <is>
+          <t>/articles/karetka-bokovogo-smescheniya-saydshift-dlya-vilochnogo-pogruzchika/</t>
+        </is>
+      </c>
+      <c r="F82" s="19" t="n">
+        <v>13</v>
+      </c>
+      <c r="G82" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="H82" s="20" t="inlineStr">
+        <is>
+          <t>500–800</t>
+        </is>
+      </c>
+      <c r="I82" s="20" t="inlineStr">
+        <is>
+          <t>Не начато</t>
+        </is>
+      </c>
+      <c r="J82" s="21" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="19" t="n">
+        <v>79</v>
+      </c>
+      <c r="B83" s="20" t="inlineStr">
+        <is>
+          <t>Неделя 27</t>
+        </is>
+      </c>
+      <c r="C83" s="20" t="inlineStr">
+        <is>
+          <t>Эксплуатация</t>
+        </is>
+      </c>
+      <c r="D83" s="21" t="inlineStr">
+        <is>
           <t>Регистрация вилочного погрузчика в Гостехнадзоре: что нужно знать владельцу</t>
         </is>
       </c>
-      <c r="E80" s="21" t="inlineStr">
+      <c r="E83" s="21" t="inlineStr">
         <is>
           <t>/articles/registraciya-vilochnogo-pogruzchika-v-gostehnadzore/</t>
         </is>
       </c>
-      <c r="F80" s="19" t="n">
+      <c r="F83" s="19" t="n">
         <v>517</v>
       </c>
-      <c r="G80" s="19" t="n">
+      <c r="G83" s="19" t="n">
         <v>143</v>
       </c>
-      <c r="H80" s="20" t="inlineStr">
+      <c r="H83" s="20" t="inlineStr">
         <is>
           <t>500–800</t>
         </is>
       </c>
-      <c r="I80" s="20" t="inlineStr">
+      <c r="I83" s="20" t="inlineStr">
         <is>
           <t>Не начато</t>
         </is>
       </c>
-      <c r="J80" s="21" t="inlineStr"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="22" t="n">
-        <v>77</v>
-      </c>
-      <c r="B81" s="23" t="inlineStr">
-        <is>
-          <t>Неделя 27</t>
-        </is>
-      </c>
-      <c r="C81" s="23" t="inlineStr">
+      <c r="J83" s="21" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="22" t="n">
+        <v>80</v>
+      </c>
+      <c r="B84" s="23" t="inlineStr">
+        <is>
+          <t>Неделя 28</t>
+        </is>
+      </c>
+      <c r="C84" s="23" t="inlineStr">
         <is>
           <t>Аренда</t>
         </is>
       </c>
-      <c r="D81" s="24" t="inlineStr">
+      <c r="D84" s="24" t="inlineStr">
         <is>
           <t>Аренда вилочного погрузчика: когда выгоднее покупки</t>
         </is>
       </c>
-      <c r="E81" s="24" t="inlineStr">
+      <c r="E84" s="24" t="inlineStr">
         <is>
           <t>/articles/arenda-vilochnogo-pogruzchika/</t>
         </is>
       </c>
-      <c r="F81" s="22" t="n">
+      <c r="F84" s="22" t="n">
         <v>1781</v>
       </c>
-      <c r="G81" s="22" t="n">
+      <c r="G84" s="22" t="n">
         <v>669</v>
       </c>
-      <c r="H81" s="23" t="inlineStr">
+      <c r="H84" s="23" t="inlineStr">
         <is>
           <t>1000–1200</t>
         </is>
       </c>
-      <c r="I81" s="23" t="inlineStr">
+      <c r="I84" s="23" t="inlineStr">
         <is>
           <t>Не начато</t>
         </is>
       </c>
-      <c r="J81" s="24" t="inlineStr"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="25" t="n"/>
-      <c r="B82" s="25" t="n"/>
-      <c r="C82" s="25" t="n"/>
-      <c r="D82" s="26" t="inlineStr">
+      <c r="J84" s="24" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="25" t="n"/>
+      <c r="B85" s="25" t="n"/>
+      <c r="C85" s="25" t="n"/>
+      <c r="D85" s="26" t="inlineStr">
         <is>
           <t>Итого по плану</t>
         </is>
       </c>
-      <c r="E82" s="25" t="n"/>
-      <c r="F82" s="27" t="n">
-        <v>33762</v>
-      </c>
-      <c r="G82" s="25" t="n"/>
-      <c r="H82" s="25" t="n"/>
-      <c r="I82" s="25" t="n"/>
-      <c r="J82" s="25" t="n"/>
+      <c r="E85" s="25" t="n"/>
+      <c r="F85" s="27" t="n">
+        <v>33821</v>
+      </c>
+      <c r="G85" s="25" t="n"/>
+      <c r="H85" s="25" t="n"/>
+      <c r="I85" s="25" t="n"/>
+      <c r="J85" s="25" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -3928,7 +4054,7 @@
     <mergeCell ref="A2:J2"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="I5 I6 I7 I8 I9 I10 I11 I12 I13 I14 I15 I16 I17 I18 I19 I20 I21 I22 I23 I24 I25 I26 I27 I28 I29 I30 I31 I32 I33 I34 I35 I36 I37 I38 I39 I40 I41 I42 I43 I44 I45 I46 I47 I48 I49 I50 I51 I52 I53 I54 I55 I56 I57 I58 I59 I60 I61 I62 I63 I64 I65 I66 I67 I68 I69 I70 I71 I72 I73 I74 I75 I76 I77 I78 I79 I80 I81" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="I5 I6 I7 I8 I9 I10 I11 I12 I13 I14 I15 I16 I17 I18 I19 I20 I21 I22 I23 I24 I25 I26 I27 I28 I29 I30 I31 I32 I33 I34 I35 I36 I37 I38 I39 I40 I41 I42 I43 I44 I45 I46 I47 I48 I49 I50 I51 I52 I53 I54 I55 I56 I57 I58 I59 I60 I61 I62 I63 I64 I65 I66 I67 I68 I69 I70 I71 I72 I73 I74 I75 I76 I77 I78 I79 I80 I81 I82 I83 I84" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Не начато,Пишется,Написано,Опубликовано"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4183,7 +4309,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E742"/>
+  <dimension ref="A1:E770"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -6347,11 +6473,11 @@
       </c>
       <c r="C105" s="29" t="inlineStr">
         <is>
-          <t>класс каретки вилочного погрузчика</t>
+          <t>мачта на вилочный погрузчик</t>
         </is>
       </c>
       <c r="D105" s="28" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E105" s="28" t="n">
         <v>3</v>
@@ -6368,11 +6494,11 @@
       </c>
       <c r="C106" s="29" t="inlineStr">
         <is>
-          <t>мачта на вилочный погрузчик</t>
+          <t>высота подъема вилочного погрузчика</t>
         </is>
       </c>
       <c r="D106" s="28" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E106" s="28" t="n">
         <v>4</v>
@@ -6389,11 +6515,11 @@
       </c>
       <c r="C107" s="29" t="inlineStr">
         <is>
-          <t>высота подъема вилочного погрузчика</t>
+          <t>вилочного погрузчика габариты</t>
         </is>
       </c>
       <c r="D107" s="28" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E107" s="28" t="n">
         <v>5</v>
@@ -6410,11 +6536,11 @@
       </c>
       <c r="C108" s="29" t="inlineStr">
         <is>
-          <t>вилочного погрузчика габариты</t>
+          <t>габариты вилочного погрузчика 3 тонны</t>
         </is>
       </c>
       <c r="D108" s="28" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="E108" s="28" t="n">
         <v>6</v>
@@ -6431,11 +6557,11 @@
       </c>
       <c r="C109" s="29" t="inlineStr">
         <is>
-          <t>габариты вилочного погрузчика 3 тонны</t>
+          <t>мачта для вилочного погрузчика</t>
         </is>
       </c>
       <c r="D109" s="28" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E109" s="28" t="n">
         <v>7</v>
@@ -6452,11 +6578,11 @@
       </c>
       <c r="C110" s="29" t="inlineStr">
         <is>
-          <t>мачта для вилочного погрузчика</t>
+          <t>габариты вилочного погрузчика 5 тонн</t>
         </is>
       </c>
       <c r="D110" s="28" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E110" s="28" t="n">
         <v>8</v>
@@ -6473,11 +6599,11 @@
       </c>
       <c r="C111" s="29" t="inlineStr">
         <is>
-          <t>габариты вилочного погрузчика 5 тонн</t>
+          <t>мачта для погрузчика вилочного погрузчика</t>
         </is>
       </c>
       <c r="D111" s="28" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E111" s="28" t="n">
         <v>9</v>
@@ -6494,11 +6620,11 @@
       </c>
       <c r="C112" s="29" t="inlineStr">
         <is>
-          <t>класс каретки вилочного погрузчика таблица</t>
+          <t>мачта вилочного погрузчика бу купить</t>
         </is>
       </c>
       <c r="D112" s="28" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E112" s="28" t="n">
         <v>10</v>
@@ -17871,16 +17997,16 @@
       </c>
       <c r="B654" s="29" t="inlineStr">
         <is>
-          <t>Монтажная платформа и корзина для вилочного погрузчика</t>
+          <t>Каретка вилочного погрузчика: устройство, класс и расширитель</t>
         </is>
       </c>
       <c r="C654" s="29" t="inlineStr">
         <is>
-          <t>монтажная платформа для вилочного погрузчика</t>
+          <t>каретка вилочного погрузчика</t>
         </is>
       </c>
       <c r="D654" s="28" t="n">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="E654" s="28" t="n">
         <v>1</v>
@@ -17892,16 +18018,16 @@
       </c>
       <c r="B655" s="29" t="inlineStr">
         <is>
-          <t>Монтажная платформа и корзина для вилочного погрузчика</t>
+          <t>Каретка вилочного погрузчика: устройство, класс и расширитель</t>
         </is>
       </c>
       <c r="C655" s="29" t="inlineStr">
         <is>
-          <t>монтажная корзина для вилочного погрузчика</t>
+          <t>класс каретки вилочного погрузчика</t>
         </is>
       </c>
       <c r="D655" s="28" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E655" s="28" t="n">
         <v>2</v>
@@ -17913,16 +18039,16 @@
       </c>
       <c r="B656" s="29" t="inlineStr">
         <is>
-          <t>Монтажная платформа и корзина для вилочного погрузчика</t>
+          <t>Каретка вилочного погрузчика: устройство, класс и расширитель</t>
         </is>
       </c>
       <c r="C656" s="29" t="inlineStr">
         <is>
-          <t>люлька монтажная платформа для вилочного погрузчика</t>
+          <t>каретка для вилочного погрузчика</t>
         </is>
       </c>
       <c r="D656" s="28" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E656" s="28" t="n">
         <v>3</v>
@@ -17934,16 +18060,16 @@
       </c>
       <c r="B657" s="29" t="inlineStr">
         <is>
-          <t>Монтажная платформа и корзина для вилочного погрузчика</t>
+          <t>Каретка вилочного погрузчика: устройство, класс и расширитель</t>
         </is>
       </c>
       <c r="C657" s="29" t="inlineStr">
         <is>
-          <t>монтажная корзина для вилочных погрузчиков</t>
+          <t>класс каретки вилочного погрузчика таблица</t>
         </is>
       </c>
       <c r="D657" s="28" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E657" s="28" t="n">
         <v>4</v>
@@ -17955,16 +18081,16 @@
       </c>
       <c r="B658" s="29" t="inlineStr">
         <is>
-          <t>Монтажная платформа и корзина для вилочного погрузчика</t>
+          <t>Каретка вилочного погрузчика: устройство, класс и расширитель</t>
         </is>
       </c>
       <c r="C658" s="29" t="inlineStr">
         <is>
-          <t>монтажная платформа для вилочного погрузчика км2</t>
+          <t>расширитель каретки вилочного погрузчика</t>
         </is>
       </c>
       <c r="D658" s="28" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E658" s="28" t="n">
         <v>5</v>
@@ -17976,16 +18102,16 @@
       </c>
       <c r="B659" s="29" t="inlineStr">
         <is>
-          <t>Монтажная платформа и корзина для вилочного погрузчика</t>
+          <t>Каретка вилочного погрузчика: устройство, класс и расширитель</t>
         </is>
       </c>
       <c r="C659" s="29" t="inlineStr">
         <is>
-          <t>монтажная корзина платформа для вилочных погрузчиков</t>
+          <t>каретка на вилочный погрузчик</t>
         </is>
       </c>
       <c r="D659" s="28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E659" s="28" t="n">
         <v>6</v>
@@ -17997,16 +18123,16 @@
       </c>
       <c r="B660" s="29" t="inlineStr">
         <is>
-          <t>Монтажная платформа и корзина для вилочного погрузчика</t>
+          <t>Каретка вилочного погрузчика: устройство, класс и расширитель</t>
         </is>
       </c>
       <c r="C660" s="29" t="inlineStr">
         <is>
-          <t>монтажная платформа для вилочного погрузчика купить в москве</t>
+          <t>свободный ход каретки вилочного погрузчика это</t>
         </is>
       </c>
       <c r="D660" s="28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E660" s="28" t="n">
         <v>7</v>
@@ -18018,16 +18144,16 @@
       </c>
       <c r="B661" s="29" t="inlineStr">
         <is>
-          <t>Монтажная платформа и корзина для вилочного погрузчика</t>
+          <t>Каретка вилочного погрузчика: устройство, класс и расширитель</t>
         </is>
       </c>
       <c r="C661" s="29" t="inlineStr">
         <is>
-          <t>монтажная платформа для вилочного погрузчика купить</t>
+          <t>устройство каретки вилочного погрузчика</t>
         </is>
       </c>
       <c r="D661" s="28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E661" s="28" t="n">
         <v>8</v>
@@ -18039,16 +18165,16 @@
       </c>
       <c r="B662" s="29" t="inlineStr">
         <is>
-          <t>Монтажная платформа и корзина для вилочного погрузчика</t>
+          <t>Каретка вилочного погрузчика: устройство, класс и расширитель</t>
         </is>
       </c>
       <c r="C662" s="29" t="inlineStr">
         <is>
-          <t>монтажная платформа для вилочного погрузчика руководство по эксплуатации</t>
+          <t>смещение каретки на вилочном погрузчике</t>
         </is>
       </c>
       <c r="D662" s="28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E662" s="28" t="n">
         <v>9</v>
@@ -18056,23 +18182,23 @@
     </row>
     <row r="663">
       <c r="A663" s="28" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B663" s="29" t="inlineStr">
         <is>
-          <t>Вилы для вилочного погрузчика: какие бывают</t>
+          <t>Каретка вилочного погрузчика: устройство, класс и расширитель</t>
         </is>
       </c>
       <c r="C663" s="29" t="inlineStr">
         <is>
-          <t>купить вилы на вилочный погрузчик</t>
+          <t>смещение каретки на вилочном погрузчике что это</t>
         </is>
       </c>
       <c r="D663" s="28" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="E663" s="28" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="664">
@@ -18081,19 +18207,19 @@
       </c>
       <c r="B664" s="29" t="inlineStr">
         <is>
-          <t>Вилы для вилочного погрузчика: какие бывают</t>
+          <t>Монтажная платформа и корзина для вилочного погрузчика</t>
         </is>
       </c>
       <c r="C664" s="29" t="inlineStr">
         <is>
-          <t>вилы для вилочного погрузчика</t>
+          <t>монтажная платформа для вилочного погрузчика</t>
         </is>
       </c>
       <c r="D664" s="28" t="n">
-        <v>12</v>
+        <v>43</v>
       </c>
       <c r="E664" s="28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="665">
@@ -18102,19 +18228,19 @@
       </c>
       <c r="B665" s="29" t="inlineStr">
         <is>
-          <t>Вилы для вилочного погрузчика: какие бывают</t>
+          <t>Монтажная платформа и корзина для вилочного погрузчика</t>
         </is>
       </c>
       <c r="C665" s="29" t="inlineStr">
         <is>
-          <t>вилы погрузчика вилочного погрузчика</t>
+          <t>монтажная корзина для вилочного погрузчика</t>
         </is>
       </c>
       <c r="D665" s="28" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="E665" s="28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="666">
@@ -18123,19 +18249,19 @@
       </c>
       <c r="B666" s="29" t="inlineStr">
         <is>
-          <t>Вилы для вилочного погрузчика: какие бывают</t>
+          <t>Монтажная платформа и корзина для вилочного погрузчика</t>
         </is>
       </c>
       <c r="C666" s="29" t="inlineStr">
         <is>
-          <t>вилы для вилочного погрузчика купить</t>
+          <t>люлька монтажная платформа для вилочного погрузчика</t>
         </is>
       </c>
       <c r="D666" s="28" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E666" s="28" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="667">
@@ -18144,19 +18270,19 @@
       </c>
       <c r="B667" s="29" t="inlineStr">
         <is>
-          <t>Вилы для вилочного погрузчика: какие бывают</t>
+          <t>Монтажная платформа и корзина для вилочного погрузчика</t>
         </is>
       </c>
       <c r="C667" s="29" t="inlineStr">
         <is>
-          <t>вилы на вилочный погрузчик</t>
+          <t>монтажная корзина для вилочных погрузчиков</t>
         </is>
       </c>
       <c r="D667" s="28" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E667" s="28" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="668">
@@ -18165,19 +18291,19 @@
       </c>
       <c r="B668" s="29" t="inlineStr">
         <is>
-          <t>Вилы для вилочного погрузчика: какие бывают</t>
+          <t>Монтажная платформа и корзина для вилочного погрузчика</t>
         </is>
       </c>
       <c r="C668" s="29" t="inlineStr">
         <is>
-          <t>вилы на вилочный погрузчик бу</t>
+          <t>монтажная платформа для вилочного погрузчика км2</t>
         </is>
       </c>
       <c r="D668" s="28" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E668" s="28" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="669">
@@ -18186,19 +18312,19 @@
       </c>
       <c r="B669" s="29" t="inlineStr">
         <is>
-          <t>Вилы для вилочного погрузчика: какие бывают</t>
+          <t>Монтажная платформа и корзина для вилочного погрузчика</t>
         </is>
       </c>
       <c r="C669" s="29" t="inlineStr">
         <is>
-          <t>вилы вилочного погрузчика</t>
+          <t>монтажная корзина платформа для вилочных погрузчиков</t>
         </is>
       </c>
       <c r="D669" s="28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E669" s="28" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="670">
@@ -18207,19 +18333,19 @@
       </c>
       <c r="B670" s="29" t="inlineStr">
         <is>
-          <t>Вилы для вилочного погрузчика: какие бывают</t>
+          <t>Монтажная платформа и корзина для вилочного погрузчика</t>
         </is>
       </c>
       <c r="C670" s="29" t="inlineStr">
         <is>
-          <t>вилы на вилочный погрузчик 2 метра</t>
+          <t>монтажная платформа для вилочного погрузчика купить в москве</t>
         </is>
       </c>
       <c r="D670" s="28" t="n">
         <v>2</v>
       </c>
       <c r="E670" s="28" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="671">
@@ -18228,19 +18354,19 @@
       </c>
       <c r="B671" s="29" t="inlineStr">
         <is>
-          <t>Вилы для вилочного погрузчика: какие бывают</t>
+          <t>Монтажная платформа и корзина для вилочного погрузчика</t>
         </is>
       </c>
       <c r="C671" s="29" t="inlineStr">
         <is>
-          <t>вилы на вилочный погрузчик купить в спб</t>
+          <t>монтажная платформа для вилочного погрузчика купить</t>
         </is>
       </c>
       <c r="D671" s="28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E671" s="28" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="672">
@@ -18249,19 +18375,19 @@
       </c>
       <c r="B672" s="29" t="inlineStr">
         <is>
-          <t>Вилы для вилочного погрузчика: какие бывают</t>
+          <t>Монтажная платформа и корзина для вилочного погрузчика</t>
         </is>
       </c>
       <c r="C672" s="29" t="inlineStr">
         <is>
-          <t>вилы для автопогрузчика</t>
+          <t>монтажная платформа для вилочного погрузчика руководство по эксплуатации</t>
         </is>
       </c>
       <c r="D672" s="28" t="n">
         <v>1</v>
       </c>
       <c r="E672" s="28" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="673">
@@ -18270,16 +18396,16 @@
       </c>
       <c r="B673" s="29" t="inlineStr">
         <is>
-          <t>Двигатель вилочного погрузчика: ресурс и обслуживание</t>
+          <t>Вилы для вилочного погрузчика: какие бывают</t>
         </is>
       </c>
       <c r="C673" s="29" t="inlineStr">
         <is>
-          <t>двигатель вилочного погрузчика</t>
+          <t>купить вилы на вилочный погрузчик</t>
         </is>
       </c>
       <c r="D673" s="28" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="E673" s="28" t="n">
         <v>1</v>
@@ -18291,16 +18417,16 @@
       </c>
       <c r="B674" s="29" t="inlineStr">
         <is>
-          <t>Двигатель вилочного погрузчика: ресурс и обслуживание</t>
+          <t>Вилы для вилочного погрузчика: какие бывают</t>
         </is>
       </c>
       <c r="C674" s="29" t="inlineStr">
         <is>
-          <t>двигатель для вилочного погрузчика</t>
+          <t>вилы для вилочного погрузчика</t>
         </is>
       </c>
       <c r="D674" s="28" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E674" s="28" t="n">
         <v>2</v>
@@ -18312,16 +18438,16 @@
       </c>
       <c r="B675" s="29" t="inlineStr">
         <is>
-          <t>Двигатель вилочного погрузчика: ресурс и обслуживание</t>
+          <t>Вилы для вилочного погрузчика: какие бывают</t>
         </is>
       </c>
       <c r="C675" s="29" t="inlineStr">
         <is>
-          <t>электромотор от вилочного погрузчика</t>
+          <t>вилы погрузчика вилочного погрузчика</t>
         </is>
       </c>
       <c r="D675" s="28" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E675" s="28" t="n">
         <v>3</v>
@@ -18333,16 +18459,16 @@
       </c>
       <c r="B676" s="29" t="inlineStr">
         <is>
-          <t>Двигатель вилочного погрузчика: ресурс и обслуживание</t>
+          <t>Вилы для вилочного погрузчика: какие бывают</t>
         </is>
       </c>
       <c r="C676" s="29" t="inlineStr">
         <is>
-          <t>погрузчик вилочный мощность двигателя</t>
+          <t>вилы для вилочного погрузчика купить</t>
         </is>
       </c>
       <c r="D676" s="28" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E676" s="28" t="n">
         <v>4</v>
@@ -18354,16 +18480,16 @@
       </c>
       <c r="B677" s="29" t="inlineStr">
         <is>
-          <t>Двигатель вилочного погрузчика: ресурс и обслуживание</t>
+          <t>Вилы для вилочного погрузчика: какие бывают</t>
         </is>
       </c>
       <c r="C677" s="29" t="inlineStr">
         <is>
-          <t>двигатель на вилочный погрузчик</t>
+          <t>вилы на вилочный погрузчик</t>
         </is>
       </c>
       <c r="D677" s="28" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E677" s="28" t="n">
         <v>5</v>
@@ -18375,16 +18501,16 @@
       </c>
       <c r="B678" s="29" t="inlineStr">
         <is>
-          <t>Двигатель вилочного погрузчика: ресурс и обслуживание</t>
+          <t>Вилы для вилочного погрузчика: какие бывают</t>
         </is>
       </c>
       <c r="C678" s="29" t="inlineStr">
         <is>
-          <t>электродвигатель для вилочного погрузчика</t>
+          <t>вилы на вилочный погрузчик бу</t>
         </is>
       </c>
       <c r="D678" s="28" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E678" s="28" t="n">
         <v>6</v>
@@ -18396,16 +18522,16 @@
       </c>
       <c r="B679" s="29" t="inlineStr">
         <is>
-          <t>Двигатель вилочного погрузчика: ресурс и обслуживание</t>
+          <t>Вилы для вилочного погрузчика: какие бывают</t>
         </is>
       </c>
       <c r="C679" s="29" t="inlineStr">
         <is>
-          <t>дизельный двигатель на погрузчик вилочный</t>
+          <t>вилы вилочного погрузчика</t>
         </is>
       </c>
       <c r="D679" s="28" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E679" s="28" t="n">
         <v>7</v>
@@ -18417,16 +18543,16 @@
       </c>
       <c r="B680" s="29" t="inlineStr">
         <is>
-          <t>Двигатель вилочного погрузчика: ресурс и обслуживание</t>
+          <t>Вилы для вилочного погрузчика: какие бывают</t>
         </is>
       </c>
       <c r="C680" s="29" t="inlineStr">
         <is>
-          <t>вилочный погрузчик с москвичевским двигателем</t>
+          <t>вилы на вилочный погрузчик 2 метра</t>
         </is>
       </c>
       <c r="D680" s="28" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E680" s="28" t="n">
         <v>8</v>
@@ -18438,16 +18564,16 @@
       </c>
       <c r="B681" s="29" t="inlineStr">
         <is>
-          <t>Двигатель вилочного погрузчика: ресурс и обслуживание</t>
+          <t>Вилы для вилочного погрузчика: какие бывают</t>
         </is>
       </c>
       <c r="C681" s="29" t="inlineStr">
         <is>
-          <t>электродвигатель вилочного погрузчика</t>
+          <t>вилы на вилочный погрузчик купить в спб</t>
         </is>
       </c>
       <c r="D681" s="28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E681" s="28" t="n">
         <v>9</v>
@@ -18459,16 +18585,16 @@
       </c>
       <c r="B682" s="29" t="inlineStr">
         <is>
-          <t>Двигатель вилочного погрузчика: ресурс и обслуживание</t>
+          <t>Вилы для вилочного погрузчика: какие бывают</t>
         </is>
       </c>
       <c r="C682" s="29" t="inlineStr">
         <is>
-          <t>двигатель автопогрузчика</t>
+          <t>вилы для автопогрузчика</t>
         </is>
       </c>
       <c r="D682" s="28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E682" s="28" t="n">
         <v>10</v>
@@ -18480,16 +18606,16 @@
       </c>
       <c r="B683" s="29" t="inlineStr">
         <is>
-          <t>Каретка бокового смещения (сайдшифт) для вилочного погрузчика</t>
+          <t>Двигатель вилочного погрузчика: ресурс и обслуживание</t>
         </is>
       </c>
       <c r="C683" s="29" t="inlineStr">
         <is>
-          <t>каретка вилочного погрузчика</t>
+          <t>двигатель вилочного погрузчика</t>
         </is>
       </c>
       <c r="D683" s="28" t="n">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="E683" s="28" t="n">
         <v>1</v>
@@ -18501,16 +18627,16 @@
       </c>
       <c r="B684" s="29" t="inlineStr">
         <is>
-          <t>Каретка бокового смещения (сайдшифт) для вилочного погрузчика</t>
+          <t>Двигатель вилочного погрузчика: ресурс и обслуживание</t>
         </is>
       </c>
       <c r="C684" s="29" t="inlineStr">
         <is>
-          <t>каретка для вилочного погрузчика</t>
+          <t>двигатель для вилочного погрузчика</t>
         </is>
       </c>
       <c r="D684" s="28" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E684" s="28" t="n">
         <v>2</v>
@@ -18522,16 +18648,16 @@
       </c>
       <c r="B685" s="29" t="inlineStr">
         <is>
-          <t>Каретка бокового смещения (сайдшифт) для вилочного погрузчика</t>
+          <t>Двигатель вилочного погрузчика: ресурс и обслуживание</t>
         </is>
       </c>
       <c r="C685" s="29" t="inlineStr">
         <is>
-          <t>каретка бокового смещения для вилочного погрузчика</t>
+          <t>электромотор от вилочного погрузчика</t>
         </is>
       </c>
       <c r="D685" s="28" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E685" s="28" t="n">
         <v>3</v>
@@ -18543,16 +18669,16 @@
       </c>
       <c r="B686" s="29" t="inlineStr">
         <is>
-          <t>Каретка бокового смещения (сайдшифт) для вилочного погрузчика</t>
+          <t>Двигатель вилочного погрузчика: ресурс и обслуживание</t>
         </is>
       </c>
       <c r="C686" s="29" t="inlineStr">
         <is>
-          <t>каретка на вилочный погрузчик</t>
+          <t>погрузчик вилочный мощность двигателя</t>
         </is>
       </c>
       <c r="D686" s="28" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E686" s="28" t="n">
         <v>4</v>
@@ -18564,16 +18690,16 @@
       </c>
       <c r="B687" s="29" t="inlineStr">
         <is>
-          <t>Каретка бокового смещения (сайдшифт) для вилочного погрузчика</t>
+          <t>Двигатель вилочного погрузчика: ресурс и обслуживание</t>
         </is>
       </c>
       <c r="C687" s="29" t="inlineStr">
         <is>
-          <t>каретка бокового смещения для вилочного погрузчика что это</t>
+          <t>двигатель на вилочный погрузчик</t>
         </is>
       </c>
       <c r="D687" s="28" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E687" s="28" t="n">
         <v>5</v>
@@ -18585,16 +18711,16 @@
       </c>
       <c r="B688" s="29" t="inlineStr">
         <is>
-          <t>Каретка бокового смещения (сайдшифт) для вилочного погрузчика</t>
+          <t>Двигатель вилочного погрузчика: ресурс и обслуживание</t>
         </is>
       </c>
       <c r="C688" s="29" t="inlineStr">
         <is>
-          <t>каретка автопогрузчика</t>
+          <t>электродвигатель для вилочного погрузчика</t>
         </is>
       </c>
       <c r="D688" s="28" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E688" s="28" t="n">
         <v>6</v>
@@ -18606,16 +18732,16 @@
       </c>
       <c r="B689" s="29" t="inlineStr">
         <is>
-          <t>Каретка бокового смещения (сайдшифт) для вилочного погрузчика</t>
+          <t>Двигатель вилочного погрузчика: ресурс и обслуживание</t>
         </is>
       </c>
       <c r="C689" s="29" t="inlineStr">
         <is>
-          <t>поворотная каретка на вилочный погрузчик</t>
+          <t>дизельный двигатель на погрузчик вилочный</t>
         </is>
       </c>
       <c r="D689" s="28" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E689" s="28" t="n">
         <v>7</v>
@@ -18627,16 +18753,16 @@
       </c>
       <c r="B690" s="29" t="inlineStr">
         <is>
-          <t>Каретка бокового смещения (сайдшифт) для вилочного погрузчика</t>
+          <t>Двигатель вилочного погрузчика: ресурс и обслуживание</t>
         </is>
       </c>
       <c r="C690" s="29" t="inlineStr">
         <is>
-          <t>смещающаяся каретка на вилочном погрузчике</t>
+          <t>вилочный погрузчик с москвичевским двигателем</t>
         </is>
       </c>
       <c r="D690" s="28" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E690" s="28" t="n">
         <v>8</v>
@@ -18648,16 +18774,16 @@
       </c>
       <c r="B691" s="29" t="inlineStr">
         <is>
-          <t>Каретка бокового смещения (сайдшифт) для вилочного погрузчика</t>
+          <t>Двигатель вилочного погрузчика: ресурс и обслуживание</t>
         </is>
       </c>
       <c r="C691" s="29" t="inlineStr">
         <is>
-          <t>широкая каретка для вилочного погрузчика</t>
+          <t>электродвигатель вилочного погрузчика</t>
         </is>
       </c>
       <c r="D691" s="28" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E691" s="28" t="n">
         <v>9</v>
@@ -18669,16 +18795,16 @@
       </c>
       <c r="B692" s="29" t="inlineStr">
         <is>
-          <t>Каретка бокового смещения (сайдшифт) для вилочного погрузчика</t>
+          <t>Двигатель вилочного погрузчика: ресурс и обслуживание</t>
         </is>
       </c>
       <c r="C692" s="29" t="inlineStr">
         <is>
-          <t>каретка на автопогрузчик</t>
+          <t>двигатель автопогрузчика</t>
         </is>
       </c>
       <c r="D692" s="28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E692" s="28" t="n">
         <v>10</v>
@@ -19110,16 +19236,16 @@
       </c>
       <c r="B713" s="29" t="inlineStr">
         <is>
-          <t>Цепь и ролики мачты вилочного погрузчика</t>
+          <t>Рама и шасси вилочного погрузчика</t>
         </is>
       </c>
       <c r="C713" s="29" t="inlineStr">
         <is>
-          <t>цепь для вилочного погрузчика</t>
+          <t>рулевой мост вилочного погрузчика</t>
         </is>
       </c>
       <c r="D713" s="28" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E713" s="28" t="n">
         <v>1</v>
@@ -19131,16 +19257,16 @@
       </c>
       <c r="B714" s="29" t="inlineStr">
         <is>
-          <t>Цепь и ролики мачты вилочного погрузчика</t>
+          <t>Рама и шасси вилочного погрузчика</t>
         </is>
       </c>
       <c r="C714" s="29" t="inlineStr">
         <is>
-          <t>цепь мачты вилочного погрузчика</t>
+          <t>рама вилочного погрузчика</t>
         </is>
       </c>
       <c r="D714" s="28" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E714" s="28" t="n">
         <v>2</v>
@@ -19152,16 +19278,16 @@
       </c>
       <c r="B715" s="29" t="inlineStr">
         <is>
-          <t>Цепь и ролики мачты вилочного погрузчика</t>
+          <t>Рама и шасси вилочного погрузчика</t>
         </is>
       </c>
       <c r="C715" s="29" t="inlineStr">
         <is>
-          <t>цепь на вилочный погрузчик</t>
+          <t>ведущий мост вилочного погрузчика</t>
         </is>
       </c>
       <c r="D715" s="28" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E715" s="28" t="n">
         <v>3</v>
@@ -19173,16 +19299,16 @@
       </c>
       <c r="B716" s="29" t="inlineStr">
         <is>
-          <t>Цепь и ролики мачты вилочного погрузчика</t>
+          <t>Рама и шасси вилочного погрузчика</t>
         </is>
       </c>
       <c r="C716" s="29" t="inlineStr">
         <is>
-          <t>цепь для автопогрузчика</t>
+          <t>рама погрузчика вилочного погрузчика</t>
         </is>
       </c>
       <c r="D716" s="28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E716" s="28" t="n">
         <v>4</v>
@@ -19194,16 +19320,16 @@
       </c>
       <c r="B717" s="29" t="inlineStr">
         <is>
-          <t>Цепь и ролики мачты вилочного погрузчика</t>
+          <t>Рама и шасси вилочного погрузчика</t>
         </is>
       </c>
       <c r="C717" s="29" t="inlineStr">
         <is>
-          <t>цепь противоскольжения для вилочного погрузчика</t>
+          <t>номер рамы вилочного погрузчика</t>
         </is>
       </c>
       <c r="D717" s="28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E717" s="28" t="n">
         <v>5</v>
@@ -19215,16 +19341,16 @@
       </c>
       <c r="B718" s="29" t="inlineStr">
         <is>
-          <t>Цепь и ролики мачты вилочного погрузчика</t>
+          <t>Рама и шасси вилочного погрузчика</t>
         </is>
       </c>
       <c r="C718" s="29" t="inlineStr">
         <is>
-          <t>цепь мачты для вилочного погрузчика</t>
+          <t>ведущий мост погрузчика вилочного погрузчика</t>
         </is>
       </c>
       <c r="D718" s="28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E718" s="28" t="n">
         <v>6</v>
@@ -19236,16 +19362,16 @@
       </c>
       <c r="B719" s="29" t="inlineStr">
         <is>
-          <t>Цепь и ролики мачты вилочного погрузчика</t>
+          <t>Рама и шасси вилочного погрузчика</t>
         </is>
       </c>
       <c r="C719" s="29" t="inlineStr">
         <is>
-          <t>цепь автопогрузчика</t>
+          <t>мост вилочного погрузчика</t>
         </is>
       </c>
       <c r="D719" s="28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E719" s="28" t="n">
         <v>7</v>
@@ -19257,16 +19383,16 @@
       </c>
       <c r="B720" s="29" t="inlineStr">
         <is>
-          <t>Цепь и ролики мачты вилочного погрузчика</t>
+          <t>Рама и шасси вилочного погрузчика</t>
         </is>
       </c>
       <c r="C720" s="29" t="inlineStr">
         <is>
-          <t>цепь погрузчик вилочный</t>
+          <t>управляемый мост вилочного погрузчика</t>
         </is>
       </c>
       <c r="D720" s="28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E720" s="28" t="n">
         <v>8</v>
@@ -19278,16 +19404,16 @@
       </c>
       <c r="B721" s="29" t="inlineStr">
         <is>
-          <t>Цепь и ролики мачты вилочного погрузчика</t>
+          <t>Рама и шасси вилочного погрузчика</t>
         </is>
       </c>
       <c r="C721" s="29" t="inlineStr">
         <is>
-          <t>цепь на автопогрузчик</t>
+          <t>задний мост вилочного погрузчика</t>
         </is>
       </c>
       <c r="D721" s="28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E721" s="28" t="n">
         <v>9</v>
@@ -19299,16 +19425,16 @@
       </c>
       <c r="B722" s="29" t="inlineStr">
         <is>
-          <t>Цепь и ролики мачты вилочного погрузчика</t>
+          <t>Рама и шасси вилочного погрузчика</t>
         </is>
       </c>
       <c r="C722" s="29" t="inlineStr">
         <is>
-          <t>цепь для вилочных погрузчиков</t>
+          <t>передний мост вилочного погрузчика</t>
         </is>
       </c>
       <c r="D722" s="28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E722" s="28" t="n">
         <v>10</v>
@@ -19320,16 +19446,16 @@
       </c>
       <c r="B723" s="29" t="inlineStr">
         <is>
-          <t>Регистрация вилочного погрузчика в Гостехнадзоре: что нужно знать владельцу</t>
+          <t>Цепь и ролики мачты вилочного погрузчика</t>
         </is>
       </c>
       <c r="C723" s="29" t="inlineStr">
         <is>
-          <t>какие права нужны на вилочный погрузчик</t>
+          <t>цепь для вилочного погрузчика</t>
         </is>
       </c>
       <c r="D723" s="28" t="n">
-        <v>119</v>
+        <v>11</v>
       </c>
       <c r="E723" s="28" t="n">
         <v>1</v>
@@ -19341,16 +19467,16 @@
       </c>
       <c r="B724" s="29" t="inlineStr">
         <is>
-          <t>Регистрация вилочного погрузчика в Гостехнадзоре: что нужно знать владельцу</t>
+          <t>Цепь и ролики мачты вилочного погрузчика</t>
         </is>
       </c>
       <c r="C724" s="29" t="inlineStr">
         <is>
-          <t>к какой группе ос относится вилочный погрузчик</t>
+          <t>цепь мачты вилочного погрузчика</t>
         </is>
       </c>
       <c r="D724" s="28" t="n">
-        <v>70</v>
+        <v>7</v>
       </c>
       <c r="E724" s="28" t="n">
         <v>2</v>
@@ -19362,16 +19488,16 @@
       </c>
       <c r="B725" s="29" t="inlineStr">
         <is>
-          <t>Регистрация вилочного погрузчика в Гостехнадзоре: что нужно знать владельцу</t>
+          <t>Цепь и ролики мачты вилочного погрузчика</t>
         </is>
       </c>
       <c r="C725" s="29" t="inlineStr">
         <is>
-          <t>какие права нужны для вилочного погрузчика</t>
+          <t>цепь на вилочный погрузчик</t>
         </is>
       </c>
       <c r="D725" s="28" t="n">
-        <v>37</v>
+        <v>4</v>
       </c>
       <c r="E725" s="28" t="n">
         <v>3</v>
@@ -19383,16 +19509,16 @@
       </c>
       <c r="B726" s="29" t="inlineStr">
         <is>
-          <t>Регистрация вилочного погрузчика в Гостехнадзоре: что нужно знать владельцу</t>
+          <t>Цепь и ролики мачты вилочного погрузчика</t>
         </is>
       </c>
       <c r="C726" s="29" t="inlineStr">
         <is>
-          <t>как поставить на учет вилочный погрузчик</t>
+          <t>цепь для автопогрузчика</t>
         </is>
       </c>
       <c r="D726" s="28" t="n">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="E726" s="28" t="n">
         <v>4</v>
@@ -19404,16 +19530,16 @@
       </c>
       <c r="B727" s="29" t="inlineStr">
         <is>
-          <t>Регистрация вилочного погрузчика в Гостехнадзоре: что нужно знать владельцу</t>
+          <t>Цепь и ролики мачты вилочного погрузчика</t>
         </is>
       </c>
       <c r="C727" s="29" t="inlineStr">
         <is>
-          <t>какие права нужны на кару вилочный погрузчик</t>
+          <t>цепь противоскольжения для вилочного погрузчика</t>
         </is>
       </c>
       <c r="D727" s="28" t="n">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="E727" s="28" t="n">
         <v>5</v>
@@ -19425,16 +19551,16 @@
       </c>
       <c r="B728" s="29" t="inlineStr">
         <is>
-          <t>Регистрация вилочного погрузчика в Гостехнадзоре: что нужно знать владельцу</t>
+          <t>Цепь и ролики мачты вилочного погрузчика</t>
         </is>
       </c>
       <c r="C728" s="29" t="inlineStr">
         <is>
-          <t>какие права нужны для управления погрузчиком вилочным</t>
+          <t>цепь мачты для вилочного погрузчика</t>
         </is>
       </c>
       <c r="D728" s="28" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="E728" s="28" t="n">
         <v>6</v>
@@ -19446,16 +19572,16 @@
       </c>
       <c r="B729" s="29" t="inlineStr">
         <is>
-          <t>Регистрация вилочного погрузчика в Гостехнадзоре: что нужно знать владельцу</t>
+          <t>Цепь и ролики мачты вилочного погрузчика</t>
         </is>
       </c>
       <c r="C729" s="29" t="inlineStr">
         <is>
-          <t>какие права нужны на вилочный погрузчик на складе</t>
+          <t>цепь автопогрузчика</t>
         </is>
       </c>
       <c r="D729" s="28" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="E729" s="28" t="n">
         <v>7</v>
@@ -19467,16 +19593,16 @@
       </c>
       <c r="B730" s="29" t="inlineStr">
         <is>
-          <t>Регистрация вилочного погрузчика в Гостехнадзоре: что нужно знать владельцу</t>
+          <t>Цепь и ролики мачты вилочного погрузчика</t>
         </is>
       </c>
       <c r="C730" s="29" t="inlineStr">
         <is>
-          <t>как поставить вилочный погрузчик на учет в гостехнадзоре</t>
+          <t>цепь погрузчик вилочный</t>
         </is>
       </c>
       <c r="D730" s="28" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="E730" s="28" t="n">
         <v>8</v>
@@ -19488,16 +19614,16 @@
       </c>
       <c r="B731" s="29" t="inlineStr">
         <is>
-          <t>Регистрация вилочного погрузчика в Гостехнадзоре: что нужно знать владельцу</t>
+          <t>Цепь и ролики мачты вилочного погрузчика</t>
         </is>
       </c>
       <c r="C731" s="29" t="inlineStr">
         <is>
-          <t>нужно ли ставить на учет вилочный погрузчик</t>
+          <t>цепь на автопогрузчик</t>
         </is>
       </c>
       <c r="D731" s="28" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E731" s="28" t="n">
         <v>9</v>
@@ -19509,16 +19635,16 @@
       </c>
       <c r="B732" s="29" t="inlineStr">
         <is>
-          <t>Регистрация вилочного погрузчика в Гостехнадзоре: что нужно знать владельцу</t>
+          <t>Цепь и ролики мачты вилочного погрузчика</t>
         </is>
       </c>
       <c r="C732" s="29" t="inlineStr">
         <is>
-          <t>вилочный погрузчик какие права нужны</t>
+          <t>цепь для вилочных погрузчиков</t>
         </is>
       </c>
       <c r="D732" s="28" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E732" s="28" t="n">
         <v>10</v>
@@ -19530,16 +19656,16 @@
       </c>
       <c r="B733" s="29" t="inlineStr">
         <is>
-          <t>Аренда вилочного погрузчика: когда выгоднее покупки</t>
+          <t>Противовес вилочного погрузчика</t>
         </is>
       </c>
       <c r="C733" s="29" t="inlineStr">
         <is>
-          <t>аренда вилочного погрузчика</t>
+          <t>как снять противовес с вилочного погрузчика</t>
         </is>
       </c>
       <c r="D733" s="28" t="n">
-        <v>270</v>
+        <v>9</v>
       </c>
       <c r="E733" s="28" t="n">
         <v>1</v>
@@ -19551,16 +19677,16 @@
       </c>
       <c r="B734" s="29" t="inlineStr">
         <is>
-          <t>Аренда вилочного погрузчика: когда выгоднее покупки</t>
+          <t>Противовес вилочного погрузчика</t>
         </is>
       </c>
       <c r="C734" s="29" t="inlineStr">
         <is>
-          <t>аренда погрузчика вилочного цена</t>
+          <t>из чего сделан противовес на вилочном погрузчике</t>
         </is>
       </c>
       <c r="D734" s="28" t="n">
-        <v>65</v>
+        <v>5</v>
       </c>
       <c r="E734" s="28" t="n">
         <v>2</v>
@@ -19572,16 +19698,16 @@
       </c>
       <c r="B735" s="29" t="inlineStr">
         <is>
-          <t>Аренда вилочного погрузчика: когда выгоднее покупки</t>
+          <t>Противовес вилочного погрузчика</t>
         </is>
       </c>
       <c r="C735" s="29" t="inlineStr">
         <is>
-          <t>погрузчик вилочный в аренду</t>
+          <t>купить противовес для вилочного погрузчика</t>
         </is>
       </c>
       <c r="D735" s="28" t="n">
-        <v>64</v>
+        <v>3</v>
       </c>
       <c r="E735" s="28" t="n">
         <v>3</v>
@@ -19593,16 +19719,16 @@
       </c>
       <c r="B736" s="29" t="inlineStr">
         <is>
-          <t>Аренда вилочного погрузчика: когда выгоднее покупки</t>
+          <t>Противовес вилочного погрузчика</t>
         </is>
       </c>
       <c r="C736" s="29" t="inlineStr">
         <is>
-          <t>аренда вилочных погрузчиков</t>
+          <t>противовес погрузчика вилочного</t>
         </is>
       </c>
       <c r="D736" s="28" t="n">
-        <v>57</v>
+        <v>1</v>
       </c>
       <c r="E736" s="28" t="n">
         <v>4</v>
@@ -19614,16 +19740,16 @@
       </c>
       <c r="B737" s="29" t="inlineStr">
         <is>
-          <t>Аренда вилочного погрузчика: когда выгоднее покупки</t>
+          <t>Противовес вилочного погрузчика</t>
         </is>
       </c>
       <c r="C737" s="29" t="inlineStr">
         <is>
-          <t>аренда погрузчика вилочного в спб</t>
+          <t>вилочный погрузчик с противовесом</t>
         </is>
       </c>
       <c r="D737" s="28" t="n">
-        <v>49</v>
+        <v>1</v>
       </c>
       <c r="E737" s="28" t="n">
         <v>5</v>
@@ -19635,16 +19761,16 @@
       </c>
       <c r="B738" s="29" t="inlineStr">
         <is>
-          <t>Аренда вилочного погрузчика: когда выгоднее покупки</t>
+          <t>Противовес вилочного погрузчика</t>
         </is>
       </c>
       <c r="C738" s="29" t="inlineStr">
         <is>
-          <t>аренда вилочного погрузчика спб</t>
+          <t>дополнительный противовес для вилочного погрузчика</t>
         </is>
       </c>
       <c r="D738" s="28" t="n">
-        <v>44</v>
+        <v>1</v>
       </c>
       <c r="E738" s="28" t="n">
         <v>6</v>
@@ -19656,16 +19782,16 @@
       </c>
       <c r="B739" s="29" t="inlineStr">
         <is>
-          <t>Аренда вилочного погрузчика: когда выгоднее покупки</t>
+          <t>Противовес вилочного погрузчика</t>
         </is>
       </c>
       <c r="C739" s="29" t="inlineStr">
         <is>
-          <t>аренда погрузчика вилочного москва</t>
+          <t>противовес на вилочный погрузчик купить</t>
         </is>
       </c>
       <c r="D739" s="28" t="n">
-        <v>42</v>
+        <v>1</v>
       </c>
       <c r="E739" s="28" t="n">
         <v>7</v>
@@ -19677,16 +19803,16 @@
       </c>
       <c r="B740" s="29" t="inlineStr">
         <is>
-          <t>Аренда вилочного погрузчика: когда выгоднее покупки</t>
+          <t>Противовес вилочного погрузчика</t>
         </is>
       </c>
       <c r="C740" s="29" t="inlineStr">
         <is>
-          <t>аренда вилочных погрузчиков в москве и московской области</t>
+          <t>противовес автопогрузчика</t>
         </is>
       </c>
       <c r="D740" s="28" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="E740" s="28" t="n">
         <v>8</v>
@@ -19698,16 +19824,16 @@
       </c>
       <c r="B741" s="29" t="inlineStr">
         <is>
-          <t>Аренда вилочного погрузчика: когда выгоднее покупки</t>
+          <t>Противовес вилочного погрузчика</t>
         </is>
       </c>
       <c r="C741" s="29" t="inlineStr">
         <is>
-          <t>аренда вилочных погрузчиков в москве</t>
+          <t>вилочный противовесный погрузчик</t>
         </is>
       </c>
       <c r="D741" s="28" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="E741" s="28" t="n">
         <v>9</v>
@@ -19719,18 +19845,606 @@
       </c>
       <c r="B742" s="29" t="inlineStr">
         <is>
+          <t>Противовес вилочного погрузчика</t>
+        </is>
+      </c>
+      <c r="C742" s="29" t="inlineStr">
+        <is>
+          <t>противовес на вилочный погрузчик</t>
+        </is>
+      </c>
+      <c r="D742" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E742" s="28" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" s="28" t="n">
+        <v>78</v>
+      </c>
+      <c r="B743" s="29" t="inlineStr">
+        <is>
+          <t>Каретка бокового смещения (сайдшифт) для вилочного погрузчика</t>
+        </is>
+      </c>
+      <c r="C743" s="29" t="inlineStr">
+        <is>
+          <t>каретка бокового смещения для вилочного погрузчика</t>
+        </is>
+      </c>
+      <c r="D743" s="28" t="n">
+        <v>10</v>
+      </c>
+      <c r="E743" s="28" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" s="28" t="n">
+        <v>78</v>
+      </c>
+      <c r="B744" s="29" t="inlineStr">
+        <is>
+          <t>Каретка бокового смещения (сайдшифт) для вилочного погрузчика</t>
+        </is>
+      </c>
+      <c r="C744" s="29" t="inlineStr">
+        <is>
+          <t>каретка бокового смещения для вилочного погрузчика что это</t>
+        </is>
+      </c>
+      <c r="D744" s="28" t="n">
+        <v>3</v>
+      </c>
+      <c r="E744" s="28" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" s="28" t="n">
+        <v>78</v>
+      </c>
+      <c r="B745" s="29" t="inlineStr">
+        <is>
+          <t>Каретка бокового смещения (сайдшифт) для вилочного погрузчика</t>
+        </is>
+      </c>
+      <c r="C745" s="29" t="inlineStr">
+        <is>
+          <t>сайдшифт на вилочном погрузчике</t>
+        </is>
+      </c>
+      <c r="D745" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E745" s="28" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" s="28" t="n">
+        <v>78</v>
+      </c>
+      <c r="B746" s="29" t="inlineStr">
+        <is>
+          <t>Каретка бокового смещения (сайдшифт) для вилочного погрузчика</t>
+        </is>
+      </c>
+      <c r="C746" s="29" t="inlineStr">
+        <is>
+          <t>вилочный погрузчик с сайдшифтом</t>
+        </is>
+      </c>
+      <c r="D746" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E746" s="28" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" s="28" t="n">
+        <v>78</v>
+      </c>
+      <c r="B747" s="29" t="inlineStr">
+        <is>
+          <t>Каретка бокового смещения (сайдшифт) для вилочного погрузчика</t>
+        </is>
+      </c>
+      <c r="C747" s="29" t="inlineStr">
+        <is>
+          <t>каретка бокового смещения вил автопогрузчика</t>
+        </is>
+      </c>
+      <c r="D747" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E747" s="28" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" s="28" t="n">
+        <v>78</v>
+      </c>
+      <c r="B748" s="29" t="inlineStr">
+        <is>
+          <t>Каретка бокового смещения (сайдшифт) для вилочного погрузчика</t>
+        </is>
+      </c>
+      <c r="C748" s="29" t="inlineStr">
+        <is>
+          <t>каретки бокового смещения для вилочных погрузчиков</t>
+        </is>
+      </c>
+      <c r="D748" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E748" s="28" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" s="28" t="n">
+        <v>78</v>
+      </c>
+      <c r="B749" s="29" t="inlineStr">
+        <is>
+          <t>Каретка бокового смещения (сайдшифт) для вилочного погрузчика</t>
+        </is>
+      </c>
+      <c r="C749" s="29" t="inlineStr">
+        <is>
+          <t>каретка бокового смещения для вилочного погрузчика это</t>
+        </is>
+      </c>
+      <c r="D749" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E749" s="28" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" s="28" t="n">
+        <v>78</v>
+      </c>
+      <c r="B750" s="29" t="inlineStr">
+        <is>
+          <t>Каретка бокового смещения (сайдшифт) для вилочного погрузчика</t>
+        </is>
+      </c>
+      <c r="C750" s="29" t="inlineStr">
+        <is>
+          <t>каретка бокового смещения для вилочного</t>
+        </is>
+      </c>
+      <c r="D750" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E750" s="28" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" s="28" t="n">
+        <v>79</v>
+      </c>
+      <c r="B751" s="29" t="inlineStr">
+        <is>
+          <t>Регистрация вилочного погрузчика в Гостехнадзоре: что нужно знать владельцу</t>
+        </is>
+      </c>
+      <c r="C751" s="29" t="inlineStr">
+        <is>
+          <t>какие права нужны на вилочный погрузчик</t>
+        </is>
+      </c>
+      <c r="D751" s="28" t="n">
+        <v>119</v>
+      </c>
+      <c r="E751" s="28" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="752">
+      <c r="A752" s="28" t="n">
+        <v>79</v>
+      </c>
+      <c r="B752" s="29" t="inlineStr">
+        <is>
+          <t>Регистрация вилочного погрузчика в Гостехнадзоре: что нужно знать владельцу</t>
+        </is>
+      </c>
+      <c r="C752" s="29" t="inlineStr">
+        <is>
+          <t>к какой группе ос относится вилочный погрузчик</t>
+        </is>
+      </c>
+      <c r="D752" s="28" t="n">
+        <v>70</v>
+      </c>
+      <c r="E752" s="28" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="753">
+      <c r="A753" s="28" t="n">
+        <v>79</v>
+      </c>
+      <c r="B753" s="29" t="inlineStr">
+        <is>
+          <t>Регистрация вилочного погрузчика в Гостехнадзоре: что нужно знать владельцу</t>
+        </is>
+      </c>
+      <c r="C753" s="29" t="inlineStr">
+        <is>
+          <t>какие права нужны для вилочного погрузчика</t>
+        </is>
+      </c>
+      <c r="D753" s="28" t="n">
+        <v>37</v>
+      </c>
+      <c r="E753" s="28" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="754">
+      <c r="A754" s="28" t="n">
+        <v>79</v>
+      </c>
+      <c r="B754" s="29" t="inlineStr">
+        <is>
+          <t>Регистрация вилочного погрузчика в Гостехнадзоре: что нужно знать владельцу</t>
+        </is>
+      </c>
+      <c r="C754" s="29" t="inlineStr">
+        <is>
+          <t>как поставить на учет вилочный погрузчик</t>
+        </is>
+      </c>
+      <c r="D754" s="28" t="n">
+        <v>27</v>
+      </c>
+      <c r="E754" s="28" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" s="28" t="n">
+        <v>79</v>
+      </c>
+      <c r="B755" s="29" t="inlineStr">
+        <is>
+          <t>Регистрация вилочного погрузчика в Гостехнадзоре: что нужно знать владельцу</t>
+        </is>
+      </c>
+      <c r="C755" s="29" t="inlineStr">
+        <is>
+          <t>какие права нужны на кару вилочный погрузчик</t>
+        </is>
+      </c>
+      <c r="D755" s="28" t="n">
+        <v>27</v>
+      </c>
+      <c r="E755" s="28" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="756">
+      <c r="A756" s="28" t="n">
+        <v>79</v>
+      </c>
+      <c r="B756" s="29" t="inlineStr">
+        <is>
+          <t>Регистрация вилочного погрузчика в Гостехнадзоре: что нужно знать владельцу</t>
+        </is>
+      </c>
+      <c r="C756" s="29" t="inlineStr">
+        <is>
+          <t>какие права нужны для управления погрузчиком вилочным</t>
+        </is>
+      </c>
+      <c r="D756" s="28" t="n">
+        <v>25</v>
+      </c>
+      <c r="E756" s="28" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="757">
+      <c r="A757" s="28" t="n">
+        <v>79</v>
+      </c>
+      <c r="B757" s="29" t="inlineStr">
+        <is>
+          <t>Регистрация вилочного погрузчика в Гостехнадзоре: что нужно знать владельцу</t>
+        </is>
+      </c>
+      <c r="C757" s="29" t="inlineStr">
+        <is>
+          <t>какие права нужны на вилочный погрузчик на складе</t>
+        </is>
+      </c>
+      <c r="D757" s="28" t="n">
+        <v>23</v>
+      </c>
+      <c r="E757" s="28" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="758">
+      <c r="A758" s="28" t="n">
+        <v>79</v>
+      </c>
+      <c r="B758" s="29" t="inlineStr">
+        <is>
+          <t>Регистрация вилочного погрузчика в Гостехнадзоре: что нужно знать владельцу</t>
+        </is>
+      </c>
+      <c r="C758" s="29" t="inlineStr">
+        <is>
+          <t>как поставить вилочный погрузчик на учет в гостехнадзоре</t>
+        </is>
+      </c>
+      <c r="D758" s="28" t="n">
+        <v>16</v>
+      </c>
+      <c r="E758" s="28" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="759">
+      <c r="A759" s="28" t="n">
+        <v>79</v>
+      </c>
+      <c r="B759" s="29" t="inlineStr">
+        <is>
+          <t>Регистрация вилочного погрузчика в Гостехнадзоре: что нужно знать владельцу</t>
+        </is>
+      </c>
+      <c r="C759" s="29" t="inlineStr">
+        <is>
+          <t>нужно ли ставить на учет вилочный погрузчик</t>
+        </is>
+      </c>
+      <c r="D759" s="28" t="n">
+        <v>12</v>
+      </c>
+      <c r="E759" s="28" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="760">
+      <c r="A760" s="28" t="n">
+        <v>79</v>
+      </c>
+      <c r="B760" s="29" t="inlineStr">
+        <is>
+          <t>Регистрация вилочного погрузчика в Гостехнадзоре: что нужно знать владельцу</t>
+        </is>
+      </c>
+      <c r="C760" s="29" t="inlineStr">
+        <is>
+          <t>вилочный погрузчик какие права нужны</t>
+        </is>
+      </c>
+      <c r="D760" s="28" t="n">
+        <v>9</v>
+      </c>
+      <c r="E760" s="28" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="761">
+      <c r="A761" s="28" t="n">
+        <v>80</v>
+      </c>
+      <c r="B761" s="29" t="inlineStr">
+        <is>
           <t>Аренда вилочного погрузчика: когда выгоднее покупки</t>
         </is>
       </c>
-      <c r="C742" s="29" t="inlineStr">
+      <c r="C761" s="29" t="inlineStr">
+        <is>
+          <t>аренда вилочного погрузчика</t>
+        </is>
+      </c>
+      <c r="D761" s="28" t="n">
+        <v>270</v>
+      </c>
+      <c r="E761" s="28" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="762">
+      <c r="A762" s="28" t="n">
+        <v>80</v>
+      </c>
+      <c r="B762" s="29" t="inlineStr">
+        <is>
+          <t>Аренда вилочного погрузчика: когда выгоднее покупки</t>
+        </is>
+      </c>
+      <c r="C762" s="29" t="inlineStr">
+        <is>
+          <t>аренда погрузчика вилочного цена</t>
+        </is>
+      </c>
+      <c r="D762" s="28" t="n">
+        <v>65</v>
+      </c>
+      <c r="E762" s="28" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="763">
+      <c r="A763" s="28" t="n">
+        <v>80</v>
+      </c>
+      <c r="B763" s="29" t="inlineStr">
+        <is>
+          <t>Аренда вилочного погрузчика: когда выгоднее покупки</t>
+        </is>
+      </c>
+      <c r="C763" s="29" t="inlineStr">
+        <is>
+          <t>погрузчик вилочный в аренду</t>
+        </is>
+      </c>
+      <c r="D763" s="28" t="n">
+        <v>64</v>
+      </c>
+      <c r="E763" s="28" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="764">
+      <c r="A764" s="28" t="n">
+        <v>80</v>
+      </c>
+      <c r="B764" s="29" t="inlineStr">
+        <is>
+          <t>Аренда вилочного погрузчика: когда выгоднее покупки</t>
+        </is>
+      </c>
+      <c r="C764" s="29" t="inlineStr">
+        <is>
+          <t>аренда вилочных погрузчиков</t>
+        </is>
+      </c>
+      <c r="D764" s="28" t="n">
+        <v>57</v>
+      </c>
+      <c r="E764" s="28" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="765">
+      <c r="A765" s="28" t="n">
+        <v>80</v>
+      </c>
+      <c r="B765" s="29" t="inlineStr">
+        <is>
+          <t>Аренда вилочного погрузчика: когда выгоднее покупки</t>
+        </is>
+      </c>
+      <c r="C765" s="29" t="inlineStr">
+        <is>
+          <t>аренда погрузчика вилочного в спб</t>
+        </is>
+      </c>
+      <c r="D765" s="28" t="n">
+        <v>49</v>
+      </c>
+      <c r="E765" s="28" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="766">
+      <c r="A766" s="28" t="n">
+        <v>80</v>
+      </c>
+      <c r="B766" s="29" t="inlineStr">
+        <is>
+          <t>Аренда вилочного погрузчика: когда выгоднее покупки</t>
+        </is>
+      </c>
+      <c r="C766" s="29" t="inlineStr">
+        <is>
+          <t>аренда вилочного погрузчика спб</t>
+        </is>
+      </c>
+      <c r="D766" s="28" t="n">
+        <v>44</v>
+      </c>
+      <c r="E766" s="28" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="767">
+      <c r="A767" s="28" t="n">
+        <v>80</v>
+      </c>
+      <c r="B767" s="29" t="inlineStr">
+        <is>
+          <t>Аренда вилочного погрузчика: когда выгоднее покупки</t>
+        </is>
+      </c>
+      <c r="C767" s="29" t="inlineStr">
+        <is>
+          <t>аренда погрузчика вилочного москва</t>
+        </is>
+      </c>
+      <c r="D767" s="28" t="n">
+        <v>42</v>
+      </c>
+      <c r="E767" s="28" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="768">
+      <c r="A768" s="28" t="n">
+        <v>80</v>
+      </c>
+      <c r="B768" s="29" t="inlineStr">
+        <is>
+          <t>Аренда вилочного погрузчика: когда выгоднее покупки</t>
+        </is>
+      </c>
+      <c r="C768" s="29" t="inlineStr">
+        <is>
+          <t>аренда вилочных погрузчиков в москве и московской области</t>
+        </is>
+      </c>
+      <c r="D768" s="28" t="n">
+        <v>35</v>
+      </c>
+      <c r="E768" s="28" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="769">
+      <c r="A769" s="28" t="n">
+        <v>80</v>
+      </c>
+      <c r="B769" s="29" t="inlineStr">
+        <is>
+          <t>Аренда вилочного погрузчика: когда выгоднее покупки</t>
+        </is>
+      </c>
+      <c r="C769" s="29" t="inlineStr">
+        <is>
+          <t>аренда вилочных погрузчиков в москве</t>
+        </is>
+      </c>
+      <c r="D769" s="28" t="n">
+        <v>34</v>
+      </c>
+      <c r="E769" s="28" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="770">
+      <c r="A770" s="28" t="n">
+        <v>80</v>
+      </c>
+      <c r="B770" s="29" t="inlineStr">
+        <is>
+          <t>Аренда вилочного погрузчика: когда выгоднее покупки</t>
+        </is>
+      </c>
+      <c r="C770" s="29" t="inlineStr">
         <is>
           <t>аренда вилочного погрузчика с оператором</t>
         </is>
       </c>
-      <c r="D742" s="28" t="n">
+      <c r="D770" s="28" t="n">
         <v>31</v>
       </c>
-      <c r="E742" s="28" t="n">
+      <c r="E770" s="28" t="n">
         <v>10</v>
       </c>
     </row>
@@ -19775,7 +20489,7 @@
     <row r="4" ht="60" customHeight="1">
       <c r="A4" s="31" t="inlineStr">
         <is>
-          <t>По вашей просьбе больше не укрупняю темы ради солидного объёма показов на статью — дроблю до предела: одна статья на каждый различимый интент, даже если у него 15–30 показов. Было 26 статей, потом 37, теперь 77. Все 27 брендов, которые раньше частично шли группами, теперь по отдельности, кроме «Кара» (не бренд, а жаргонное название техники) и обзорной статьи про советские марки в целом. Навесное оборудование и запчасти разбиты по узлам: 10 статей про навеску, 11 про запчасти. Тип привода — теперь 4 статьи вместо одной (сравнение + отдельно электро, дизель, газ). Виды — 3 отдельные статьи вместо одной обзорной.</t>
+          <t>По вашей просьбе больше не укрупняю темы ради солидного объёма показов на статью — дроблю до предела: одна статья на каждый различимый интент, даже если у него 15–30 показов. Было 26 статей, потом 37, теперь 80. Все 27 брендов, которые раньше частично шли группами, теперь по отдельности, кроме «Кара» (не бренд, а жаргонное название техники) и обзорной статьи про советские марки в целом. Навесное оборудование и запчасти разбиты по узлам: 10 статей про навеску, 11 про запчасти. Тип привода — теперь 4 статьи вместо одной (сравнение + отдельно электро, дизель, газ). Виды — 3 отдельные статьи вместо одной обзорной.</t>
         </is>
       </c>
     </row>
@@ -19867,7 +20581,7 @@
     <row r="20" ht="60" customHeight="1">
       <c r="A20" s="31" t="inlineStr">
         <is>
-          <t>3 статьи в неделю, кроме первой (только хаб — на него ссылаются все остальные). Весь план — 27 недель, это примерно 6.2 месяцев. При 77 статьях меньший темп растянет план почти на год — решайте по своим силам: если пишете сами, лучше реалистичный темп с полной структурой на каждой статье, чем ускоренный график с пустыми заглушками. Тонкие узкие статьи (запчасти, навеска) можно писать быстрее — по 500–800 слов на статью час-полтора работы; крупные (хаб, статьи выбора, покупка) требуют больше времени, закладывайте это при планировании недели.</t>
+          <t>3 статьи в неделю, кроме первой (только хаб — на него ссылаются все остальные). Весь план — 28 недель, это примерно 6.5 месяцев. При 80 статьях меньший темп растянет план почти на год — решайте по своим силам: если пишете сами, лучше реалистичный темп с полной структурой на каждой статье, чем ускоренный график с пустыми заглушками. Тонкие узкие статьи (запчасти, навеска) можно писать быстрее — по 500–800 слов на статью час-полтора работы; крупные (хаб, статьи выбора, покупка) требуют больше времени, закладывайте это при планировании недели.</t>
         </is>
       </c>
     </row>
@@ -19884,7 +20598,7 @@
     <row r="23" ht="60" customHeight="1">
       <c r="A23" s="31" t="inlineStr">
         <is>
-          <t>Каждая фраза закреплена ровно за одной статьёй — проверено программно на всех 77 статьях, дублей нет. При таком дроблении риск каннибализации выше, чем при крупных статьях, — держите правило строго: если пишете сами и видите, что тема пересекается с уже опубликованной статьёй, не создавайте новую страницу, а дополните существующую.</t>
+          <t>Каждая фраза закреплена ровно за одной статьёй — проверено программно на всех 80 статьях, дублей нет. При таком дроблении риск каннибализации выше, чем при крупных статьях, — держите правило строго: если пишете сами и видите, что тема пересекается с уже опубликованной статьёй, не создавайте новую страницу, а дополните существующую.</t>
         </is>
       </c>
     </row>
